--- a/packages/server/src/arpa_reporter/data/treasury/project236BulkUpload.xlsx
+++ b/packages/server/src/arpa_reporter/data/treasury/project236BulkUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29622"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Documents\Projects\arpa-reporter\packages\server\src\arpa_reporter\data\treasury\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kgu82\Desktop\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\SLFRFBulkUploadTemplates\Quarter 4 2025 Project Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA680FAB-61CD-45C9-A45F-1BB12014889D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{41B42A82-67CF-4A6D-AFF3-05880679AC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E51384B2-B241-45D4-BAA7-7EFD54A5982A}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22875" windowHeight="13141" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -511,7 +511,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -586,12 +586,18 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -684,7 +690,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -932,7 +938,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ1000"/>
-  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="57.5" style="3" customWidth="1"/>
     <col min="2" max="20" width="35.5" style="3" customWidth="1"/>
@@ -944,7 +950,7 @@
     <col min="37" max="16384" width="12.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" ht="13.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -984,7 +990,7 @@
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
     </row>
-    <row r="2" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" ht="13.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1024,7 +1030,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
     </row>
-    <row r="3" spans="1:36" ht="210.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" ht="210.95" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -1064,7 +1070,7 @@
       <c r="AI3" s="2"/>
       <c r="AJ3" s="2"/>
     </row>
-    <row r="4" spans="1:36" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" ht="76.5" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1174,7 +1180,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>39</v>
       </c>
@@ -1284,7 +1290,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="51" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" ht="52.9">
       <c r="A6" s="4" t="s">
         <v>43</v>
       </c>
@@ -1394,7 +1400,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="408.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" ht="408.95" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>78</v>
       </c>
@@ -1504,7 +1510,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="75.2" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" ht="75.2" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1542,7 +1548,7 @@
       <c r="AI8" s="2"/>
       <c r="AJ8" s="2"/>
     </row>
-    <row r="9" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" ht="13.15">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1580,7 +1586,7 @@
       <c r="AI9" s="2"/>
       <c r="AJ9" s="2"/>
     </row>
-    <row r="10" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" ht="13.15">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1618,7 +1624,7 @@
       <c r="AI10" s="2"/>
       <c r="AJ10" s="2"/>
     </row>
-    <row r="11" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" ht="13.15">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1656,7 +1662,7 @@
       <c r="AI11" s="2"/>
       <c r="AJ11" s="2"/>
     </row>
-    <row r="12" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" ht="13.15">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1694,7 +1700,7 @@
       <c r="AI12" s="2"/>
       <c r="AJ12" s="2"/>
     </row>
-    <row r="13" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" ht="13.15">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1732,7 +1738,7 @@
       <c r="AI13" s="2"/>
       <c r="AJ13" s="2"/>
     </row>
-    <row r="14" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" ht="13.15">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1770,7 +1776,7 @@
       <c r="AI14" s="2"/>
       <c r="AJ14" s="2"/>
     </row>
-    <row r="15" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" ht="13.15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1808,7 +1814,7 @@
       <c r="AI15" s="2"/>
       <c r="AJ15" s="2"/>
     </row>
-    <row r="16" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" ht="13.15">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1846,7 +1852,7 @@
       <c r="AI16" s="2"/>
       <c r="AJ16" s="2"/>
     </row>
-    <row r="17" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" ht="13.15">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1884,7 +1890,7 @@
       <c r="AI17" s="2"/>
       <c r="AJ17" s="2"/>
     </row>
-    <row r="18" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" ht="13.15">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1922,7 +1928,7 @@
       <c r="AI18" s="2"/>
       <c r="AJ18" s="2"/>
     </row>
-    <row r="19" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" ht="13.15">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1960,7 +1966,7 @@
       <c r="AI19" s="2"/>
       <c r="AJ19" s="2"/>
     </row>
-    <row r="20" spans="1:36" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:36" ht="13.15">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1998,7 +2004,7 @@
       <c r="AI20" s="2"/>
       <c r="AJ20" s="2"/>
     </row>
-    <row r="21" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" ht="15.95" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2036,7 +2042,7 @@
       <c r="AI21" s="2"/>
       <c r="AJ21" s="2"/>
     </row>
-    <row r="22" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:36" ht="15.95" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2074,7 +2080,7 @@
       <c r="AI22" s="2"/>
       <c r="AJ22" s="2"/>
     </row>
-    <row r="23" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:36" ht="15.95" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2112,7 +2118,7 @@
       <c r="AI23" s="2"/>
       <c r="AJ23" s="2"/>
     </row>
-    <row r="24" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:36" ht="15.95" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2150,7 +2156,7 @@
       <c r="AI24" s="2"/>
       <c r="AJ24" s="2"/>
     </row>
-    <row r="25" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:36" ht="15.95" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2188,7 +2194,7 @@
       <c r="AI25" s="2"/>
       <c r="AJ25" s="2"/>
     </row>
-    <row r="26" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:36" ht="15.95" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2226,7 +2232,7 @@
       <c r="AI26" s="2"/>
       <c r="AJ26" s="2"/>
     </row>
-    <row r="27" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:36" ht="15.95" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2264,7 +2270,7 @@
       <c r="AI27" s="2"/>
       <c r="AJ27" s="2"/>
     </row>
-    <row r="28" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:36" ht="15.95" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2302,7 +2308,7 @@
       <c r="AI28" s="2"/>
       <c r="AJ28" s="2"/>
     </row>
-    <row r="29" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:36" ht="15.95" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2340,7 +2346,7 @@
       <c r="AI29" s="2"/>
       <c r="AJ29" s="2"/>
     </row>
-    <row r="30" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:36" ht="15.95" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2378,7 +2384,7 @@
       <c r="AI30" s="2"/>
       <c r="AJ30" s="2"/>
     </row>
-    <row r="31" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:36" ht="15.95" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2416,7 +2422,7 @@
       <c r="AI31" s="2"/>
       <c r="AJ31" s="2"/>
     </row>
-    <row r="32" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:36" ht="15.95" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2454,7 +2460,7 @@
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
     </row>
-    <row r="33" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:36" ht="15.95" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2492,7 +2498,7 @@
       <c r="AI33" s="2"/>
       <c r="AJ33" s="2"/>
     </row>
-    <row r="34" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:36" ht="15.95" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2530,7 +2536,7 @@
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
     </row>
-    <row r="35" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:36" ht="15.95" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2568,7 +2574,7 @@
       <c r="AI35" s="2"/>
       <c r="AJ35" s="2"/>
     </row>
-    <row r="36" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:36" ht="15.95" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2606,7 +2612,7 @@
       <c r="AI36" s="2"/>
       <c r="AJ36" s="2"/>
     </row>
-    <row r="37" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:36" ht="15.95" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2644,7 +2650,7 @@
       <c r="AI37" s="2"/>
       <c r="AJ37" s="2"/>
     </row>
-    <row r="38" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:36" ht="15.95" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2682,7 +2688,7 @@
       <c r="AI38" s="2"/>
       <c r="AJ38" s="2"/>
     </row>
-    <row r="39" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:36" ht="15.95" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2720,7 +2726,7 @@
       <c r="AI39" s="2"/>
       <c r="AJ39" s="2"/>
     </row>
-    <row r="40" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:36" ht="15.95" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2758,7 +2764,7 @@
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
     </row>
-    <row r="41" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:36" ht="15.95" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2796,7 +2802,7 @@
       <c r="AI41" s="2"/>
       <c r="AJ41" s="2"/>
     </row>
-    <row r="42" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:36" ht="15.95" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2834,7 +2840,7 @@
       <c r="AI42" s="2"/>
       <c r="AJ42" s="2"/>
     </row>
-    <row r="43" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:36" ht="15.95" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2872,7 +2878,7 @@
       <c r="AI43" s="2"/>
       <c r="AJ43" s="2"/>
     </row>
-    <row r="44" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:36" ht="15.95" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2910,7 +2916,7 @@
       <c r="AI44" s="2"/>
       <c r="AJ44" s="2"/>
     </row>
-    <row r="45" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:36" ht="15.95" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2948,7 +2954,7 @@
       <c r="AI45" s="2"/>
       <c r="AJ45" s="2"/>
     </row>
-    <row r="46" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:36" ht="15.95" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2986,7 +2992,7 @@
       <c r="AI46" s="2"/>
       <c r="AJ46" s="2"/>
     </row>
-    <row r="47" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:36" ht="15.95" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3024,7 +3030,7 @@
       <c r="AI47" s="2"/>
       <c r="AJ47" s="2"/>
     </row>
-    <row r="48" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:36" ht="15.95" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3062,7 +3068,7 @@
       <c r="AI48" s="2"/>
       <c r="AJ48" s="2"/>
     </row>
-    <row r="49" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:36" ht="15.95" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -3100,7 +3106,7 @@
       <c r="AI49" s="2"/>
       <c r="AJ49" s="2"/>
     </row>
-    <row r="50" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:36" ht="15.95" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3138,7 +3144,7 @@
       <c r="AI50" s="2"/>
       <c r="AJ50" s="2"/>
     </row>
-    <row r="51" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:36" ht="15.95" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3176,7 +3182,7 @@
       <c r="AI51" s="2"/>
       <c r="AJ51" s="2"/>
     </row>
-    <row r="52" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:36" ht="15.95" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3214,7 +3220,7 @@
       <c r="AI52" s="2"/>
       <c r="AJ52" s="2"/>
     </row>
-    <row r="53" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:36" ht="15.95" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3252,7 +3258,7 @@
       <c r="AI53" s="2"/>
       <c r="AJ53" s="2"/>
     </row>
-    <row r="54" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:36" ht="15.95" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3290,7 +3296,7 @@
       <c r="AI54" s="2"/>
       <c r="AJ54" s="2"/>
     </row>
-    <row r="55" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:36" ht="15.95" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3328,7 +3334,7 @@
       <c r="AI55" s="2"/>
       <c r="AJ55" s="2"/>
     </row>
-    <row r="56" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:36" ht="15.95" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3366,7 +3372,7 @@
       <c r="AI56" s="2"/>
       <c r="AJ56" s="2"/>
     </row>
-    <row r="57" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:36" ht="15.95" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3404,7 +3410,7 @@
       <c r="AI57" s="2"/>
       <c r="AJ57" s="2"/>
     </row>
-    <row r="58" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:36" ht="15.95" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3442,7 +3448,7 @@
       <c r="AI58" s="2"/>
       <c r="AJ58" s="2"/>
     </row>
-    <row r="59" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:36" ht="15.95" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3480,7 +3486,7 @@
       <c r="AI59" s="2"/>
       <c r="AJ59" s="2"/>
     </row>
-    <row r="60" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:36" ht="15.95" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -3518,7 +3524,7 @@
       <c r="AI60" s="2"/>
       <c r="AJ60" s="2"/>
     </row>
-    <row r="61" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:36" ht="15.95" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3556,7 +3562,7 @@
       <c r="AI61" s="2"/>
       <c r="AJ61" s="2"/>
     </row>
-    <row r="62" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:36" ht="15.95" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3594,7 +3600,7 @@
       <c r="AI62" s="2"/>
       <c r="AJ62" s="2"/>
     </row>
-    <row r="63" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:36" ht="15.95" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3632,7 +3638,7 @@
       <c r="AI63" s="2"/>
       <c r="AJ63" s="2"/>
     </row>
-    <row r="64" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:36" ht="15.95" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3670,7 +3676,7 @@
       <c r="AI64" s="2"/>
       <c r="AJ64" s="2"/>
     </row>
-    <row r="65" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:36" ht="15.95" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -3708,7 +3714,7 @@
       <c r="AI65" s="2"/>
       <c r="AJ65" s="2"/>
     </row>
-    <row r="66" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:36" ht="15.95" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -3746,7 +3752,7 @@
       <c r="AI66" s="2"/>
       <c r="AJ66" s="2"/>
     </row>
-    <row r="67" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:36" ht="15.95" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3784,7 +3790,7 @@
       <c r="AI67" s="2"/>
       <c r="AJ67" s="2"/>
     </row>
-    <row r="68" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:36" ht="15.95" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3822,7 +3828,7 @@
       <c r="AI68" s="2"/>
       <c r="AJ68" s="2"/>
     </row>
-    <row r="69" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:36" ht="15.95" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3860,7 +3866,7 @@
       <c r="AI69" s="2"/>
       <c r="AJ69" s="2"/>
     </row>
-    <row r="70" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:36" ht="15.95" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3898,7 +3904,7 @@
       <c r="AI70" s="2"/>
       <c r="AJ70" s="2"/>
     </row>
-    <row r="71" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:36" ht="15.95" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3936,7 +3942,7 @@
       <c r="AI71" s="2"/>
       <c r="AJ71" s="2"/>
     </row>
-    <row r="72" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:36" ht="15.95" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3974,7 +3980,7 @@
       <c r="AI72" s="2"/>
       <c r="AJ72" s="2"/>
     </row>
-    <row r="73" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:36" ht="15.95" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -4012,7 +4018,7 @@
       <c r="AI73" s="2"/>
       <c r="AJ73" s="2"/>
     </row>
-    <row r="74" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:36" ht="15.95" customHeight="1">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -4050,7 +4056,7 @@
       <c r="AI74" s="2"/>
       <c r="AJ74" s="2"/>
     </row>
-    <row r="75" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:36" ht="15.95" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -4088,7 +4094,7 @@
       <c r="AI75" s="2"/>
       <c r="AJ75" s="2"/>
     </row>
-    <row r="76" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:36" ht="15.95" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -4126,7 +4132,7 @@
       <c r="AI76" s="2"/>
       <c r="AJ76" s="2"/>
     </row>
-    <row r="77" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:36" ht="15.95" customHeight="1">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4164,7 +4170,7 @@
       <c r="AI77" s="2"/>
       <c r="AJ77" s="2"/>
     </row>
-    <row r="78" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:36" ht="15.95" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -4202,7 +4208,7 @@
       <c r="AI78" s="2"/>
       <c r="AJ78" s="2"/>
     </row>
-    <row r="79" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:36" ht="15.95" customHeight="1">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -4240,7 +4246,7 @@
       <c r="AI79" s="2"/>
       <c r="AJ79" s="2"/>
     </row>
-    <row r="80" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:36" ht="15.95" customHeight="1">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -4278,7 +4284,7 @@
       <c r="AI80" s="2"/>
       <c r="AJ80" s="2"/>
     </row>
-    <row r="81" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:36" ht="15.95" customHeight="1">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -4316,7 +4322,7 @@
       <c r="AI81" s="2"/>
       <c r="AJ81" s="2"/>
     </row>
-    <row r="82" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:36" ht="15.95" customHeight="1">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -4354,7 +4360,7 @@
       <c r="AI82" s="2"/>
       <c r="AJ82" s="2"/>
     </row>
-    <row r="83" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:36" ht="15.95" customHeight="1">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -4392,7 +4398,7 @@
       <c r="AI83" s="2"/>
       <c r="AJ83" s="2"/>
     </row>
-    <row r="84" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:36" ht="15.95" customHeight="1">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4430,7 +4436,7 @@
       <c r="AI84" s="2"/>
       <c r="AJ84" s="2"/>
     </row>
-    <row r="85" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:36" ht="15.95" customHeight="1">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -4468,7 +4474,7 @@
       <c r="AI85" s="2"/>
       <c r="AJ85" s="2"/>
     </row>
-    <row r="86" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:36" ht="15.95" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4506,7 +4512,7 @@
       <c r="AI86" s="2"/>
       <c r="AJ86" s="2"/>
     </row>
-    <row r="87" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:36" ht="15.95" customHeight="1">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4544,7 +4550,7 @@
       <c r="AI87" s="2"/>
       <c r="AJ87" s="2"/>
     </row>
-    <row r="88" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:36" ht="15.95" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -4582,7 +4588,7 @@
       <c r="AI88" s="2"/>
       <c r="AJ88" s="2"/>
     </row>
-    <row r="89" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:36" ht="15.95" customHeight="1">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -4620,7 +4626,7 @@
       <c r="AI89" s="2"/>
       <c r="AJ89" s="2"/>
     </row>
-    <row r="90" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:36" ht="15.95" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -4658,7 +4664,7 @@
       <c r="AI90" s="2"/>
       <c r="AJ90" s="2"/>
     </row>
-    <row r="91" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:36" ht="15.95" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -4696,7 +4702,7 @@
       <c r="AI91" s="2"/>
       <c r="AJ91" s="2"/>
     </row>
-    <row r="92" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:36" ht="15.95" customHeight="1">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -4734,7 +4740,7 @@
       <c r="AI92" s="2"/>
       <c r="AJ92" s="2"/>
     </row>
-    <row r="93" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:36" ht="15.95" customHeight="1">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -4772,7 +4778,7 @@
       <c r="AI93" s="2"/>
       <c r="AJ93" s="2"/>
     </row>
-    <row r="94" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:36" ht="15.95" customHeight="1">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4810,7 +4816,7 @@
       <c r="AI94" s="2"/>
       <c r="AJ94" s="2"/>
     </row>
-    <row r="95" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:36" ht="15.95" customHeight="1">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -4848,7 +4854,7 @@
       <c r="AI95" s="2"/>
       <c r="AJ95" s="2"/>
     </row>
-    <row r="96" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:36" ht="15.95" customHeight="1">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -4886,7 +4892,7 @@
       <c r="AI96" s="2"/>
       <c r="AJ96" s="2"/>
     </row>
-    <row r="97" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:36" ht="15.95" customHeight="1">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -4924,7 +4930,7 @@
       <c r="AI97" s="2"/>
       <c r="AJ97" s="2"/>
     </row>
-    <row r="98" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:36" ht="15.95" customHeight="1">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -4962,7 +4968,7 @@
       <c r="AI98" s="2"/>
       <c r="AJ98" s="2"/>
     </row>
-    <row r="99" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:36" ht="15.95" customHeight="1">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -5000,7 +5006,7 @@
       <c r="AI99" s="2"/>
       <c r="AJ99" s="2"/>
     </row>
-    <row r="100" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:36" ht="15.95" customHeight="1">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -5038,7 +5044,7 @@
       <c r="AI100" s="2"/>
       <c r="AJ100" s="2"/>
     </row>
-    <row r="101" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:36" ht="15.95" customHeight="1">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -5076,7 +5082,7 @@
       <c r="AI101" s="2"/>
       <c r="AJ101" s="2"/>
     </row>
-    <row r="102" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:36" ht="15.95" customHeight="1">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -5114,7 +5120,7 @@
       <c r="AI102" s="2"/>
       <c r="AJ102" s="2"/>
     </row>
-    <row r="103" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:36" ht="15.95" customHeight="1">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -5152,7 +5158,7 @@
       <c r="AI103" s="2"/>
       <c r="AJ103" s="2"/>
     </row>
-    <row r="104" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:36" ht="15.95" customHeight="1">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -5190,7 +5196,7 @@
       <c r="AI104" s="2"/>
       <c r="AJ104" s="2"/>
     </row>
-    <row r="105" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:36" ht="15.95" customHeight="1">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -5228,7 +5234,7 @@
       <c r="AI105" s="2"/>
       <c r="AJ105" s="2"/>
     </row>
-    <row r="106" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:36" ht="15.95" customHeight="1">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -5266,7 +5272,7 @@
       <c r="AI106" s="2"/>
       <c r="AJ106" s="2"/>
     </row>
-    <row r="107" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:36" ht="15.95" customHeight="1">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -5304,7 +5310,7 @@
       <c r="AI107" s="2"/>
       <c r="AJ107" s="2"/>
     </row>
-    <row r="108" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:36" ht="15.95" customHeight="1">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -5342,7 +5348,7 @@
       <c r="AI108" s="2"/>
       <c r="AJ108" s="2"/>
     </row>
-    <row r="109" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:36" ht="15.95" customHeight="1">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -5380,7 +5386,7 @@
       <c r="AI109" s="2"/>
       <c r="AJ109" s="2"/>
     </row>
-    <row r="110" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:36" ht="15.95" customHeight="1">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -5418,7 +5424,7 @@
       <c r="AI110" s="2"/>
       <c r="AJ110" s="2"/>
     </row>
-    <row r="111" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:36" ht="15.95" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -5456,7 +5462,7 @@
       <c r="AI111" s="2"/>
       <c r="AJ111" s="2"/>
     </row>
-    <row r="112" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:36" ht="15.95" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -5494,7 +5500,7 @@
       <c r="AI112" s="2"/>
       <c r="AJ112" s="2"/>
     </row>
-    <row r="113" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:36" ht="15.95" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -5532,7 +5538,7 @@
       <c r="AI113" s="2"/>
       <c r="AJ113" s="2"/>
     </row>
-    <row r="114" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:36" ht="15.95" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -5570,7 +5576,7 @@
       <c r="AI114" s="2"/>
       <c r="AJ114" s="2"/>
     </row>
-    <row r="115" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:36" ht="15.95" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -5608,7 +5614,7 @@
       <c r="AI115" s="2"/>
       <c r="AJ115" s="2"/>
     </row>
-    <row r="116" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:36" ht="15.95" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -5646,7 +5652,7 @@
       <c r="AI116" s="2"/>
       <c r="AJ116" s="2"/>
     </row>
-    <row r="117" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:36" ht="15.95" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -5684,7 +5690,7 @@
       <c r="AI117" s="2"/>
       <c r="AJ117" s="2"/>
     </row>
-    <row r="118" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:36" ht="15.95" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -5722,7 +5728,7 @@
       <c r="AI118" s="2"/>
       <c r="AJ118" s="2"/>
     </row>
-    <row r="119" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:36" ht="15.95" customHeight="1">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -5760,7 +5766,7 @@
       <c r="AI119" s="2"/>
       <c r="AJ119" s="2"/>
     </row>
-    <row r="120" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:36" ht="15.95" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -5798,7 +5804,7 @@
       <c r="AI120" s="2"/>
       <c r="AJ120" s="2"/>
     </row>
-    <row r="121" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:36" ht="15.95" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -5836,7 +5842,7 @@
       <c r="AI121" s="2"/>
       <c r="AJ121" s="2"/>
     </row>
-    <row r="122" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:36" ht="15.95" customHeight="1">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -5874,7 +5880,7 @@
       <c r="AI122" s="2"/>
       <c r="AJ122" s="2"/>
     </row>
-    <row r="123" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:36" ht="15.95" customHeight="1">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -5912,7 +5918,7 @@
       <c r="AI123" s="2"/>
       <c r="AJ123" s="2"/>
     </row>
-    <row r="124" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:36" ht="15.95" customHeight="1">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -5950,7 +5956,7 @@
       <c r="AI124" s="2"/>
       <c r="AJ124" s="2"/>
     </row>
-    <row r="125" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:36" ht="15.95" customHeight="1">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -5988,7 +5994,7 @@
       <c r="AI125" s="2"/>
       <c r="AJ125" s="2"/>
     </row>
-    <row r="126" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:36" ht="15.95" customHeight="1">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -6026,7 +6032,7 @@
       <c r="AI126" s="2"/>
       <c r="AJ126" s="2"/>
     </row>
-    <row r="127" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:36" ht="15.95" customHeight="1">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -6064,7 +6070,7 @@
       <c r="AI127" s="2"/>
       <c r="AJ127" s="2"/>
     </row>
-    <row r="128" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:36" ht="15.95" customHeight="1">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -6102,7 +6108,7 @@
       <c r="AI128" s="2"/>
       <c r="AJ128" s="2"/>
     </row>
-    <row r="129" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:36" ht="15.95" customHeight="1">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -6140,7 +6146,7 @@
       <c r="AI129" s="2"/>
       <c r="AJ129" s="2"/>
     </row>
-    <row r="130" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:36" ht="15.95" customHeight="1">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -6178,7 +6184,7 @@
       <c r="AI130" s="2"/>
       <c r="AJ130" s="2"/>
     </row>
-    <row r="131" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:36" ht="15.95" customHeight="1">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -6216,7 +6222,7 @@
       <c r="AI131" s="2"/>
       <c r="AJ131" s="2"/>
     </row>
-    <row r="132" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:36" ht="15.95" customHeight="1">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -6254,7 +6260,7 @@
       <c r="AI132" s="2"/>
       <c r="AJ132" s="2"/>
     </row>
-    <row r="133" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:36" ht="15.95" customHeight="1">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -6292,7 +6298,7 @@
       <c r="AI133" s="2"/>
       <c r="AJ133" s="2"/>
     </row>
-    <row r="134" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:36" ht="15.95" customHeight="1">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -6330,7 +6336,7 @@
       <c r="AI134" s="2"/>
       <c r="AJ134" s="2"/>
     </row>
-    <row r="135" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:36" ht="15.95" customHeight="1">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -6368,7 +6374,7 @@
       <c r="AI135" s="2"/>
       <c r="AJ135" s="2"/>
     </row>
-    <row r="136" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:36" ht="15.95" customHeight="1">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -6406,7 +6412,7 @@
       <c r="AI136" s="2"/>
       <c r="AJ136" s="2"/>
     </row>
-    <row r="137" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:36" ht="15.95" customHeight="1">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -6444,7 +6450,7 @@
       <c r="AI137" s="2"/>
       <c r="AJ137" s="2"/>
     </row>
-    <row r="138" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:36" ht="15.95" customHeight="1">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -6482,7 +6488,7 @@
       <c r="AI138" s="2"/>
       <c r="AJ138" s="2"/>
     </row>
-    <row r="139" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:36" ht="15.95" customHeight="1">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -6520,7 +6526,7 @@
       <c r="AI139" s="2"/>
       <c r="AJ139" s="2"/>
     </row>
-    <row r="140" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:36" ht="15.95" customHeight="1">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -6558,7 +6564,7 @@
       <c r="AI140" s="2"/>
       <c r="AJ140" s="2"/>
     </row>
-    <row r="141" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:36" ht="15.95" customHeight="1">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -6596,7 +6602,7 @@
       <c r="AI141" s="2"/>
       <c r="AJ141" s="2"/>
     </row>
-    <row r="142" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:36" ht="15.95" customHeight="1">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -6634,7 +6640,7 @@
       <c r="AI142" s="2"/>
       <c r="AJ142" s="2"/>
     </row>
-    <row r="143" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:36" ht="15.95" customHeight="1">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -6672,7 +6678,7 @@
       <c r="AI143" s="2"/>
       <c r="AJ143" s="2"/>
     </row>
-    <row r="144" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:36" ht="15.95" customHeight="1">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -6710,7 +6716,7 @@
       <c r="AI144" s="2"/>
       <c r="AJ144" s="2"/>
     </row>
-    <row r="145" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:36" ht="15.95" customHeight="1">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -6748,7 +6754,7 @@
       <c r="AI145" s="2"/>
       <c r="AJ145" s="2"/>
     </row>
-    <row r="146" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:36" ht="15.95" customHeight="1">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -6786,7 +6792,7 @@
       <c r="AI146" s="2"/>
       <c r="AJ146" s="2"/>
     </row>
-    <row r="147" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:36" ht="15.95" customHeight="1">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -6824,7 +6830,7 @@
       <c r="AI147" s="2"/>
       <c r="AJ147" s="2"/>
     </row>
-    <row r="148" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:36" ht="15.95" customHeight="1">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -6862,7 +6868,7 @@
       <c r="AI148" s="2"/>
       <c r="AJ148" s="2"/>
     </row>
-    <row r="149" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:36" ht="15.95" customHeight="1">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -6900,7 +6906,7 @@
       <c r="AI149" s="2"/>
       <c r="AJ149" s="2"/>
     </row>
-    <row r="150" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:36" ht="15.95" customHeight="1">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -6938,7 +6944,7 @@
       <c r="AI150" s="2"/>
       <c r="AJ150" s="2"/>
     </row>
-    <row r="151" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:36" ht="15.95" customHeight="1">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -6976,7 +6982,7 @@
       <c r="AI151" s="2"/>
       <c r="AJ151" s="2"/>
     </row>
-    <row r="152" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:36" ht="15.95" customHeight="1">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -7014,7 +7020,7 @@
       <c r="AI152" s="2"/>
       <c r="AJ152" s="2"/>
     </row>
-    <row r="153" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:36" ht="15.95" customHeight="1">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -7052,7 +7058,7 @@
       <c r="AI153" s="2"/>
       <c r="AJ153" s="2"/>
     </row>
-    <row r="154" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:36" ht="15.95" customHeight="1">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -7090,7 +7096,7 @@
       <c r="AI154" s="2"/>
       <c r="AJ154" s="2"/>
     </row>
-    <row r="155" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:36" ht="15.95" customHeight="1">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -7128,7 +7134,7 @@
       <c r="AI155" s="2"/>
       <c r="AJ155" s="2"/>
     </row>
-    <row r="156" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:36" ht="15.95" customHeight="1">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -7166,7 +7172,7 @@
       <c r="AI156" s="2"/>
       <c r="AJ156" s="2"/>
     </row>
-    <row r="157" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:36" ht="15.95" customHeight="1">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -7204,7 +7210,7 @@
       <c r="AI157" s="2"/>
       <c r="AJ157" s="2"/>
     </row>
-    <row r="158" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:36" ht="15.95" customHeight="1">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -7242,7 +7248,7 @@
       <c r="AI158" s="2"/>
       <c r="AJ158" s="2"/>
     </row>
-    <row r="159" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:36" ht="15.95" customHeight="1">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -7280,7 +7286,7 @@
       <c r="AI159" s="2"/>
       <c r="AJ159" s="2"/>
     </row>
-    <row r="160" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:36" ht="15.95" customHeight="1">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -7318,7 +7324,7 @@
       <c r="AI160" s="2"/>
       <c r="AJ160" s="2"/>
     </row>
-    <row r="161" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:36" ht="15.95" customHeight="1">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -7356,7 +7362,7 @@
       <c r="AI161" s="2"/>
       <c r="AJ161" s="2"/>
     </row>
-    <row r="162" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:36" ht="15.95" customHeight="1">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -7394,7 +7400,7 @@
       <c r="AI162" s="2"/>
       <c r="AJ162" s="2"/>
     </row>
-    <row r="163" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:36" ht="15.95" customHeight="1">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -7432,7 +7438,7 @@
       <c r="AI163" s="2"/>
       <c r="AJ163" s="2"/>
     </row>
-    <row r="164" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:36" ht="15.95" customHeight="1">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -7470,7 +7476,7 @@
       <c r="AI164" s="2"/>
       <c r="AJ164" s="2"/>
     </row>
-    <row r="165" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:36" ht="15.95" customHeight="1">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -7508,7 +7514,7 @@
       <c r="AI165" s="2"/>
       <c r="AJ165" s="2"/>
     </row>
-    <row r="166" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:36" ht="15.95" customHeight="1">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -7546,7 +7552,7 @@
       <c r="AI166" s="2"/>
       <c r="AJ166" s="2"/>
     </row>
-    <row r="167" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:36" ht="15.95" customHeight="1">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -7584,7 +7590,7 @@
       <c r="AI167" s="2"/>
       <c r="AJ167" s="2"/>
     </row>
-    <row r="168" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:36" ht="15.95" customHeight="1">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -7622,7 +7628,7 @@
       <c r="AI168" s="2"/>
       <c r="AJ168" s="2"/>
     </row>
-    <row r="169" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:36" ht="15.95" customHeight="1">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -7660,7 +7666,7 @@
       <c r="AI169" s="2"/>
       <c r="AJ169" s="2"/>
     </row>
-    <row r="170" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:36" ht="15.95" customHeight="1">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -7698,7 +7704,7 @@
       <c r="AI170" s="2"/>
       <c r="AJ170" s="2"/>
     </row>
-    <row r="171" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:36" ht="15.95" customHeight="1">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -7736,7 +7742,7 @@
       <c r="AI171" s="2"/>
       <c r="AJ171" s="2"/>
     </row>
-    <row r="172" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:36" ht="15.95" customHeight="1">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -7774,7 +7780,7 @@
       <c r="AI172" s="2"/>
       <c r="AJ172" s="2"/>
     </row>
-    <row r="173" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:36" ht="15.95" customHeight="1">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -7812,7 +7818,7 @@
       <c r="AI173" s="2"/>
       <c r="AJ173" s="2"/>
     </row>
-    <row r="174" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:36" ht="15.95" customHeight="1">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -7850,7 +7856,7 @@
       <c r="AI174" s="2"/>
       <c r="AJ174" s="2"/>
     </row>
-    <row r="175" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:36" ht="15.95" customHeight="1">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -7888,7 +7894,7 @@
       <c r="AI175" s="2"/>
       <c r="AJ175" s="2"/>
     </row>
-    <row r="176" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:36" ht="15.95" customHeight="1">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -7926,7 +7932,7 @@
       <c r="AI176" s="2"/>
       <c r="AJ176" s="2"/>
     </row>
-    <row r="177" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:36" ht="15.95" customHeight="1">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -7964,7 +7970,7 @@
       <c r="AI177" s="2"/>
       <c r="AJ177" s="2"/>
     </row>
-    <row r="178" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:36" ht="15.95" customHeight="1">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -8002,7 +8008,7 @@
       <c r="AI178" s="2"/>
       <c r="AJ178" s="2"/>
     </row>
-    <row r="179" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:36" ht="15.95" customHeight="1">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -8040,7 +8046,7 @@
       <c r="AI179" s="2"/>
       <c r="AJ179" s="2"/>
     </row>
-    <row r="180" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:36" ht="15.95" customHeight="1">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -8078,7 +8084,7 @@
       <c r="AI180" s="2"/>
       <c r="AJ180" s="2"/>
     </row>
-    <row r="181" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:36" ht="15.95" customHeight="1">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -8116,7 +8122,7 @@
       <c r="AI181" s="2"/>
       <c r="AJ181" s="2"/>
     </row>
-    <row r="182" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:36" ht="15.95" customHeight="1">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -8154,7 +8160,7 @@
       <c r="AI182" s="2"/>
       <c r="AJ182" s="2"/>
     </row>
-    <row r="183" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:36" ht="15.95" customHeight="1">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -8192,7 +8198,7 @@
       <c r="AI183" s="2"/>
       <c r="AJ183" s="2"/>
     </row>
-    <row r="184" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:36" ht="15.95" customHeight="1">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -8230,7 +8236,7 @@
       <c r="AI184" s="2"/>
       <c r="AJ184" s="2"/>
     </row>
-    <row r="185" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:36" ht="15.95" customHeight="1">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -8268,7 +8274,7 @@
       <c r="AI185" s="2"/>
       <c r="AJ185" s="2"/>
     </row>
-    <row r="186" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:36" ht="15.95" customHeight="1">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -8306,7 +8312,7 @@
       <c r="AI186" s="2"/>
       <c r="AJ186" s="2"/>
     </row>
-    <row r="187" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:36" ht="15.95" customHeight="1">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -8344,7 +8350,7 @@
       <c r="AI187" s="2"/>
       <c r="AJ187" s="2"/>
     </row>
-    <row r="188" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:36" ht="15.95" customHeight="1">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -8382,7 +8388,7 @@
       <c r="AI188" s="2"/>
       <c r="AJ188" s="2"/>
     </row>
-    <row r="189" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:36" ht="15.95" customHeight="1">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -8420,7 +8426,7 @@
       <c r="AI189" s="2"/>
       <c r="AJ189" s="2"/>
     </row>
-    <row r="190" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:36" ht="15.95" customHeight="1">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -8458,7 +8464,7 @@
       <c r="AI190" s="2"/>
       <c r="AJ190" s="2"/>
     </row>
-    <row r="191" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:36" ht="15.95" customHeight="1">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -8496,7 +8502,7 @@
       <c r="AI191" s="2"/>
       <c r="AJ191" s="2"/>
     </row>
-    <row r="192" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:36" ht="15.95" customHeight="1">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -8534,7 +8540,7 @@
       <c r="AI192" s="2"/>
       <c r="AJ192" s="2"/>
     </row>
-    <row r="193" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:36" ht="15.95" customHeight="1">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -8572,7 +8578,7 @@
       <c r="AI193" s="2"/>
       <c r="AJ193" s="2"/>
     </row>
-    <row r="194" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:36" ht="15.95" customHeight="1">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -8610,7 +8616,7 @@
       <c r="AI194" s="2"/>
       <c r="AJ194" s="2"/>
     </row>
-    <row r="195" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:36" ht="15.95" customHeight="1">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -8648,7 +8654,7 @@
       <c r="AI195" s="2"/>
       <c r="AJ195" s="2"/>
     </row>
-    <row r="196" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:36" ht="15.95" customHeight="1">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -8686,7 +8692,7 @@
       <c r="AI196" s="2"/>
       <c r="AJ196" s="2"/>
     </row>
-    <row r="197" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:36" ht="15.95" customHeight="1">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -8724,7 +8730,7 @@
       <c r="AI197" s="2"/>
       <c r="AJ197" s="2"/>
     </row>
-    <row r="198" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:36" ht="15.95" customHeight="1">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -8762,7 +8768,7 @@
       <c r="AI198" s="2"/>
       <c r="AJ198" s="2"/>
     </row>
-    <row r="199" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:36" ht="15.95" customHeight="1">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -8800,7 +8806,7 @@
       <c r="AI199" s="2"/>
       <c r="AJ199" s="2"/>
     </row>
-    <row r="200" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:36" ht="15.95" customHeight="1">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -8838,7 +8844,7 @@
       <c r="AI200" s="2"/>
       <c r="AJ200" s="2"/>
     </row>
-    <row r="201" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:36" ht="15.95" customHeight="1">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -8876,7 +8882,7 @@
       <c r="AI201" s="2"/>
       <c r="AJ201" s="2"/>
     </row>
-    <row r="202" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:36" ht="15.95" customHeight="1">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -8914,7 +8920,7 @@
       <c r="AI202" s="2"/>
       <c r="AJ202" s="2"/>
     </row>
-    <row r="203" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:36" ht="15.95" customHeight="1">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -8952,7 +8958,7 @@
       <c r="AI203" s="2"/>
       <c r="AJ203" s="2"/>
     </row>
-    <row r="204" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:36" ht="15.95" customHeight="1">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -8990,7 +8996,7 @@
       <c r="AI204" s="2"/>
       <c r="AJ204" s="2"/>
     </row>
-    <row r="205" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:36" ht="15.95" customHeight="1">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -9028,7 +9034,7 @@
       <c r="AI205" s="2"/>
       <c r="AJ205" s="2"/>
     </row>
-    <row r="206" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:36" ht="15.95" customHeight="1">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -9066,7 +9072,7 @@
       <c r="AI206" s="2"/>
       <c r="AJ206" s="2"/>
     </row>
-    <row r="207" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:36" ht="15.95" customHeight="1">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -9104,7 +9110,7 @@
       <c r="AI207" s="2"/>
       <c r="AJ207" s="2"/>
     </row>
-    <row r="208" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:36" ht="15.95" customHeight="1">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -9142,7 +9148,7 @@
       <c r="AI208" s="2"/>
       <c r="AJ208" s="2"/>
     </row>
-    <row r="209" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:36" ht="15.95" customHeight="1">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -9180,7 +9186,7 @@
       <c r="AI209" s="2"/>
       <c r="AJ209" s="2"/>
     </row>
-    <row r="210" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:36" ht="15.95" customHeight="1">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -9218,7 +9224,7 @@
       <c r="AI210" s="2"/>
       <c r="AJ210" s="2"/>
     </row>
-    <row r="211" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:36" ht="15.95" customHeight="1">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -9256,7 +9262,7 @@
       <c r="AI211" s="2"/>
       <c r="AJ211" s="2"/>
     </row>
-    <row r="212" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:36" ht="15.95" customHeight="1">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -9294,7 +9300,7 @@
       <c r="AI212" s="2"/>
       <c r="AJ212" s="2"/>
     </row>
-    <row r="213" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:36" ht="15.95" customHeight="1">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -9332,7 +9338,7 @@
       <c r="AI213" s="2"/>
       <c r="AJ213" s="2"/>
     </row>
-    <row r="214" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:36" ht="15.95" customHeight="1">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -9370,7 +9376,7 @@
       <c r="AI214" s="2"/>
       <c r="AJ214" s="2"/>
     </row>
-    <row r="215" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:36" ht="15.95" customHeight="1">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -9408,7 +9414,7 @@
       <c r="AI215" s="2"/>
       <c r="AJ215" s="2"/>
     </row>
-    <row r="216" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:36" ht="15.95" customHeight="1">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -9446,7 +9452,7 @@
       <c r="AI216" s="2"/>
       <c r="AJ216" s="2"/>
     </row>
-    <row r="217" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:36" ht="15.95" customHeight="1">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -9484,7 +9490,7 @@
       <c r="AI217" s="2"/>
       <c r="AJ217" s="2"/>
     </row>
-    <row r="218" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:36" ht="15.95" customHeight="1">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -9522,7 +9528,7 @@
       <c r="AI218" s="2"/>
       <c r="AJ218" s="2"/>
     </row>
-    <row r="219" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:36" ht="15.95" customHeight="1">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -9560,7 +9566,7 @@
       <c r="AI219" s="2"/>
       <c r="AJ219" s="2"/>
     </row>
-    <row r="220" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:36" ht="15.95" customHeight="1">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -9598,7 +9604,7 @@
       <c r="AI220" s="2"/>
       <c r="AJ220" s="2"/>
     </row>
-    <row r="221" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:36" ht="15.95" customHeight="1">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -9636,7 +9642,7 @@
       <c r="AI221" s="2"/>
       <c r="AJ221" s="2"/>
     </row>
-    <row r="222" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:36" ht="15.95" customHeight="1">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -9674,7 +9680,7 @@
       <c r="AI222" s="2"/>
       <c r="AJ222" s="2"/>
     </row>
-    <row r="223" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:36" ht="15.95" customHeight="1">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -9712,7 +9718,7 @@
       <c r="AI223" s="2"/>
       <c r="AJ223" s="2"/>
     </row>
-    <row r="224" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:36" ht="15.95" customHeight="1">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -9750,7 +9756,7 @@
       <c r="AI224" s="2"/>
       <c r="AJ224" s="2"/>
     </row>
-    <row r="225" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:36" ht="15.95" customHeight="1">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -9788,7 +9794,7 @@
       <c r="AI225" s="2"/>
       <c r="AJ225" s="2"/>
     </row>
-    <row r="226" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:36" ht="15.95" customHeight="1">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -9826,7 +9832,7 @@
       <c r="AI226" s="2"/>
       <c r="AJ226" s="2"/>
     </row>
-    <row r="227" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:36" ht="15.95" customHeight="1">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -9864,7 +9870,7 @@
       <c r="AI227" s="2"/>
       <c r="AJ227" s="2"/>
     </row>
-    <row r="228" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:36" ht="15.95" customHeight="1">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -9902,7 +9908,7 @@
       <c r="AI228" s="2"/>
       <c r="AJ228" s="2"/>
     </row>
-    <row r="229" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:36" ht="15.95" customHeight="1">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -9940,7 +9946,7 @@
       <c r="AI229" s="2"/>
       <c r="AJ229" s="2"/>
     </row>
-    <row r="230" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:36" ht="15.95" customHeight="1">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -9978,7 +9984,7 @@
       <c r="AI230" s="2"/>
       <c r="AJ230" s="2"/>
     </row>
-    <row r="231" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:36" ht="15.95" customHeight="1">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -10016,7 +10022,7 @@
       <c r="AI231" s="2"/>
       <c r="AJ231" s="2"/>
     </row>
-    <row r="232" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:36" ht="15.95" customHeight="1">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -10054,7 +10060,7 @@
       <c r="AI232" s="2"/>
       <c r="AJ232" s="2"/>
     </row>
-    <row r="233" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:36" ht="15.95" customHeight="1">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -10092,7 +10098,7 @@
       <c r="AI233" s="2"/>
       <c r="AJ233" s="2"/>
     </row>
-    <row r="234" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:36" ht="15.95" customHeight="1">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -10130,7 +10136,7 @@
       <c r="AI234" s="2"/>
       <c r="AJ234" s="2"/>
     </row>
-    <row r="235" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:36" ht="15.95" customHeight="1">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -10168,7 +10174,7 @@
       <c r="AI235" s="2"/>
       <c r="AJ235" s="2"/>
     </row>
-    <row r="236" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:36" ht="15.95" customHeight="1">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -10206,7 +10212,7 @@
       <c r="AI236" s="2"/>
       <c r="AJ236" s="2"/>
     </row>
-    <row r="237" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:36" ht="15.95" customHeight="1">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -10244,7 +10250,7 @@
       <c r="AI237" s="2"/>
       <c r="AJ237" s="2"/>
     </row>
-    <row r="238" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:36" ht="15.95" customHeight="1">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -10282,7 +10288,7 @@
       <c r="AI238" s="2"/>
       <c r="AJ238" s="2"/>
     </row>
-    <row r="239" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:36" ht="15.95" customHeight="1">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -10320,7 +10326,7 @@
       <c r="AI239" s="2"/>
       <c r="AJ239" s="2"/>
     </row>
-    <row r="240" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:36" ht="15.95" customHeight="1">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -10358,7 +10364,7 @@
       <c r="AI240" s="2"/>
       <c r="AJ240" s="2"/>
     </row>
-    <row r="241" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:36" ht="15.95" customHeight="1">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -10396,7 +10402,7 @@
       <c r="AI241" s="2"/>
       <c r="AJ241" s="2"/>
     </row>
-    <row r="242" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:36" ht="15.95" customHeight="1">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -10434,7 +10440,7 @@
       <c r="AI242" s="2"/>
       <c r="AJ242" s="2"/>
     </row>
-    <row r="243" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:36" ht="15.95" customHeight="1">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -10472,7 +10478,7 @@
       <c r="AI243" s="2"/>
       <c r="AJ243" s="2"/>
     </row>
-    <row r="244" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:36" ht="15.95" customHeight="1">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -10510,7 +10516,7 @@
       <c r="AI244" s="2"/>
       <c r="AJ244" s="2"/>
     </row>
-    <row r="245" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:36" ht="15.95" customHeight="1">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -10548,7 +10554,7 @@
       <c r="AI245" s="2"/>
       <c r="AJ245" s="2"/>
     </row>
-    <row r="246" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:36" ht="15.95" customHeight="1">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -10586,7 +10592,7 @@
       <c r="AI246" s="2"/>
       <c r="AJ246" s="2"/>
     </row>
-    <row r="247" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:36" ht="15.95" customHeight="1">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -10624,7 +10630,7 @@
       <c r="AI247" s="2"/>
       <c r="AJ247" s="2"/>
     </row>
-    <row r="248" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:36" ht="15.95" customHeight="1">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -10662,7 +10668,7 @@
       <c r="AI248" s="2"/>
       <c r="AJ248" s="2"/>
     </row>
-    <row r="249" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:36" ht="15.95" customHeight="1">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -10700,7 +10706,7 @@
       <c r="AI249" s="2"/>
       <c r="AJ249" s="2"/>
     </row>
-    <row r="250" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:36" ht="15.95" customHeight="1">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -10738,7 +10744,7 @@
       <c r="AI250" s="2"/>
       <c r="AJ250" s="2"/>
     </row>
-    <row r="251" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:36" ht="15.95" customHeight="1">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -10776,7 +10782,7 @@
       <c r="AI251" s="2"/>
       <c r="AJ251" s="2"/>
     </row>
-    <row r="252" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:36" ht="15.95" customHeight="1">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -10814,7 +10820,7 @@
       <c r="AI252" s="2"/>
       <c r="AJ252" s="2"/>
     </row>
-    <row r="253" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:36" ht="15.95" customHeight="1">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -10852,7 +10858,7 @@
       <c r="AI253" s="2"/>
       <c r="AJ253" s="2"/>
     </row>
-    <row r="254" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:36" ht="15.95" customHeight="1">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -10890,7 +10896,7 @@
       <c r="AI254" s="2"/>
       <c r="AJ254" s="2"/>
     </row>
-    <row r="255" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:36" ht="15.95" customHeight="1">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -10928,7 +10934,7 @@
       <c r="AI255" s="2"/>
       <c r="AJ255" s="2"/>
     </row>
-    <row r="256" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:36" ht="15.95" customHeight="1">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -10966,7 +10972,7 @@
       <c r="AI256" s="2"/>
       <c r="AJ256" s="2"/>
     </row>
-    <row r="257" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:36" ht="15.95" customHeight="1">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -11004,7 +11010,7 @@
       <c r="AI257" s="2"/>
       <c r="AJ257" s="2"/>
     </row>
-    <row r="258" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:36" ht="15.95" customHeight="1">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -11042,7 +11048,7 @@
       <c r="AI258" s="2"/>
       <c r="AJ258" s="2"/>
     </row>
-    <row r="259" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:36" ht="15.95" customHeight="1">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -11080,7 +11086,7 @@
       <c r="AI259" s="2"/>
       <c r="AJ259" s="2"/>
     </row>
-    <row r="260" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:36" ht="15.95" customHeight="1">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -11118,7 +11124,7 @@
       <c r="AI260" s="2"/>
       <c r="AJ260" s="2"/>
     </row>
-    <row r="261" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:36" ht="15.95" customHeight="1">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -11156,7 +11162,7 @@
       <c r="AI261" s="2"/>
       <c r="AJ261" s="2"/>
     </row>
-    <row r="262" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:36" ht="15.95" customHeight="1">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -11194,7 +11200,7 @@
       <c r="AI262" s="2"/>
       <c r="AJ262" s="2"/>
     </row>
-    <row r="263" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:36" ht="15.95" customHeight="1">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -11232,7 +11238,7 @@
       <c r="AI263" s="2"/>
       <c r="AJ263" s="2"/>
     </row>
-    <row r="264" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:36" ht="15.95" customHeight="1">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -11270,7 +11276,7 @@
       <c r="AI264" s="2"/>
       <c r="AJ264" s="2"/>
     </row>
-    <row r="265" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:36" ht="15.95" customHeight="1">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -11308,7 +11314,7 @@
       <c r="AI265" s="2"/>
       <c r="AJ265" s="2"/>
     </row>
-    <row r="266" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:36" ht="15.95" customHeight="1">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -11346,7 +11352,7 @@
       <c r="AI266" s="2"/>
       <c r="AJ266" s="2"/>
     </row>
-    <row r="267" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:36" ht="15.95" customHeight="1">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -11384,7 +11390,7 @@
       <c r="AI267" s="2"/>
       <c r="AJ267" s="2"/>
     </row>
-    <row r="268" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:36" ht="15.95" customHeight="1">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -11422,7 +11428,7 @@
       <c r="AI268" s="2"/>
       <c r="AJ268" s="2"/>
     </row>
-    <row r="269" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:36" ht="15.95" customHeight="1">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -11460,7 +11466,7 @@
       <c r="AI269" s="2"/>
       <c r="AJ269" s="2"/>
     </row>
-    <row r="270" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:36" ht="15.95" customHeight="1">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -11498,7 +11504,7 @@
       <c r="AI270" s="2"/>
       <c r="AJ270" s="2"/>
     </row>
-    <row r="271" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:36" ht="15.95" customHeight="1">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -11536,7 +11542,7 @@
       <c r="AI271" s="2"/>
       <c r="AJ271" s="2"/>
     </row>
-    <row r="272" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:36" ht="15.95" customHeight="1">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -11574,7 +11580,7 @@
       <c r="AI272" s="2"/>
       <c r="AJ272" s="2"/>
     </row>
-    <row r="273" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:36" ht="15.95" customHeight="1">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -11612,7 +11618,7 @@
       <c r="AI273" s="2"/>
       <c r="AJ273" s="2"/>
     </row>
-    <row r="274" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:36" ht="15.95" customHeight="1">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -11650,7 +11656,7 @@
       <c r="AI274" s="2"/>
       <c r="AJ274" s="2"/>
     </row>
-    <row r="275" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:36" ht="15.95" customHeight="1">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -11688,7 +11694,7 @@
       <c r="AI275" s="2"/>
       <c r="AJ275" s="2"/>
     </row>
-    <row r="276" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:36" ht="15.95" customHeight="1">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -11726,7 +11732,7 @@
       <c r="AI276" s="2"/>
       <c r="AJ276" s="2"/>
     </row>
-    <row r="277" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:36" ht="15.95" customHeight="1">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -11764,7 +11770,7 @@
       <c r="AI277" s="2"/>
       <c r="AJ277" s="2"/>
     </row>
-    <row r="278" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:36" ht="15.95" customHeight="1">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -11802,7 +11808,7 @@
       <c r="AI278" s="2"/>
       <c r="AJ278" s="2"/>
     </row>
-    <row r="279" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:36" ht="15.95" customHeight="1">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -11840,7 +11846,7 @@
       <c r="AI279" s="2"/>
       <c r="AJ279" s="2"/>
     </row>
-    <row r="280" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:36" ht="15.95" customHeight="1">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -11878,7 +11884,7 @@
       <c r="AI280" s="2"/>
       <c r="AJ280" s="2"/>
     </row>
-    <row r="281" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:36" ht="15.95" customHeight="1">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -11916,7 +11922,7 @@
       <c r="AI281" s="2"/>
       <c r="AJ281" s="2"/>
     </row>
-    <row r="282" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:36" ht="15.95" customHeight="1">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -11954,7 +11960,7 @@
       <c r="AI282" s="2"/>
       <c r="AJ282" s="2"/>
     </row>
-    <row r="283" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:36" ht="15.95" customHeight="1">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -11992,7 +11998,7 @@
       <c r="AI283" s="2"/>
       <c r="AJ283" s="2"/>
     </row>
-    <row r="284" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:36" ht="15.95" customHeight="1">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -12030,7 +12036,7 @@
       <c r="AI284" s="2"/>
       <c r="AJ284" s="2"/>
     </row>
-    <row r="285" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:36" ht="15.95" customHeight="1">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -12068,7 +12074,7 @@
       <c r="AI285" s="2"/>
       <c r="AJ285" s="2"/>
     </row>
-    <row r="286" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:36" ht="15.95" customHeight="1">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -12106,7 +12112,7 @@
       <c r="AI286" s="2"/>
       <c r="AJ286" s="2"/>
     </row>
-    <row r="287" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:36" ht="15.95" customHeight="1">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -12144,7 +12150,7 @@
       <c r="AI287" s="2"/>
       <c r="AJ287" s="2"/>
     </row>
-    <row r="288" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:36" ht="15.95" customHeight="1">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -12182,7 +12188,7 @@
       <c r="AI288" s="2"/>
       <c r="AJ288" s="2"/>
     </row>
-    <row r="289" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:36" ht="15.95" customHeight="1">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -12220,7 +12226,7 @@
       <c r="AI289" s="2"/>
       <c r="AJ289" s="2"/>
     </row>
-    <row r="290" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:36" ht="15.95" customHeight="1">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -12258,7 +12264,7 @@
       <c r="AI290" s="2"/>
       <c r="AJ290" s="2"/>
     </row>
-    <row r="291" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:36" ht="15.95" customHeight="1">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -12296,7 +12302,7 @@
       <c r="AI291" s="2"/>
       <c r="AJ291" s="2"/>
     </row>
-    <row r="292" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:36" ht="15.95" customHeight="1">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -12334,7 +12340,7 @@
       <c r="AI292" s="2"/>
       <c r="AJ292" s="2"/>
     </row>
-    <row r="293" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:36" ht="15.95" customHeight="1">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -12372,7 +12378,7 @@
       <c r="AI293" s="2"/>
       <c r="AJ293" s="2"/>
     </row>
-    <row r="294" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:36" ht="15.95" customHeight="1">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -12410,7 +12416,7 @@
       <c r="AI294" s="2"/>
       <c r="AJ294" s="2"/>
     </row>
-    <row r="295" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:36" ht="15.95" customHeight="1">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -12448,7 +12454,7 @@
       <c r="AI295" s="2"/>
       <c r="AJ295" s="2"/>
     </row>
-    <row r="296" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:36" ht="15.95" customHeight="1">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -12486,7 +12492,7 @@
       <c r="AI296" s="2"/>
       <c r="AJ296" s="2"/>
     </row>
-    <row r="297" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:36" ht="15.95" customHeight="1">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -12524,7 +12530,7 @@
       <c r="AI297" s="2"/>
       <c r="AJ297" s="2"/>
     </row>
-    <row r="298" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:36" ht="15.95" customHeight="1">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -12562,7 +12568,7 @@
       <c r="AI298" s="2"/>
       <c r="AJ298" s="2"/>
     </row>
-    <row r="299" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:36" ht="15.95" customHeight="1">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -12600,7 +12606,7 @@
       <c r="AI299" s="2"/>
       <c r="AJ299" s="2"/>
     </row>
-    <row r="300" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:36" ht="15.95" customHeight="1">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -12638,7 +12644,7 @@
       <c r="AI300" s="2"/>
       <c r="AJ300" s="2"/>
     </row>
-    <row r="301" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:36" ht="15.95" customHeight="1">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -12676,7 +12682,7 @@
       <c r="AI301" s="2"/>
       <c r="AJ301" s="2"/>
     </row>
-    <row r="302" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:36" ht="15.95" customHeight="1">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -12714,7 +12720,7 @@
       <c r="AI302" s="2"/>
       <c r="AJ302" s="2"/>
     </row>
-    <row r="303" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:36" ht="15.95" customHeight="1">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -12752,7 +12758,7 @@
       <c r="AI303" s="2"/>
       <c r="AJ303" s="2"/>
     </row>
-    <row r="304" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:36" ht="15.95" customHeight="1">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -12790,7 +12796,7 @@
       <c r="AI304" s="2"/>
       <c r="AJ304" s="2"/>
     </row>
-    <row r="305" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:36" ht="15.95" customHeight="1">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -12828,7 +12834,7 @@
       <c r="AI305" s="2"/>
       <c r="AJ305" s="2"/>
     </row>
-    <row r="306" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:36" ht="15.95" customHeight="1">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -12866,7 +12872,7 @@
       <c r="AI306" s="2"/>
       <c r="AJ306" s="2"/>
     </row>
-    <row r="307" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:36" ht="15.95" customHeight="1">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -12904,7 +12910,7 @@
       <c r="AI307" s="2"/>
       <c r="AJ307" s="2"/>
     </row>
-    <row r="308" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:36" ht="15.95" customHeight="1">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -12942,7 +12948,7 @@
       <c r="AI308" s="2"/>
       <c r="AJ308" s="2"/>
     </row>
-    <row r="309" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:36" ht="15.95" customHeight="1">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -12980,7 +12986,7 @@
       <c r="AI309" s="2"/>
       <c r="AJ309" s="2"/>
     </row>
-    <row r="310" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:36" ht="15.95" customHeight="1">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -13018,7 +13024,7 @@
       <c r="AI310" s="2"/>
       <c r="AJ310" s="2"/>
     </row>
-    <row r="311" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:36" ht="15.95" customHeight="1">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -13056,7 +13062,7 @@
       <c r="AI311" s="2"/>
       <c r="AJ311" s="2"/>
     </row>
-    <row r="312" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:36" ht="15.95" customHeight="1">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -13094,7 +13100,7 @@
       <c r="AI312" s="2"/>
       <c r="AJ312" s="2"/>
     </row>
-    <row r="313" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:36" ht="15.95" customHeight="1">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -13132,7 +13138,7 @@
       <c r="AI313" s="2"/>
       <c r="AJ313" s="2"/>
     </row>
-    <row r="314" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:36" ht="15.95" customHeight="1">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -13170,7 +13176,7 @@
       <c r="AI314" s="2"/>
       <c r="AJ314" s="2"/>
     </row>
-    <row r="315" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:36" ht="15.95" customHeight="1">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -13208,7 +13214,7 @@
       <c r="AI315" s="2"/>
       <c r="AJ315" s="2"/>
     </row>
-    <row r="316" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:36" ht="15.95" customHeight="1">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -13246,7 +13252,7 @@
       <c r="AI316" s="2"/>
       <c r="AJ316" s="2"/>
     </row>
-    <row r="317" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:36" ht="15.95" customHeight="1">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -13284,7 +13290,7 @@
       <c r="AI317" s="2"/>
       <c r="AJ317" s="2"/>
     </row>
-    <row r="318" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:36" ht="15.95" customHeight="1">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -13322,7 +13328,7 @@
       <c r="AI318" s="2"/>
       <c r="AJ318" s="2"/>
     </row>
-    <row r="319" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:36" ht="15.95" customHeight="1">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -13360,7 +13366,7 @@
       <c r="AI319" s="2"/>
       <c r="AJ319" s="2"/>
     </row>
-    <row r="320" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:36" ht="15.95" customHeight="1">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -13398,7 +13404,7 @@
       <c r="AI320" s="2"/>
       <c r="AJ320" s="2"/>
     </row>
-    <row r="321" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:36" ht="15.95" customHeight="1">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -13436,7 +13442,7 @@
       <c r="AI321" s="2"/>
       <c r="AJ321" s="2"/>
     </row>
-    <row r="322" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:36" ht="15.95" customHeight="1">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -13474,7 +13480,7 @@
       <c r="AI322" s="2"/>
       <c r="AJ322" s="2"/>
     </row>
-    <row r="323" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:36" ht="15.95" customHeight="1">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -13512,7 +13518,7 @@
       <c r="AI323" s="2"/>
       <c r="AJ323" s="2"/>
     </row>
-    <row r="324" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:36" ht="15.95" customHeight="1">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -13550,7 +13556,7 @@
       <c r="AI324" s="2"/>
       <c r="AJ324" s="2"/>
     </row>
-    <row r="325" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:36" ht="15.95" customHeight="1">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -13588,7 +13594,7 @@
       <c r="AI325" s="2"/>
       <c r="AJ325" s="2"/>
     </row>
-    <row r="326" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:36" ht="15.95" customHeight="1">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -13626,7 +13632,7 @@
       <c r="AI326" s="2"/>
       <c r="AJ326" s="2"/>
     </row>
-    <row r="327" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:36" ht="15.95" customHeight="1">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -13664,7 +13670,7 @@
       <c r="AI327" s="2"/>
       <c r="AJ327" s="2"/>
     </row>
-    <row r="328" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:36" ht="15.95" customHeight="1">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -13702,7 +13708,7 @@
       <c r="AI328" s="2"/>
       <c r="AJ328" s="2"/>
     </row>
-    <row r="329" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:36" ht="15.95" customHeight="1">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -13740,7 +13746,7 @@
       <c r="AI329" s="2"/>
       <c r="AJ329" s="2"/>
     </row>
-    <row r="330" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:36" ht="15.95" customHeight="1">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
@@ -13778,7 +13784,7 @@
       <c r="AI330" s="2"/>
       <c r="AJ330" s="2"/>
     </row>
-    <row r="331" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:36" ht="15.95" customHeight="1">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -13816,7 +13822,7 @@
       <c r="AI331" s="2"/>
       <c r="AJ331" s="2"/>
     </row>
-    <row r="332" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:36" ht="15.95" customHeight="1">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -13854,7 +13860,7 @@
       <c r="AI332" s="2"/>
       <c r="AJ332" s="2"/>
     </row>
-    <row r="333" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:36" ht="15.95" customHeight="1">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -13892,7 +13898,7 @@
       <c r="AI333" s="2"/>
       <c r="AJ333" s="2"/>
     </row>
-    <row r="334" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:36" ht="15.95" customHeight="1">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -13930,7 +13936,7 @@
       <c r="AI334" s="2"/>
       <c r="AJ334" s="2"/>
     </row>
-    <row r="335" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:36" ht="15.95" customHeight="1">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
@@ -13968,7 +13974,7 @@
       <c r="AI335" s="2"/>
       <c r="AJ335" s="2"/>
     </row>
-    <row r="336" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:36" ht="15.95" customHeight="1">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -14006,7 +14012,7 @@
       <c r="AI336" s="2"/>
       <c r="AJ336" s="2"/>
     </row>
-    <row r="337" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:36" ht="15.95" customHeight="1">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
@@ -14044,7 +14050,7 @@
       <c r="AI337" s="2"/>
       <c r="AJ337" s="2"/>
     </row>
-    <row r="338" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:36" ht="15.95" customHeight="1">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -14082,7 +14088,7 @@
       <c r="AI338" s="2"/>
       <c r="AJ338" s="2"/>
     </row>
-    <row r="339" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:36" ht="15.95" customHeight="1">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
@@ -14120,7 +14126,7 @@
       <c r="AI339" s="2"/>
       <c r="AJ339" s="2"/>
     </row>
-    <row r="340" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:36" ht="15.95" customHeight="1">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -14158,7 +14164,7 @@
       <c r="AI340" s="2"/>
       <c r="AJ340" s="2"/>
     </row>
-    <row r="341" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:36" ht="15.95" customHeight="1">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
@@ -14196,7 +14202,7 @@
       <c r="AI341" s="2"/>
       <c r="AJ341" s="2"/>
     </row>
-    <row r="342" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:36" ht="15.95" customHeight="1">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -14234,7 +14240,7 @@
       <c r="AI342" s="2"/>
       <c r="AJ342" s="2"/>
     </row>
-    <row r="343" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:36" ht="15.95" customHeight="1">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
@@ -14272,7 +14278,7 @@
       <c r="AI343" s="2"/>
       <c r="AJ343" s="2"/>
     </row>
-    <row r="344" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:36" ht="15.95" customHeight="1">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -14310,7 +14316,7 @@
       <c r="AI344" s="2"/>
       <c r="AJ344" s="2"/>
     </row>
-    <row r="345" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:36" ht="15.95" customHeight="1">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
@@ -14348,7 +14354,7 @@
       <c r="AI345" s="2"/>
       <c r="AJ345" s="2"/>
     </row>
-    <row r="346" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:36" ht="15.95" customHeight="1">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -14386,7 +14392,7 @@
       <c r="AI346" s="2"/>
       <c r="AJ346" s="2"/>
     </row>
-    <row r="347" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:36" ht="15.95" customHeight="1">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -14424,7 +14430,7 @@
       <c r="AI347" s="2"/>
       <c r="AJ347" s="2"/>
     </row>
-    <row r="348" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:36" ht="15.95" customHeight="1">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -14462,7 +14468,7 @@
       <c r="AI348" s="2"/>
       <c r="AJ348" s="2"/>
     </row>
-    <row r="349" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:36" ht="15.95" customHeight="1">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -14500,7 +14506,7 @@
       <c r="AI349" s="2"/>
       <c r="AJ349" s="2"/>
     </row>
-    <row r="350" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:36" ht="15.95" customHeight="1">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
@@ -14538,7 +14544,7 @@
       <c r="AI350" s="2"/>
       <c r="AJ350" s="2"/>
     </row>
-    <row r="351" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:36" ht="15.95" customHeight="1">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -14576,7 +14582,7 @@
       <c r="AI351" s="2"/>
       <c r="AJ351" s="2"/>
     </row>
-    <row r="352" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:36" ht="15.95" customHeight="1">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -14614,7 +14620,7 @@
       <c r="AI352" s="2"/>
       <c r="AJ352" s="2"/>
     </row>
-    <row r="353" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:36" ht="15.95" customHeight="1">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
@@ -14652,7 +14658,7 @@
       <c r="AI353" s="2"/>
       <c r="AJ353" s="2"/>
     </row>
-    <row r="354" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:36" ht="15.95" customHeight="1">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
@@ -14690,7 +14696,7 @@
       <c r="AI354" s="2"/>
       <c r="AJ354" s="2"/>
     </row>
-    <row r="355" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:36" ht="15.95" customHeight="1">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -14728,7 +14734,7 @@
       <c r="AI355" s="2"/>
       <c r="AJ355" s="2"/>
     </row>
-    <row r="356" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:36" ht="15.95" customHeight="1">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
@@ -14766,7 +14772,7 @@
       <c r="AI356" s="2"/>
       <c r="AJ356" s="2"/>
     </row>
-    <row r="357" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:36" ht="15.95" customHeight="1">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -14804,7 +14810,7 @@
       <c r="AI357" s="2"/>
       <c r="AJ357" s="2"/>
     </row>
-    <row r="358" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:36" ht="15.95" customHeight="1">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -14842,7 +14848,7 @@
       <c r="AI358" s="2"/>
       <c r="AJ358" s="2"/>
     </row>
-    <row r="359" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:36" ht="15.95" customHeight="1">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -14880,7 +14886,7 @@
       <c r="AI359" s="2"/>
       <c r="AJ359" s="2"/>
     </row>
-    <row r="360" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:36" ht="15.95" customHeight="1">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
@@ -14918,7 +14924,7 @@
       <c r="AI360" s="2"/>
       <c r="AJ360" s="2"/>
     </row>
-    <row r="361" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:36" ht="15.95" customHeight="1">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
@@ -14956,7 +14962,7 @@
       <c r="AI361" s="2"/>
       <c r="AJ361" s="2"/>
     </row>
-    <row r="362" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:36" ht="15.95" customHeight="1">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -14994,7 +15000,7 @@
       <c r="AI362" s="2"/>
       <c r="AJ362" s="2"/>
     </row>
-    <row r="363" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:36" ht="15.95" customHeight="1">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -15032,7 +15038,7 @@
       <c r="AI363" s="2"/>
       <c r="AJ363" s="2"/>
     </row>
-    <row r="364" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:36" ht="15.95" customHeight="1">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
@@ -15070,7 +15076,7 @@
       <c r="AI364" s="2"/>
       <c r="AJ364" s="2"/>
     </row>
-    <row r="365" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:36" ht="15.95" customHeight="1">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -15108,7 +15114,7 @@
       <c r="AI365" s="2"/>
       <c r="AJ365" s="2"/>
     </row>
-    <row r="366" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:36" ht="15.95" customHeight="1">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -15146,7 +15152,7 @@
       <c r="AI366" s="2"/>
       <c r="AJ366" s="2"/>
     </row>
-    <row r="367" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:36" ht="15.95" customHeight="1">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
@@ -15184,7 +15190,7 @@
       <c r="AI367" s="2"/>
       <c r="AJ367" s="2"/>
     </row>
-    <row r="368" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:36" ht="15.95" customHeight="1">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -15222,7 +15228,7 @@
       <c r="AI368" s="2"/>
       <c r="AJ368" s="2"/>
     </row>
-    <row r="369" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:36" ht="15.95" customHeight="1">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
@@ -15260,7 +15266,7 @@
       <c r="AI369" s="2"/>
       <c r="AJ369" s="2"/>
     </row>
-    <row r="370" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:36" ht="15.95" customHeight="1">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -15298,7 +15304,7 @@
       <c r="AI370" s="2"/>
       <c r="AJ370" s="2"/>
     </row>
-    <row r="371" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:36" ht="15.95" customHeight="1">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -15336,7 +15342,7 @@
       <c r="AI371" s="2"/>
       <c r="AJ371" s="2"/>
     </row>
-    <row r="372" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:36" ht="15.95" customHeight="1">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -15374,7 +15380,7 @@
       <c r="AI372" s="2"/>
       <c r="AJ372" s="2"/>
     </row>
-    <row r="373" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:36" ht="15.95" customHeight="1">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
@@ -15412,7 +15418,7 @@
       <c r="AI373" s="2"/>
       <c r="AJ373" s="2"/>
     </row>
-    <row r="374" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:36" ht="15.95" customHeight="1">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -15450,7 +15456,7 @@
       <c r="AI374" s="2"/>
       <c r="AJ374" s="2"/>
     </row>
-    <row r="375" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:36" ht="15.95" customHeight="1">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -15488,7 +15494,7 @@
       <c r="AI375" s="2"/>
       <c r="AJ375" s="2"/>
     </row>
-    <row r="376" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:36" ht="15.95" customHeight="1">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -15526,7 +15532,7 @@
       <c r="AI376" s="2"/>
       <c r="AJ376" s="2"/>
     </row>
-    <row r="377" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:36" ht="15.95" customHeight="1">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
@@ -15564,7 +15570,7 @@
       <c r="AI377" s="2"/>
       <c r="AJ377" s="2"/>
     </row>
-    <row r="378" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:36" ht="15.95" customHeight="1">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -15602,7 +15608,7 @@
       <c r="AI378" s="2"/>
       <c r="AJ378" s="2"/>
     </row>
-    <row r="379" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:36" ht="15.95" customHeight="1">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -15640,7 +15646,7 @@
       <c r="AI379" s="2"/>
       <c r="AJ379" s="2"/>
     </row>
-    <row r="380" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:36" ht="15.95" customHeight="1">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
@@ -15678,7 +15684,7 @@
       <c r="AI380" s="2"/>
       <c r="AJ380" s="2"/>
     </row>
-    <row r="381" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:36" ht="15.95" customHeight="1">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
@@ -15716,7 +15722,7 @@
       <c r="AI381" s="2"/>
       <c r="AJ381" s="2"/>
     </row>
-    <row r="382" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:36" ht="15.95" customHeight="1">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -15754,7 +15760,7 @@
       <c r="AI382" s="2"/>
       <c r="AJ382" s="2"/>
     </row>
-    <row r="383" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:36" ht="15.95" customHeight="1">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
@@ -15792,7 +15798,7 @@
       <c r="AI383" s="2"/>
       <c r="AJ383" s="2"/>
     </row>
-    <row r="384" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:36" ht="15.95" customHeight="1">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -15830,7 +15836,7 @@
       <c r="AI384" s="2"/>
       <c r="AJ384" s="2"/>
     </row>
-    <row r="385" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:36" ht="15.95" customHeight="1">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -15868,7 +15874,7 @@
       <c r="AI385" s="2"/>
       <c r="AJ385" s="2"/>
     </row>
-    <row r="386" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:36" ht="15.95" customHeight="1">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -15906,7 +15912,7 @@
       <c r="AI386" s="2"/>
       <c r="AJ386" s="2"/>
     </row>
-    <row r="387" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:36" ht="15.95" customHeight="1">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -15944,7 +15950,7 @@
       <c r="AI387" s="2"/>
       <c r="AJ387" s="2"/>
     </row>
-    <row r="388" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:36" ht="15.95" customHeight="1">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
@@ -15982,7 +15988,7 @@
       <c r="AI388" s="2"/>
       <c r="AJ388" s="2"/>
     </row>
-    <row r="389" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:36" ht="15.95" customHeight="1">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -16020,7 +16026,7 @@
       <c r="AI389" s="2"/>
       <c r="AJ389" s="2"/>
     </row>
-    <row r="390" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:36" ht="15.95" customHeight="1">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -16058,7 +16064,7 @@
       <c r="AI390" s="2"/>
       <c r="AJ390" s="2"/>
     </row>
-    <row r="391" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:36" ht="15.95" customHeight="1">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -16096,7 +16102,7 @@
       <c r="AI391" s="2"/>
       <c r="AJ391" s="2"/>
     </row>
-    <row r="392" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:36" ht="15.95" customHeight="1">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -16134,7 +16140,7 @@
       <c r="AI392" s="2"/>
       <c r="AJ392" s="2"/>
     </row>
-    <row r="393" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:36" ht="15.95" customHeight="1">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -16172,7 +16178,7 @@
       <c r="AI393" s="2"/>
       <c r="AJ393" s="2"/>
     </row>
-    <row r="394" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:36" ht="15.95" customHeight="1">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
@@ -16210,7 +16216,7 @@
       <c r="AI394" s="2"/>
       <c r="AJ394" s="2"/>
     </row>
-    <row r="395" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:36" ht="15.95" customHeight="1">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -16248,7 +16254,7 @@
       <c r="AI395" s="2"/>
       <c r="AJ395" s="2"/>
     </row>
-    <row r="396" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:36" ht="15.95" customHeight="1">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -16286,7 +16292,7 @@
       <c r="AI396" s="2"/>
       <c r="AJ396" s="2"/>
     </row>
-    <row r="397" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:36" ht="15.95" customHeight="1">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
@@ -16324,7 +16330,7 @@
       <c r="AI397" s="2"/>
       <c r="AJ397" s="2"/>
     </row>
-    <row r="398" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:36" ht="15.95" customHeight="1">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
@@ -16362,7 +16368,7 @@
       <c r="AI398" s="2"/>
       <c r="AJ398" s="2"/>
     </row>
-    <row r="399" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:36" ht="15.95" customHeight="1">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -16400,7 +16406,7 @@
       <c r="AI399" s="2"/>
       <c r="AJ399" s="2"/>
     </row>
-    <row r="400" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:36" ht="15.95" customHeight="1">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
@@ -16438,7 +16444,7 @@
       <c r="AI400" s="2"/>
       <c r="AJ400" s="2"/>
     </row>
-    <row r="401" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:36" ht="15.95" customHeight="1">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
@@ -16476,7 +16482,7 @@
       <c r="AI401" s="2"/>
       <c r="AJ401" s="2"/>
     </row>
-    <row r="402" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:36" ht="15.95" customHeight="1">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -16514,7 +16520,7 @@
       <c r="AI402" s="2"/>
       <c r="AJ402" s="2"/>
     </row>
-    <row r="403" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:36" ht="15.95" customHeight="1">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -16552,7 +16558,7 @@
       <c r="AI403" s="2"/>
       <c r="AJ403" s="2"/>
     </row>
-    <row r="404" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:36" ht="15.95" customHeight="1">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -16590,7 +16596,7 @@
       <c r="AI404" s="2"/>
       <c r="AJ404" s="2"/>
     </row>
-    <row r="405" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:36" ht="15.95" customHeight="1">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
@@ -16628,7 +16634,7 @@
       <c r="AI405" s="2"/>
       <c r="AJ405" s="2"/>
     </row>
-    <row r="406" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:36" ht="15.95" customHeight="1">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
@@ -16666,7 +16672,7 @@
       <c r="AI406" s="2"/>
       <c r="AJ406" s="2"/>
     </row>
-    <row r="407" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:36" ht="15.95" customHeight="1">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
@@ -16704,7 +16710,7 @@
       <c r="AI407" s="2"/>
       <c r="AJ407" s="2"/>
     </row>
-    <row r="408" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:36" ht="15.95" customHeight="1">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
@@ -16742,7 +16748,7 @@
       <c r="AI408" s="2"/>
       <c r="AJ408" s="2"/>
     </row>
-    <row r="409" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:36" ht="15.95" customHeight="1">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
@@ -16780,7 +16786,7 @@
       <c r="AI409" s="2"/>
       <c r="AJ409" s="2"/>
     </row>
-    <row r="410" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:36" ht="15.95" customHeight="1">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
@@ -16818,7 +16824,7 @@
       <c r="AI410" s="2"/>
       <c r="AJ410" s="2"/>
     </row>
-    <row r="411" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:36" ht="15.95" customHeight="1">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
@@ -16856,7 +16862,7 @@
       <c r="AI411" s="2"/>
       <c r="AJ411" s="2"/>
     </row>
-    <row r="412" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:36" ht="15.95" customHeight="1">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
@@ -16894,7 +16900,7 @@
       <c r="AI412" s="2"/>
       <c r="AJ412" s="2"/>
     </row>
-    <row r="413" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:36" ht="15.95" customHeight="1">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
@@ -16932,7 +16938,7 @@
       <c r="AI413" s="2"/>
       <c r="AJ413" s="2"/>
     </row>
-    <row r="414" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:36" ht="15.95" customHeight="1">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
@@ -16970,7 +16976,7 @@
       <c r="AI414" s="2"/>
       <c r="AJ414" s="2"/>
     </row>
-    <row r="415" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:36" ht="15.95" customHeight="1">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
@@ -17008,7 +17014,7 @@
       <c r="AI415" s="2"/>
       <c r="AJ415" s="2"/>
     </row>
-    <row r="416" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:36" ht="15.95" customHeight="1">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
@@ -17046,7 +17052,7 @@
       <c r="AI416" s="2"/>
       <c r="AJ416" s="2"/>
     </row>
-    <row r="417" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:36" ht="15.95" customHeight="1">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
@@ -17084,7 +17090,7 @@
       <c r="AI417" s="2"/>
       <c r="AJ417" s="2"/>
     </row>
-    <row r="418" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:36" ht="15.95" customHeight="1">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
@@ -17122,7 +17128,7 @@
       <c r="AI418" s="2"/>
       <c r="AJ418" s="2"/>
     </row>
-    <row r="419" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:36" ht="15.95" customHeight="1">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
@@ -17160,7 +17166,7 @@
       <c r="AI419" s="2"/>
       <c r="AJ419" s="2"/>
     </row>
-    <row r="420" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:36" ht="15.95" customHeight="1">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
@@ -17198,7 +17204,7 @@
       <c r="AI420" s="2"/>
       <c r="AJ420" s="2"/>
     </row>
-    <row r="421" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:36" ht="15.95" customHeight="1">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
@@ -17236,7 +17242,7 @@
       <c r="AI421" s="2"/>
       <c r="AJ421" s="2"/>
     </row>
-    <row r="422" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:36" ht="15.95" customHeight="1">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
@@ -17274,7 +17280,7 @@
       <c r="AI422" s="2"/>
       <c r="AJ422" s="2"/>
     </row>
-    <row r="423" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:36" ht="15.95" customHeight="1">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
@@ -17312,7 +17318,7 @@
       <c r="AI423" s="2"/>
       <c r="AJ423" s="2"/>
     </row>
-    <row r="424" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:36" ht="15.95" customHeight="1">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
@@ -17350,7 +17356,7 @@
       <c r="AI424" s="2"/>
       <c r="AJ424" s="2"/>
     </row>
-    <row r="425" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:36" ht="15.95" customHeight="1">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
@@ -17388,7 +17394,7 @@
       <c r="AI425" s="2"/>
       <c r="AJ425" s="2"/>
     </row>
-    <row r="426" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:36" ht="15.95" customHeight="1">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
@@ -17426,7 +17432,7 @@
       <c r="AI426" s="2"/>
       <c r="AJ426" s="2"/>
     </row>
-    <row r="427" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:36" ht="15.95" customHeight="1">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
@@ -17464,7 +17470,7 @@
       <c r="AI427" s="2"/>
       <c r="AJ427" s="2"/>
     </row>
-    <row r="428" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:36" ht="15.95" customHeight="1">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
@@ -17502,7 +17508,7 @@
       <c r="AI428" s="2"/>
       <c r="AJ428" s="2"/>
     </row>
-    <row r="429" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:36" ht="15.95" customHeight="1">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
@@ -17540,7 +17546,7 @@
       <c r="AI429" s="2"/>
       <c r="AJ429" s="2"/>
     </row>
-    <row r="430" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:36" ht="15.95" customHeight="1">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -17578,7 +17584,7 @@
       <c r="AI430" s="2"/>
       <c r="AJ430" s="2"/>
     </row>
-    <row r="431" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:36" ht="15.95" customHeight="1">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
@@ -17616,7 +17622,7 @@
       <c r="AI431" s="2"/>
       <c r="AJ431" s="2"/>
     </row>
-    <row r="432" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:36" ht="15.95" customHeight="1">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
@@ -17654,7 +17660,7 @@
       <c r="AI432" s="2"/>
       <c r="AJ432" s="2"/>
     </row>
-    <row r="433" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:36" ht="15.95" customHeight="1">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
@@ -17692,7 +17698,7 @@
       <c r="AI433" s="2"/>
       <c r="AJ433" s="2"/>
     </row>
-    <row r="434" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:36" ht="15.95" customHeight="1">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
@@ -17730,7 +17736,7 @@
       <c r="AI434" s="2"/>
       <c r="AJ434" s="2"/>
     </row>
-    <row r="435" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:36" ht="15.95" customHeight="1">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -17768,7 +17774,7 @@
       <c r="AI435" s="2"/>
       <c r="AJ435" s="2"/>
     </row>
-    <row r="436" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:36" ht="15.95" customHeight="1">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
@@ -17806,7 +17812,7 @@
       <c r="AI436" s="2"/>
       <c r="AJ436" s="2"/>
     </row>
-    <row r="437" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:36" ht="15.95" customHeight="1">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
@@ -17844,7 +17850,7 @@
       <c r="AI437" s="2"/>
       <c r="AJ437" s="2"/>
     </row>
-    <row r="438" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:36" ht="15.95" customHeight="1">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
@@ -17882,7 +17888,7 @@
       <c r="AI438" s="2"/>
       <c r="AJ438" s="2"/>
     </row>
-    <row r="439" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:36" ht="15.95" customHeight="1">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
@@ -17920,7 +17926,7 @@
       <c r="AI439" s="2"/>
       <c r="AJ439" s="2"/>
     </row>
-    <row r="440" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:36" ht="15.95" customHeight="1">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
@@ -17958,7 +17964,7 @@
       <c r="AI440" s="2"/>
       <c r="AJ440" s="2"/>
     </row>
-    <row r="441" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:36" ht="15.95" customHeight="1">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -17996,7 +18002,7 @@
       <c r="AI441" s="2"/>
       <c r="AJ441" s="2"/>
     </row>
-    <row r="442" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:36" ht="15.95" customHeight="1">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
@@ -18034,7 +18040,7 @@
       <c r="AI442" s="2"/>
       <c r="AJ442" s="2"/>
     </row>
-    <row r="443" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:36" ht="15.95" customHeight="1">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
@@ -18072,7 +18078,7 @@
       <c r="AI443" s="2"/>
       <c r="AJ443" s="2"/>
     </row>
-    <row r="444" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:36" ht="15.95" customHeight="1">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
@@ -18110,7 +18116,7 @@
       <c r="AI444" s="2"/>
       <c r="AJ444" s="2"/>
     </row>
-    <row r="445" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:36" ht="15.95" customHeight="1">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
@@ -18148,7 +18154,7 @@
       <c r="AI445" s="2"/>
       <c r="AJ445" s="2"/>
     </row>
-    <row r="446" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:36" ht="15.95" customHeight="1">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
@@ -18186,7 +18192,7 @@
       <c r="AI446" s="2"/>
       <c r="AJ446" s="2"/>
     </row>
-    <row r="447" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:36" ht="15.95" customHeight="1">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
@@ -18224,7 +18230,7 @@
       <c r="AI447" s="2"/>
       <c r="AJ447" s="2"/>
     </row>
-    <row r="448" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:36" ht="15.95" customHeight="1">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
@@ -18262,7 +18268,7 @@
       <c r="AI448" s="2"/>
       <c r="AJ448" s="2"/>
     </row>
-    <row r="449" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:36" ht="15.95" customHeight="1">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
@@ -18300,7 +18306,7 @@
       <c r="AI449" s="2"/>
       <c r="AJ449" s="2"/>
     </row>
-    <row r="450" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:36" ht="15.95" customHeight="1">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
@@ -18338,7 +18344,7 @@
       <c r="AI450" s="2"/>
       <c r="AJ450" s="2"/>
     </row>
-    <row r="451" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:36" ht="15.95" customHeight="1">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
@@ -18376,7 +18382,7 @@
       <c r="AI451" s="2"/>
       <c r="AJ451" s="2"/>
     </row>
-    <row r="452" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:36" ht="15.95" customHeight="1">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
@@ -18414,7 +18420,7 @@
       <c r="AI452" s="2"/>
       <c r="AJ452" s="2"/>
     </row>
-    <row r="453" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:36" ht="15.95" customHeight="1">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
@@ -18452,7 +18458,7 @@
       <c r="AI453" s="2"/>
       <c r="AJ453" s="2"/>
     </row>
-    <row r="454" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:36" ht="15.95" customHeight="1">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
@@ -18490,7 +18496,7 @@
       <c r="AI454" s="2"/>
       <c r="AJ454" s="2"/>
     </row>
-    <row r="455" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:36" ht="15.95" customHeight="1">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
@@ -18528,7 +18534,7 @@
       <c r="AI455" s="2"/>
       <c r="AJ455" s="2"/>
     </row>
-    <row r="456" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:36" ht="15.95" customHeight="1">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
@@ -18566,7 +18572,7 @@
       <c r="AI456" s="2"/>
       <c r="AJ456" s="2"/>
     </row>
-    <row r="457" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:36" ht="15.95" customHeight="1">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
@@ -18604,7 +18610,7 @@
       <c r="AI457" s="2"/>
       <c r="AJ457" s="2"/>
     </row>
-    <row r="458" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:36" ht="15.95" customHeight="1">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
@@ -18642,7 +18648,7 @@
       <c r="AI458" s="2"/>
       <c r="AJ458" s="2"/>
     </row>
-    <row r="459" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:36" ht="15.95" customHeight="1">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
@@ -18680,7 +18686,7 @@
       <c r="AI459" s="2"/>
       <c r="AJ459" s="2"/>
     </row>
-    <row r="460" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:36" ht="15.95" customHeight="1">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
@@ -18718,7 +18724,7 @@
       <c r="AI460" s="2"/>
       <c r="AJ460" s="2"/>
     </row>
-    <row r="461" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:36" ht="15.95" customHeight="1">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
@@ -18756,7 +18762,7 @@
       <c r="AI461" s="2"/>
       <c r="AJ461" s="2"/>
     </row>
-    <row r="462" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:36" ht="15.95" customHeight="1">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
@@ -18794,7 +18800,7 @@
       <c r="AI462" s="2"/>
       <c r="AJ462" s="2"/>
     </row>
-    <row r="463" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:36" ht="15.95" customHeight="1">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
@@ -18832,7 +18838,7 @@
       <c r="AI463" s="2"/>
       <c r="AJ463" s="2"/>
     </row>
-    <row r="464" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:36" ht="15.95" customHeight="1">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
@@ -18870,7 +18876,7 @@
       <c r="AI464" s="2"/>
       <c r="AJ464" s="2"/>
     </row>
-    <row r="465" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:36" ht="15.95" customHeight="1">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
@@ -18908,7 +18914,7 @@
       <c r="AI465" s="2"/>
       <c r="AJ465" s="2"/>
     </row>
-    <row r="466" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:36" ht="15.95" customHeight="1">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
@@ -18946,7 +18952,7 @@
       <c r="AI466" s="2"/>
       <c r="AJ466" s="2"/>
     </row>
-    <row r="467" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:36" ht="15.95" customHeight="1">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
@@ -18984,7 +18990,7 @@
       <c r="AI467" s="2"/>
       <c r="AJ467" s="2"/>
     </row>
-    <row r="468" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:36" ht="15.95" customHeight="1">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
@@ -19022,7 +19028,7 @@
       <c r="AI468" s="2"/>
       <c r="AJ468" s="2"/>
     </row>
-    <row r="469" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:36" ht="15.95" customHeight="1">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
@@ -19060,7 +19066,7 @@
       <c r="AI469" s="2"/>
       <c r="AJ469" s="2"/>
     </row>
-    <row r="470" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:36" ht="15.95" customHeight="1">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
@@ -19098,7 +19104,7 @@
       <c r="AI470" s="2"/>
       <c r="AJ470" s="2"/>
     </row>
-    <row r="471" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:36" ht="15.95" customHeight="1">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
@@ -19136,7 +19142,7 @@
       <c r="AI471" s="2"/>
       <c r="AJ471" s="2"/>
     </row>
-    <row r="472" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:36" ht="15.95" customHeight="1">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
@@ -19174,7 +19180,7 @@
       <c r="AI472" s="2"/>
       <c r="AJ472" s="2"/>
     </row>
-    <row r="473" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:36" ht="15.95" customHeight="1">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
@@ -19212,7 +19218,7 @@
       <c r="AI473" s="2"/>
       <c r="AJ473" s="2"/>
     </row>
-    <row r="474" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:36" ht="15.95" customHeight="1">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
@@ -19250,7 +19256,7 @@
       <c r="AI474" s="2"/>
       <c r="AJ474" s="2"/>
     </row>
-    <row r="475" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:36" ht="15.95" customHeight="1">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
@@ -19288,7 +19294,7 @@
       <c r="AI475" s="2"/>
       <c r="AJ475" s="2"/>
     </row>
-    <row r="476" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:36" ht="15.95" customHeight="1">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
@@ -19326,7 +19332,7 @@
       <c r="AI476" s="2"/>
       <c r="AJ476" s="2"/>
     </row>
-    <row r="477" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:36" ht="15.95" customHeight="1">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
@@ -19364,7 +19370,7 @@
       <c r="AI477" s="2"/>
       <c r="AJ477" s="2"/>
     </row>
-    <row r="478" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:36" ht="15.95" customHeight="1">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
@@ -19402,7 +19408,7 @@
       <c r="AI478" s="2"/>
       <c r="AJ478" s="2"/>
     </row>
-    <row r="479" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:36" ht="15.95" customHeight="1">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
@@ -19440,7 +19446,7 @@
       <c r="AI479" s="2"/>
       <c r="AJ479" s="2"/>
     </row>
-    <row r="480" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:36" ht="15.95" customHeight="1">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -19478,7 +19484,7 @@
       <c r="AI480" s="2"/>
       <c r="AJ480" s="2"/>
     </row>
-    <row r="481" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:36" ht="15.95" customHeight="1">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -19516,7 +19522,7 @@
       <c r="AI481" s="2"/>
       <c r="AJ481" s="2"/>
     </row>
-    <row r="482" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:36" ht="15.95" customHeight="1">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
@@ -19554,7 +19560,7 @@
       <c r="AI482" s="2"/>
       <c r="AJ482" s="2"/>
     </row>
-    <row r="483" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:36" ht="15.95" customHeight="1">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
@@ -19592,7 +19598,7 @@
       <c r="AI483" s="2"/>
       <c r="AJ483" s="2"/>
     </row>
-    <row r="484" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:36" ht="15.95" customHeight="1">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
@@ -19630,7 +19636,7 @@
       <c r="AI484" s="2"/>
       <c r="AJ484" s="2"/>
     </row>
-    <row r="485" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:36" ht="15.95" customHeight="1">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
@@ -19668,7 +19674,7 @@
       <c r="AI485" s="2"/>
       <c r="AJ485" s="2"/>
     </row>
-    <row r="486" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:36" ht="15.95" customHeight="1">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
@@ -19706,7 +19712,7 @@
       <c r="AI486" s="2"/>
       <c r="AJ486" s="2"/>
     </row>
-    <row r="487" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:36" ht="15.95" customHeight="1">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
@@ -19744,7 +19750,7 @@
       <c r="AI487" s="2"/>
       <c r="AJ487" s="2"/>
     </row>
-    <row r="488" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:36" ht="15.95" customHeight="1">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
@@ -19782,7 +19788,7 @@
       <c r="AI488" s="2"/>
       <c r="AJ488" s="2"/>
     </row>
-    <row r="489" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:36" ht="15.95" customHeight="1">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
@@ -19820,7 +19826,7 @@
       <c r="AI489" s="2"/>
       <c r="AJ489" s="2"/>
     </row>
-    <row r="490" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:36" ht="15.95" customHeight="1">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
@@ -19858,7 +19864,7 @@
       <c r="AI490" s="2"/>
       <c r="AJ490" s="2"/>
     </row>
-    <row r="491" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:36" ht="15.95" customHeight="1">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -19896,7 +19902,7 @@
       <c r="AI491" s="2"/>
       <c r="AJ491" s="2"/>
     </row>
-    <row r="492" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:36" ht="15.95" customHeight="1">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
@@ -19934,7 +19940,7 @@
       <c r="AI492" s="2"/>
       <c r="AJ492" s="2"/>
     </row>
-    <row r="493" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:36" ht="15.95" customHeight="1">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
@@ -19972,7 +19978,7 @@
       <c r="AI493" s="2"/>
       <c r="AJ493" s="2"/>
     </row>
-    <row r="494" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:36" ht="15.95" customHeight="1">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
@@ -20010,7 +20016,7 @@
       <c r="AI494" s="2"/>
       <c r="AJ494" s="2"/>
     </row>
-    <row r="495" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:36" ht="15.95" customHeight="1">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
@@ -20048,7 +20054,7 @@
       <c r="AI495" s="2"/>
       <c r="AJ495" s="2"/>
     </row>
-    <row r="496" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:36" ht="15.95" customHeight="1">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
@@ -20086,7 +20092,7 @@
       <c r="AI496" s="2"/>
       <c r="AJ496" s="2"/>
     </row>
-    <row r="497" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:36" ht="15.95" customHeight="1">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
@@ -20124,7 +20130,7 @@
       <c r="AI497" s="2"/>
       <c r="AJ497" s="2"/>
     </row>
-    <row r="498" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:36" ht="15.95" customHeight="1">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
@@ -20162,7 +20168,7 @@
       <c r="AI498" s="2"/>
       <c r="AJ498" s="2"/>
     </row>
-    <row r="499" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:36" ht="15.95" customHeight="1">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
@@ -20200,7 +20206,7 @@
       <c r="AI499" s="2"/>
       <c r="AJ499" s="2"/>
     </row>
-    <row r="500" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:36" ht="15.95" customHeight="1">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
@@ -20238,7 +20244,7 @@
       <c r="AI500" s="2"/>
       <c r="AJ500" s="2"/>
     </row>
-    <row r="501" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:36" ht="15.95" customHeight="1">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="2"/>
@@ -20276,7 +20282,7 @@
       <c r="AI501" s="2"/>
       <c r="AJ501" s="2"/>
     </row>
-    <row r="502" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:36" ht="15.95" customHeight="1">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
@@ -20314,7 +20320,7 @@
       <c r="AI502" s="2"/>
       <c r="AJ502" s="2"/>
     </row>
-    <row r="503" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:36" ht="15.95" customHeight="1">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="2"/>
@@ -20352,7 +20358,7 @@
       <c r="AI503" s="2"/>
       <c r="AJ503" s="2"/>
     </row>
-    <row r="504" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:36" ht="15.95" customHeight="1">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="2"/>
@@ -20390,7 +20396,7 @@
       <c r="AI504" s="2"/>
       <c r="AJ504" s="2"/>
     </row>
-    <row r="505" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:36" ht="15.95" customHeight="1">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="2"/>
@@ -20428,7 +20434,7 @@
       <c r="AI505" s="2"/>
       <c r="AJ505" s="2"/>
     </row>
-    <row r="506" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:36" ht="15.95" customHeight="1">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="2"/>
@@ -20466,7 +20472,7 @@
       <c r="AI506" s="2"/>
       <c r="AJ506" s="2"/>
     </row>
-    <row r="507" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:36" ht="15.95" customHeight="1">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="2"/>
@@ -20504,7 +20510,7 @@
       <c r="AI507" s="2"/>
       <c r="AJ507" s="2"/>
     </row>
-    <row r="508" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:36" ht="15.95" customHeight="1">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="2"/>
@@ -20542,7 +20548,7 @@
       <c r="AI508" s="2"/>
       <c r="AJ508" s="2"/>
     </row>
-    <row r="509" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:36" ht="15.95" customHeight="1">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="2"/>
@@ -20580,7 +20586,7 @@
       <c r="AI509" s="2"/>
       <c r="AJ509" s="2"/>
     </row>
-    <row r="510" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:36" ht="15.95" customHeight="1">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="2"/>
@@ -20618,7 +20624,7 @@
       <c r="AI510" s="2"/>
       <c r="AJ510" s="2"/>
     </row>
-    <row r="511" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:36" ht="15.95" customHeight="1">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="2"/>
@@ -20656,7 +20662,7 @@
       <c r="AI511" s="2"/>
       <c r="AJ511" s="2"/>
     </row>
-    <row r="512" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:36" ht="15.95" customHeight="1">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="2"/>
@@ -20694,7 +20700,7 @@
       <c r="AI512" s="2"/>
       <c r="AJ512" s="2"/>
     </row>
-    <row r="513" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:36" ht="15.95" customHeight="1">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="2"/>
@@ -20732,7 +20738,7 @@
       <c r="AI513" s="2"/>
       <c r="AJ513" s="2"/>
     </row>
-    <row r="514" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:36" ht="15.95" customHeight="1">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="2"/>
@@ -20770,7 +20776,7 @@
       <c r="AI514" s="2"/>
       <c r="AJ514" s="2"/>
     </row>
-    <row r="515" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:36" ht="15.95" customHeight="1">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="2"/>
@@ -20808,7 +20814,7 @@
       <c r="AI515" s="2"/>
       <c r="AJ515" s="2"/>
     </row>
-    <row r="516" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:36" ht="15.95" customHeight="1">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="2"/>
@@ -20846,7 +20852,7 @@
       <c r="AI516" s="2"/>
       <c r="AJ516" s="2"/>
     </row>
-    <row r="517" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:36" ht="15.95" customHeight="1">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="2"/>
@@ -20884,7 +20890,7 @@
       <c r="AI517" s="2"/>
       <c r="AJ517" s="2"/>
     </row>
-    <row r="518" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:36" ht="15.95" customHeight="1">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="2"/>
@@ -20922,7 +20928,7 @@
       <c r="AI518" s="2"/>
       <c r="AJ518" s="2"/>
     </row>
-    <row r="519" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:36" ht="15.95" customHeight="1">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="2"/>
@@ -20960,7 +20966,7 @@
       <c r="AI519" s="2"/>
       <c r="AJ519" s="2"/>
     </row>
-    <row r="520" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:36" ht="15.95" customHeight="1">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="2"/>
@@ -20998,7 +21004,7 @@
       <c r="AI520" s="2"/>
       <c r="AJ520" s="2"/>
     </row>
-    <row r="521" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:36" ht="15.95" customHeight="1">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
@@ -21036,7 +21042,7 @@
       <c r="AI521" s="2"/>
       <c r="AJ521" s="2"/>
     </row>
-    <row r="522" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:36" ht="15.95" customHeight="1">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="2"/>
@@ -21074,7 +21080,7 @@
       <c r="AI522" s="2"/>
       <c r="AJ522" s="2"/>
     </row>
-    <row r="523" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:36" ht="15.95" customHeight="1">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="2"/>
@@ -21112,7 +21118,7 @@
       <c r="AI523" s="2"/>
       <c r="AJ523" s="2"/>
     </row>
-    <row r="524" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:36" ht="15.95" customHeight="1">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="2"/>
@@ -21150,7 +21156,7 @@
       <c r="AI524" s="2"/>
       <c r="AJ524" s="2"/>
     </row>
-    <row r="525" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:36" ht="15.95" customHeight="1">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
@@ -21188,7 +21194,7 @@
       <c r="AI525" s="2"/>
       <c r="AJ525" s="2"/>
     </row>
-    <row r="526" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:36" ht="15.95" customHeight="1">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="2"/>
@@ -21226,7 +21232,7 @@
       <c r="AI526" s="2"/>
       <c r="AJ526" s="2"/>
     </row>
-    <row r="527" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:36" ht="15.95" customHeight="1">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="2"/>
@@ -21264,7 +21270,7 @@
       <c r="AI527" s="2"/>
       <c r="AJ527" s="2"/>
     </row>
-    <row r="528" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:36" ht="15.95" customHeight="1">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="2"/>
@@ -21302,7 +21308,7 @@
       <c r="AI528" s="2"/>
       <c r="AJ528" s="2"/>
     </row>
-    <row r="529" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:36" ht="15.95" customHeight="1">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="2"/>
@@ -21340,7 +21346,7 @@
       <c r="AI529" s="2"/>
       <c r="AJ529" s="2"/>
     </row>
-    <row r="530" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:36" ht="15.95" customHeight="1">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="2"/>
@@ -21378,7 +21384,7 @@
       <c r="AI530" s="2"/>
       <c r="AJ530" s="2"/>
     </row>
-    <row r="531" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:36" ht="15.95" customHeight="1">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
@@ -21416,7 +21422,7 @@
       <c r="AI531" s="2"/>
       <c r="AJ531" s="2"/>
     </row>
-    <row r="532" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:36" ht="15.95" customHeight="1">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="2"/>
@@ -21454,7 +21460,7 @@
       <c r="AI532" s="2"/>
       <c r="AJ532" s="2"/>
     </row>
-    <row r="533" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:36" ht="15.95" customHeight="1">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="2"/>
@@ -21492,7 +21498,7 @@
       <c r="AI533" s="2"/>
       <c r="AJ533" s="2"/>
     </row>
-    <row r="534" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:36" ht="15.95" customHeight="1">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="2"/>
@@ -21530,7 +21536,7 @@
       <c r="AI534" s="2"/>
       <c r="AJ534" s="2"/>
     </row>
-    <row r="535" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:36" ht="15.95" customHeight="1">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="2"/>
@@ -21568,7 +21574,7 @@
       <c r="AI535" s="2"/>
       <c r="AJ535" s="2"/>
     </row>
-    <row r="536" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:36" ht="15.95" customHeight="1">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="2"/>
@@ -21606,7 +21612,7 @@
       <c r="AI536" s="2"/>
       <c r="AJ536" s="2"/>
     </row>
-    <row r="537" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:36" ht="15.95" customHeight="1">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="2"/>
@@ -21644,7 +21650,7 @@
       <c r="AI537" s="2"/>
       <c r="AJ537" s="2"/>
     </row>
-    <row r="538" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:36" ht="15.95" customHeight="1">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="2"/>
@@ -21682,7 +21688,7 @@
       <c r="AI538" s="2"/>
       <c r="AJ538" s="2"/>
     </row>
-    <row r="539" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:36" ht="15.95" customHeight="1">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="2"/>
@@ -21720,7 +21726,7 @@
       <c r="AI539" s="2"/>
       <c r="AJ539" s="2"/>
     </row>
-    <row r="540" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:36" ht="15.95" customHeight="1">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="2"/>
@@ -21758,7 +21764,7 @@
       <c r="AI540" s="2"/>
       <c r="AJ540" s="2"/>
     </row>
-    <row r="541" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:36" ht="15.95" customHeight="1">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="2"/>
@@ -21796,7 +21802,7 @@
       <c r="AI541" s="2"/>
       <c r="AJ541" s="2"/>
     </row>
-    <row r="542" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:36" ht="15.95" customHeight="1">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="2"/>
@@ -21834,7 +21840,7 @@
       <c r="AI542" s="2"/>
       <c r="AJ542" s="2"/>
     </row>
-    <row r="543" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:36" ht="15.95" customHeight="1">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="2"/>
@@ -21872,7 +21878,7 @@
       <c r="AI543" s="2"/>
       <c r="AJ543" s="2"/>
     </row>
-    <row r="544" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:36" ht="15.95" customHeight="1">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="2"/>
@@ -21910,7 +21916,7 @@
       <c r="AI544" s="2"/>
       <c r="AJ544" s="2"/>
     </row>
-    <row r="545" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:36" ht="15.95" customHeight="1">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="2"/>
@@ -21948,7 +21954,7 @@
       <c r="AI545" s="2"/>
       <c r="AJ545" s="2"/>
     </row>
-    <row r="546" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:36" ht="15.95" customHeight="1">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
@@ -21986,7 +21992,7 @@
       <c r="AI546" s="2"/>
       <c r="AJ546" s="2"/>
     </row>
-    <row r="547" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:36" ht="15.95" customHeight="1">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="2"/>
@@ -22024,7 +22030,7 @@
       <c r="AI547" s="2"/>
       <c r="AJ547" s="2"/>
     </row>
-    <row r="548" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:36" ht="15.95" customHeight="1">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="2"/>
@@ -22062,7 +22068,7 @@
       <c r="AI548" s="2"/>
       <c r="AJ548" s="2"/>
     </row>
-    <row r="549" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:36" ht="15.95" customHeight="1">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="2"/>
@@ -22100,7 +22106,7 @@
       <c r="AI549" s="2"/>
       <c r="AJ549" s="2"/>
     </row>
-    <row r="550" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:36" ht="15.95" customHeight="1">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="2"/>
@@ -22138,7 +22144,7 @@
       <c r="AI550" s="2"/>
       <c r="AJ550" s="2"/>
     </row>
-    <row r="551" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:36" ht="15.95" customHeight="1">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="2"/>
@@ -22176,7 +22182,7 @@
       <c r="AI551" s="2"/>
       <c r="AJ551" s="2"/>
     </row>
-    <row r="552" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:36" ht="15.95" customHeight="1">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="2"/>
@@ -22214,7 +22220,7 @@
       <c r="AI552" s="2"/>
       <c r="AJ552" s="2"/>
     </row>
-    <row r="553" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:36" ht="15.95" customHeight="1">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="2"/>
@@ -22252,7 +22258,7 @@
       <c r="AI553" s="2"/>
       <c r="AJ553" s="2"/>
     </row>
-    <row r="554" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:36" ht="15.95" customHeight="1">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="2"/>
@@ -22290,7 +22296,7 @@
       <c r="AI554" s="2"/>
       <c r="AJ554" s="2"/>
     </row>
-    <row r="555" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:36" ht="15.95" customHeight="1">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="2"/>
@@ -22328,7 +22334,7 @@
       <c r="AI555" s="2"/>
       <c r="AJ555" s="2"/>
     </row>
-    <row r="556" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:36" ht="15.95" customHeight="1">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="2"/>
@@ -22366,7 +22372,7 @@
       <c r="AI556" s="2"/>
       <c r="AJ556" s="2"/>
     </row>
-    <row r="557" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:36" ht="15.95" customHeight="1">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="2"/>
@@ -22404,7 +22410,7 @@
       <c r="AI557" s="2"/>
       <c r="AJ557" s="2"/>
     </row>
-    <row r="558" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:36" ht="15.95" customHeight="1">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="2"/>
@@ -22442,7 +22448,7 @@
       <c r="AI558" s="2"/>
       <c r="AJ558" s="2"/>
     </row>
-    <row r="559" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:36" ht="15.95" customHeight="1">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="2"/>
@@ -22480,7 +22486,7 @@
       <c r="AI559" s="2"/>
       <c r="AJ559" s="2"/>
     </row>
-    <row r="560" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:36" ht="15.95" customHeight="1">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="2"/>
@@ -22518,7 +22524,7 @@
       <c r="AI560" s="2"/>
       <c r="AJ560" s="2"/>
     </row>
-    <row r="561" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:36" ht="15.95" customHeight="1">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="2"/>
@@ -22556,7 +22562,7 @@
       <c r="AI561" s="2"/>
       <c r="AJ561" s="2"/>
     </row>
-    <row r="562" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:36" ht="15.95" customHeight="1">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="2"/>
@@ -22594,7 +22600,7 @@
       <c r="AI562" s="2"/>
       <c r="AJ562" s="2"/>
     </row>
-    <row r="563" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:36" ht="15.95" customHeight="1">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="2"/>
@@ -22632,7 +22638,7 @@
       <c r="AI563" s="2"/>
       <c r="AJ563" s="2"/>
     </row>
-    <row r="564" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:36" ht="15.95" customHeight="1">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="2"/>
@@ -22670,7 +22676,7 @@
       <c r="AI564" s="2"/>
       <c r="AJ564" s="2"/>
     </row>
-    <row r="565" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:36" ht="15.95" customHeight="1">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="2"/>
@@ -22708,7 +22714,7 @@
       <c r="AI565" s="2"/>
       <c r="AJ565" s="2"/>
     </row>
-    <row r="566" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:36" ht="15.95" customHeight="1">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="2"/>
@@ -22746,7 +22752,7 @@
       <c r="AI566" s="2"/>
       <c r="AJ566" s="2"/>
     </row>
-    <row r="567" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:36" ht="15.95" customHeight="1">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="2"/>
@@ -22784,7 +22790,7 @@
       <c r="AI567" s="2"/>
       <c r="AJ567" s="2"/>
     </row>
-    <row r="568" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:36" ht="15.95" customHeight="1">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="2"/>
@@ -22822,7 +22828,7 @@
       <c r="AI568" s="2"/>
       <c r="AJ568" s="2"/>
     </row>
-    <row r="569" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:36" ht="15.95" customHeight="1">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="2"/>
@@ -22860,7 +22866,7 @@
       <c r="AI569" s="2"/>
       <c r="AJ569" s="2"/>
     </row>
-    <row r="570" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:36" ht="15.95" customHeight="1">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="2"/>
@@ -22898,7 +22904,7 @@
       <c r="AI570" s="2"/>
       <c r="AJ570" s="2"/>
     </row>
-    <row r="571" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:36" ht="15.95" customHeight="1">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="2"/>
@@ -22936,7 +22942,7 @@
       <c r="AI571" s="2"/>
       <c r="AJ571" s="2"/>
     </row>
-    <row r="572" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:36" ht="15.95" customHeight="1">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="2"/>
@@ -22974,7 +22980,7 @@
       <c r="AI572" s="2"/>
       <c r="AJ572" s="2"/>
     </row>
-    <row r="573" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:36" ht="15.95" customHeight="1">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="2"/>
@@ -23012,7 +23018,7 @@
       <c r="AI573" s="2"/>
       <c r="AJ573" s="2"/>
     </row>
-    <row r="574" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:36" ht="15.95" customHeight="1">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="2"/>
@@ -23050,7 +23056,7 @@
       <c r="AI574" s="2"/>
       <c r="AJ574" s="2"/>
     </row>
-    <row r="575" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:36" ht="15.95" customHeight="1">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="2"/>
@@ -23088,7 +23094,7 @@
       <c r="AI575" s="2"/>
       <c r="AJ575" s="2"/>
     </row>
-    <row r="576" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:36" ht="15.95" customHeight="1">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="2"/>
@@ -23126,7 +23132,7 @@
       <c r="AI576" s="2"/>
       <c r="AJ576" s="2"/>
     </row>
-    <row r="577" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:36" ht="15.95" customHeight="1">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="2"/>
@@ -23164,7 +23170,7 @@
       <c r="AI577" s="2"/>
       <c r="AJ577" s="2"/>
     </row>
-    <row r="578" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:36" ht="15.95" customHeight="1">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="2"/>
@@ -23202,7 +23208,7 @@
       <c r="AI578" s="2"/>
       <c r="AJ578" s="2"/>
     </row>
-    <row r="579" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:36" ht="15.95" customHeight="1">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="2"/>
@@ -23240,7 +23246,7 @@
       <c r="AI579" s="2"/>
       <c r="AJ579" s="2"/>
     </row>
-    <row r="580" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:36" ht="15.95" customHeight="1">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="2"/>
@@ -23278,7 +23284,7 @@
       <c r="AI580" s="2"/>
       <c r="AJ580" s="2"/>
     </row>
-    <row r="581" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:36" ht="15.95" customHeight="1">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="2"/>
@@ -23316,7 +23322,7 @@
       <c r="AI581" s="2"/>
       <c r="AJ581" s="2"/>
     </row>
-    <row r="582" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:36" ht="15.95" customHeight="1">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="2"/>
@@ -23354,7 +23360,7 @@
       <c r="AI582" s="2"/>
       <c r="AJ582" s="2"/>
     </row>
-    <row r="583" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:36" ht="15.95" customHeight="1">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="2"/>
@@ -23392,7 +23398,7 @@
       <c r="AI583" s="2"/>
       <c r="AJ583" s="2"/>
     </row>
-    <row r="584" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:36" ht="15.95" customHeight="1">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="2"/>
@@ -23430,7 +23436,7 @@
       <c r="AI584" s="2"/>
       <c r="AJ584" s="2"/>
     </row>
-    <row r="585" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:36" ht="15.95" customHeight="1">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="2"/>
@@ -23468,7 +23474,7 @@
       <c r="AI585" s="2"/>
       <c r="AJ585" s="2"/>
     </row>
-    <row r="586" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:36" ht="15.95" customHeight="1">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="2"/>
@@ -23506,7 +23512,7 @@
       <c r="AI586" s="2"/>
       <c r="AJ586" s="2"/>
     </row>
-    <row r="587" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:36" ht="15.95" customHeight="1">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="2"/>
@@ -23544,7 +23550,7 @@
       <c r="AI587" s="2"/>
       <c r="AJ587" s="2"/>
     </row>
-    <row r="588" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:36" ht="15.95" customHeight="1">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="2"/>
@@ -23582,7 +23588,7 @@
       <c r="AI588" s="2"/>
       <c r="AJ588" s="2"/>
     </row>
-    <row r="589" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:36" ht="15.95" customHeight="1">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="2"/>
@@ -23620,7 +23626,7 @@
       <c r="AI589" s="2"/>
       <c r="AJ589" s="2"/>
     </row>
-    <row r="590" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:36" ht="15.95" customHeight="1">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="2"/>
@@ -23658,7 +23664,7 @@
       <c r="AI590" s="2"/>
       <c r="AJ590" s="2"/>
     </row>
-    <row r="591" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:36" ht="15.95" customHeight="1">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="2"/>
@@ -23696,7 +23702,7 @@
       <c r="AI591" s="2"/>
       <c r="AJ591" s="2"/>
     </row>
-    <row r="592" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:36" ht="15.95" customHeight="1">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="2"/>
@@ -23734,7 +23740,7 @@
       <c r="AI592" s="2"/>
       <c r="AJ592" s="2"/>
     </row>
-    <row r="593" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:36" ht="15.95" customHeight="1">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="2"/>
@@ -23772,7 +23778,7 @@
       <c r="AI593" s="2"/>
       <c r="AJ593" s="2"/>
     </row>
-    <row r="594" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:36" ht="15.95" customHeight="1">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="2"/>
@@ -23810,7 +23816,7 @@
       <c r="AI594" s="2"/>
       <c r="AJ594" s="2"/>
     </row>
-    <row r="595" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:36" ht="15.95" customHeight="1">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="2"/>
@@ -23848,7 +23854,7 @@
       <c r="AI595" s="2"/>
       <c r="AJ595" s="2"/>
     </row>
-    <row r="596" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:36" ht="15.95" customHeight="1">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="2"/>
@@ -23886,7 +23892,7 @@
       <c r="AI596" s="2"/>
       <c r="AJ596" s="2"/>
     </row>
-    <row r="597" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:36" ht="15.95" customHeight="1">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="2"/>
@@ -23924,7 +23930,7 @@
       <c r="AI597" s="2"/>
       <c r="AJ597" s="2"/>
     </row>
-    <row r="598" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:36" ht="15.95" customHeight="1">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="2"/>
@@ -23962,7 +23968,7 @@
       <c r="AI598" s="2"/>
       <c r="AJ598" s="2"/>
     </row>
-    <row r="599" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:36" ht="15.95" customHeight="1">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="2"/>
@@ -24000,7 +24006,7 @@
       <c r="AI599" s="2"/>
       <c r="AJ599" s="2"/>
     </row>
-    <row r="600" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:36" ht="15.95" customHeight="1">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="2"/>
@@ -24038,7 +24044,7 @@
       <c r="AI600" s="2"/>
       <c r="AJ600" s="2"/>
     </row>
-    <row r="601" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:36" ht="15.95" customHeight="1">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="2"/>
@@ -24076,7 +24082,7 @@
       <c r="AI601" s="2"/>
       <c r="AJ601" s="2"/>
     </row>
-    <row r="602" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:36" ht="15.95" customHeight="1">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="2"/>
@@ -24114,7 +24120,7 @@
       <c r="AI602" s="2"/>
       <c r="AJ602" s="2"/>
     </row>
-    <row r="603" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:36" ht="15.95" customHeight="1">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="2"/>
@@ -24152,7 +24158,7 @@
       <c r="AI603" s="2"/>
       <c r="AJ603" s="2"/>
     </row>
-    <row r="604" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:36" ht="15.95" customHeight="1">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="2"/>
@@ -24190,7 +24196,7 @@
       <c r="AI604" s="2"/>
       <c r="AJ604" s="2"/>
     </row>
-    <row r="605" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:36" ht="15.95" customHeight="1">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="2"/>
@@ -24228,7 +24234,7 @@
       <c r="AI605" s="2"/>
       <c r="AJ605" s="2"/>
     </row>
-    <row r="606" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:36" ht="15.95" customHeight="1">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="2"/>
@@ -24266,7 +24272,7 @@
       <c r="AI606" s="2"/>
       <c r="AJ606" s="2"/>
     </row>
-    <row r="607" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:36" ht="15.95" customHeight="1">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="2"/>
@@ -24304,7 +24310,7 @@
       <c r="AI607" s="2"/>
       <c r="AJ607" s="2"/>
     </row>
-    <row r="608" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:36" ht="15.95" customHeight="1">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="2"/>
@@ -24342,7 +24348,7 @@
       <c r="AI608" s="2"/>
       <c r="AJ608" s="2"/>
     </row>
-    <row r="609" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:36" ht="15.95" customHeight="1">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="2"/>
@@ -24380,7 +24386,7 @@
       <c r="AI609" s="2"/>
       <c r="AJ609" s="2"/>
     </row>
-    <row r="610" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:36" ht="15.95" customHeight="1">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="2"/>
@@ -24418,7 +24424,7 @@
       <c r="AI610" s="2"/>
       <c r="AJ610" s="2"/>
     </row>
-    <row r="611" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:36" ht="15.95" customHeight="1">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="2"/>
@@ -24456,7 +24462,7 @@
       <c r="AI611" s="2"/>
       <c r="AJ611" s="2"/>
     </row>
-    <row r="612" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:36" ht="15.95" customHeight="1">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="2"/>
@@ -24494,7 +24500,7 @@
       <c r="AI612" s="2"/>
       <c r="AJ612" s="2"/>
     </row>
-    <row r="613" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:36" ht="15.95" customHeight="1">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="2"/>
@@ -24532,7 +24538,7 @@
       <c r="AI613" s="2"/>
       <c r="AJ613" s="2"/>
     </row>
-    <row r="614" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:36" ht="15.95" customHeight="1">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="2"/>
@@ -24570,7 +24576,7 @@
       <c r="AI614" s="2"/>
       <c r="AJ614" s="2"/>
     </row>
-    <row r="615" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:36" ht="15.95" customHeight="1">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="2"/>
@@ -24608,7 +24614,7 @@
       <c r="AI615" s="2"/>
       <c r="AJ615" s="2"/>
     </row>
-    <row r="616" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:36" ht="15.95" customHeight="1">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="2"/>
@@ -24646,7 +24652,7 @@
       <c r="AI616" s="2"/>
       <c r="AJ616" s="2"/>
     </row>
-    <row r="617" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:36" ht="15.95" customHeight="1">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="2"/>
@@ -24684,7 +24690,7 @@
       <c r="AI617" s="2"/>
       <c r="AJ617" s="2"/>
     </row>
-    <row r="618" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:36" ht="15.95" customHeight="1">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="2"/>
@@ -24722,7 +24728,7 @@
       <c r="AI618" s="2"/>
       <c r="AJ618" s="2"/>
     </row>
-    <row r="619" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:36" ht="15.95" customHeight="1">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="2"/>
@@ -24760,7 +24766,7 @@
       <c r="AI619" s="2"/>
       <c r="AJ619" s="2"/>
     </row>
-    <row r="620" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:36" ht="15.95" customHeight="1">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="2"/>
@@ -24798,7 +24804,7 @@
       <c r="AI620" s="2"/>
       <c r="AJ620" s="2"/>
     </row>
-    <row r="621" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:36" ht="15.95" customHeight="1">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="2"/>
@@ -24836,7 +24842,7 @@
       <c r="AI621" s="2"/>
       <c r="AJ621" s="2"/>
     </row>
-    <row r="622" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:36" ht="15.95" customHeight="1">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="2"/>
@@ -24874,7 +24880,7 @@
       <c r="AI622" s="2"/>
       <c r="AJ622" s="2"/>
     </row>
-    <row r="623" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:36" ht="15.95" customHeight="1">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="2"/>
@@ -24912,7 +24918,7 @@
       <c r="AI623" s="2"/>
       <c r="AJ623" s="2"/>
     </row>
-    <row r="624" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:36" ht="15.95" customHeight="1">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="2"/>
@@ -24950,7 +24956,7 @@
       <c r="AI624" s="2"/>
       <c r="AJ624" s="2"/>
     </row>
-    <row r="625" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:36" ht="15.95" customHeight="1">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="2"/>
@@ -24988,7 +24994,7 @@
       <c r="AI625" s="2"/>
       <c r="AJ625" s="2"/>
     </row>
-    <row r="626" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:36" ht="15.95" customHeight="1">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="2"/>
@@ -25026,7 +25032,7 @@
       <c r="AI626" s="2"/>
       <c r="AJ626" s="2"/>
     </row>
-    <row r="627" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:36" ht="15.95" customHeight="1">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="2"/>
@@ -25064,7 +25070,7 @@
       <c r="AI627" s="2"/>
       <c r="AJ627" s="2"/>
     </row>
-    <row r="628" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:36" ht="15.95" customHeight="1">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="2"/>
@@ -25102,7 +25108,7 @@
       <c r="AI628" s="2"/>
       <c r="AJ628" s="2"/>
     </row>
-    <row r="629" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:36" ht="15.95" customHeight="1">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="2"/>
@@ -25140,7 +25146,7 @@
       <c r="AI629" s="2"/>
       <c r="AJ629" s="2"/>
     </row>
-    <row r="630" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:36" ht="15.95" customHeight="1">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="2"/>
@@ -25178,7 +25184,7 @@
       <c r="AI630" s="2"/>
       <c r="AJ630" s="2"/>
     </row>
-    <row r="631" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:36" ht="15.95" customHeight="1">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="2"/>
@@ -25216,7 +25222,7 @@
       <c r="AI631" s="2"/>
       <c r="AJ631" s="2"/>
     </row>
-    <row r="632" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:36" ht="15.95" customHeight="1">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="2"/>
@@ -25254,7 +25260,7 @@
       <c r="AI632" s="2"/>
       <c r="AJ632" s="2"/>
     </row>
-    <row r="633" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:36" ht="15.95" customHeight="1">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="2"/>
@@ -25292,7 +25298,7 @@
       <c r="AI633" s="2"/>
       <c r="AJ633" s="2"/>
     </row>
-    <row r="634" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:36" ht="15.95" customHeight="1">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="2"/>
@@ -25330,7 +25336,7 @@
       <c r="AI634" s="2"/>
       <c r="AJ634" s="2"/>
     </row>
-    <row r="635" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:36" ht="15.95" customHeight="1">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="2"/>
@@ -25368,7 +25374,7 @@
       <c r="AI635" s="2"/>
       <c r="AJ635" s="2"/>
     </row>
-    <row r="636" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:36" ht="15.95" customHeight="1">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="2"/>
@@ -25406,7 +25412,7 @@
       <c r="AI636" s="2"/>
       <c r="AJ636" s="2"/>
     </row>
-    <row r="637" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:36" ht="15.95" customHeight="1">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="2"/>
@@ -25444,7 +25450,7 @@
       <c r="AI637" s="2"/>
       <c r="AJ637" s="2"/>
     </row>
-    <row r="638" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:36" ht="15.95" customHeight="1">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="2"/>
@@ -25482,7 +25488,7 @@
       <c r="AI638" s="2"/>
       <c r="AJ638" s="2"/>
     </row>
-    <row r="639" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:36" ht="15.95" customHeight="1">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="2"/>
@@ -25520,7 +25526,7 @@
       <c r="AI639" s="2"/>
       <c r="AJ639" s="2"/>
     </row>
-    <row r="640" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:36" ht="15.95" customHeight="1">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="2"/>
@@ -25558,7 +25564,7 @@
       <c r="AI640" s="2"/>
       <c r="AJ640" s="2"/>
     </row>
-    <row r="641" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:36" ht="15.95" customHeight="1">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="2"/>
@@ -25596,7 +25602,7 @@
       <c r="AI641" s="2"/>
       <c r="AJ641" s="2"/>
     </row>
-    <row r="642" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:36" ht="15.95" customHeight="1">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="2"/>
@@ -25634,7 +25640,7 @@
       <c r="AI642" s="2"/>
       <c r="AJ642" s="2"/>
     </row>
-    <row r="643" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:36" ht="15.95" customHeight="1">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="2"/>
@@ -25672,7 +25678,7 @@
       <c r="AI643" s="2"/>
       <c r="AJ643" s="2"/>
     </row>
-    <row r="644" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:36" ht="15.95" customHeight="1">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="2"/>
@@ -25710,7 +25716,7 @@
       <c r="AI644" s="2"/>
       <c r="AJ644" s="2"/>
     </row>
-    <row r="645" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:36" ht="15.95" customHeight="1">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="2"/>
@@ -25748,7 +25754,7 @@
       <c r="AI645" s="2"/>
       <c r="AJ645" s="2"/>
     </row>
-    <row r="646" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:36" ht="15.95" customHeight="1">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="2"/>
@@ -25786,7 +25792,7 @@
       <c r="AI646" s="2"/>
       <c r="AJ646" s="2"/>
     </row>
-    <row r="647" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:36" ht="15.95" customHeight="1">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="2"/>
@@ -25824,7 +25830,7 @@
       <c r="AI647" s="2"/>
       <c r="AJ647" s="2"/>
     </row>
-    <row r="648" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:36" ht="15.95" customHeight="1">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="2"/>
@@ -25862,7 +25868,7 @@
       <c r="AI648" s="2"/>
       <c r="AJ648" s="2"/>
     </row>
-    <row r="649" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:36" ht="15.95" customHeight="1">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="2"/>
@@ -25900,7 +25906,7 @@
       <c r="AI649" s="2"/>
       <c r="AJ649" s="2"/>
     </row>
-    <row r="650" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:36" ht="15.95" customHeight="1">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="2"/>
@@ -25938,7 +25944,7 @@
       <c r="AI650" s="2"/>
       <c r="AJ650" s="2"/>
     </row>
-    <row r="651" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:36" ht="15.95" customHeight="1">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="2"/>
@@ -25976,7 +25982,7 @@
       <c r="AI651" s="2"/>
       <c r="AJ651" s="2"/>
     </row>
-    <row r="652" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:36" ht="15.95" customHeight="1">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="2"/>
@@ -26014,7 +26020,7 @@
       <c r="AI652" s="2"/>
       <c r="AJ652" s="2"/>
     </row>
-    <row r="653" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:36" ht="15.95" customHeight="1">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="2"/>
@@ -26052,7 +26058,7 @@
       <c r="AI653" s="2"/>
       <c r="AJ653" s="2"/>
     </row>
-    <row r="654" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:36" ht="15.95" customHeight="1">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="2"/>
@@ -26090,7 +26096,7 @@
       <c r="AI654" s="2"/>
       <c r="AJ654" s="2"/>
     </row>
-    <row r="655" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:36" ht="15.95" customHeight="1">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="2"/>
@@ -26128,7 +26134,7 @@
       <c r="AI655" s="2"/>
       <c r="AJ655" s="2"/>
     </row>
-    <row r="656" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:36" ht="15.95" customHeight="1">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="2"/>
@@ -26166,7 +26172,7 @@
       <c r="AI656" s="2"/>
       <c r="AJ656" s="2"/>
     </row>
-    <row r="657" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:36" ht="15.95" customHeight="1">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="2"/>
@@ -26204,7 +26210,7 @@
       <c r="AI657" s="2"/>
       <c r="AJ657" s="2"/>
     </row>
-    <row r="658" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:36" ht="15.95" customHeight="1">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="2"/>
@@ -26242,7 +26248,7 @@
       <c r="AI658" s="2"/>
       <c r="AJ658" s="2"/>
     </row>
-    <row r="659" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:36" ht="15.95" customHeight="1">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="2"/>
@@ -26280,7 +26286,7 @@
       <c r="AI659" s="2"/>
       <c r="AJ659" s="2"/>
     </row>
-    <row r="660" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:36" ht="15.95" customHeight="1">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="2"/>
@@ -26318,7 +26324,7 @@
       <c r="AI660" s="2"/>
       <c r="AJ660" s="2"/>
     </row>
-    <row r="661" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:36" ht="15.95" customHeight="1">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="2"/>
@@ -26356,7 +26362,7 @@
       <c r="AI661" s="2"/>
       <c r="AJ661" s="2"/>
     </row>
-    <row r="662" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:36" ht="15.95" customHeight="1">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="2"/>
@@ -26394,7 +26400,7 @@
       <c r="AI662" s="2"/>
       <c r="AJ662" s="2"/>
     </row>
-    <row r="663" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:36" ht="15.95" customHeight="1">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="2"/>
@@ -26432,7 +26438,7 @@
       <c r="AI663" s="2"/>
       <c r="AJ663" s="2"/>
     </row>
-    <row r="664" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:36" ht="15.95" customHeight="1">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="2"/>
@@ -26470,7 +26476,7 @@
       <c r="AI664" s="2"/>
       <c r="AJ664" s="2"/>
     </row>
-    <row r="665" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:36" ht="15.95" customHeight="1">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="2"/>
@@ -26508,7 +26514,7 @@
       <c r="AI665" s="2"/>
       <c r="AJ665" s="2"/>
     </row>
-    <row r="666" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:36" ht="15.95" customHeight="1">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="2"/>
@@ -26546,7 +26552,7 @@
       <c r="AI666" s="2"/>
       <c r="AJ666" s="2"/>
     </row>
-    <row r="667" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:36" ht="15.95" customHeight="1">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="2"/>
@@ -26584,7 +26590,7 @@
       <c r="AI667" s="2"/>
       <c r="AJ667" s="2"/>
     </row>
-    <row r="668" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:36" ht="15.95" customHeight="1">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="2"/>
@@ -26622,7 +26628,7 @@
       <c r="AI668" s="2"/>
       <c r="AJ668" s="2"/>
     </row>
-    <row r="669" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:36" ht="15.95" customHeight="1">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="2"/>
@@ -26660,7 +26666,7 @@
       <c r="AI669" s="2"/>
       <c r="AJ669" s="2"/>
     </row>
-    <row r="670" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:36" ht="15.95" customHeight="1">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="2"/>
@@ -26698,7 +26704,7 @@
       <c r="AI670" s="2"/>
       <c r="AJ670" s="2"/>
     </row>
-    <row r="671" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:36" ht="15.95" customHeight="1">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="2"/>
@@ -26736,7 +26742,7 @@
       <c r="AI671" s="2"/>
       <c r="AJ671" s="2"/>
     </row>
-    <row r="672" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:36" ht="15.95" customHeight="1">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="2"/>
@@ -26774,7 +26780,7 @@
       <c r="AI672" s="2"/>
       <c r="AJ672" s="2"/>
     </row>
-    <row r="673" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:36" ht="15.95" customHeight="1">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="2"/>
@@ -26812,7 +26818,7 @@
       <c r="AI673" s="2"/>
       <c r="AJ673" s="2"/>
     </row>
-    <row r="674" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:36" ht="15.95" customHeight="1">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="2"/>
@@ -26850,7 +26856,7 @@
       <c r="AI674" s="2"/>
       <c r="AJ674" s="2"/>
     </row>
-    <row r="675" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:36" ht="15.95" customHeight="1">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="2"/>
@@ -26888,7 +26894,7 @@
       <c r="AI675" s="2"/>
       <c r="AJ675" s="2"/>
     </row>
-    <row r="676" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:36" ht="15.95" customHeight="1">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="2"/>
@@ -26926,7 +26932,7 @@
       <c r="AI676" s="2"/>
       <c r="AJ676" s="2"/>
     </row>
-    <row r="677" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:36" ht="15.95" customHeight="1">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="2"/>
@@ -26964,7 +26970,7 @@
       <c r="AI677" s="2"/>
       <c r="AJ677" s="2"/>
     </row>
-    <row r="678" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:36" ht="15.95" customHeight="1">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="2"/>
@@ -27002,7 +27008,7 @@
       <c r="AI678" s="2"/>
       <c r="AJ678" s="2"/>
     </row>
-    <row r="679" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:36" ht="15.95" customHeight="1">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="2"/>
@@ -27040,7 +27046,7 @@
       <c r="AI679" s="2"/>
       <c r="AJ679" s="2"/>
     </row>
-    <row r="680" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:36" ht="15.95" customHeight="1">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="2"/>
@@ -27078,7 +27084,7 @@
       <c r="AI680" s="2"/>
       <c r="AJ680" s="2"/>
     </row>
-    <row r="681" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:36" ht="15.95" customHeight="1">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="2"/>
@@ -27116,7 +27122,7 @@
       <c r="AI681" s="2"/>
       <c r="AJ681" s="2"/>
     </row>
-    <row r="682" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:36" ht="15.95" customHeight="1">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="2"/>
@@ -27154,7 +27160,7 @@
       <c r="AI682" s="2"/>
       <c r="AJ682" s="2"/>
     </row>
-    <row r="683" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:36" ht="15.95" customHeight="1">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="2"/>
@@ -27192,7 +27198,7 @@
       <c r="AI683" s="2"/>
       <c r="AJ683" s="2"/>
     </row>
-    <row r="684" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:36" ht="15.95" customHeight="1">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="2"/>
@@ -27230,7 +27236,7 @@
       <c r="AI684" s="2"/>
       <c r="AJ684" s="2"/>
     </row>
-    <row r="685" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:36" ht="15.95" customHeight="1">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="2"/>
@@ -27268,7 +27274,7 @@
       <c r="AI685" s="2"/>
       <c r="AJ685" s="2"/>
     </row>
-    <row r="686" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:36" ht="15.95" customHeight="1">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="2"/>
@@ -27306,7 +27312,7 @@
       <c r="AI686" s="2"/>
       <c r="AJ686" s="2"/>
     </row>
-    <row r="687" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:36" ht="15.95" customHeight="1">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="2"/>
@@ -27344,7 +27350,7 @@
       <c r="AI687" s="2"/>
       <c r="AJ687" s="2"/>
     </row>
-    <row r="688" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:36" ht="15.95" customHeight="1">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="2"/>
@@ -27382,7 +27388,7 @@
       <c r="AI688" s="2"/>
       <c r="AJ688" s="2"/>
     </row>
-    <row r="689" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:36" ht="15.95" customHeight="1">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="2"/>
@@ -27420,7 +27426,7 @@
       <c r="AI689" s="2"/>
       <c r="AJ689" s="2"/>
     </row>
-    <row r="690" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:36" ht="15.95" customHeight="1">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="2"/>
@@ -27458,7 +27464,7 @@
       <c r="AI690" s="2"/>
       <c r="AJ690" s="2"/>
     </row>
-    <row r="691" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:36" ht="15.95" customHeight="1">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="2"/>
@@ -27496,7 +27502,7 @@
       <c r="AI691" s="2"/>
       <c r="AJ691" s="2"/>
     </row>
-    <row r="692" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:36" ht="15.95" customHeight="1">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="2"/>
@@ -27534,7 +27540,7 @@
       <c r="AI692" s="2"/>
       <c r="AJ692" s="2"/>
     </row>
-    <row r="693" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:36" ht="15.95" customHeight="1">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="2"/>
@@ -27572,7 +27578,7 @@
       <c r="AI693" s="2"/>
       <c r="AJ693" s="2"/>
     </row>
-    <row r="694" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:36" ht="15.95" customHeight="1">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="2"/>
@@ -27610,7 +27616,7 @@
       <c r="AI694" s="2"/>
       <c r="AJ694" s="2"/>
     </row>
-    <row r="695" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:36" ht="15.95" customHeight="1">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="2"/>
@@ -27648,7 +27654,7 @@
       <c r="AI695" s="2"/>
       <c r="AJ695" s="2"/>
     </row>
-    <row r="696" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:36" ht="15.95" customHeight="1">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="2"/>
@@ -27686,7 +27692,7 @@
       <c r="AI696" s="2"/>
       <c r="AJ696" s="2"/>
     </row>
-    <row r="697" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:36" ht="15.95" customHeight="1">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="2"/>
@@ -27724,7 +27730,7 @@
       <c r="AI697" s="2"/>
       <c r="AJ697" s="2"/>
     </row>
-    <row r="698" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:36" ht="15.95" customHeight="1">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="2"/>
@@ -27762,7 +27768,7 @@
       <c r="AI698" s="2"/>
       <c r="AJ698" s="2"/>
     </row>
-    <row r="699" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:36" ht="15.95" customHeight="1">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="2"/>
@@ -27800,7 +27806,7 @@
       <c r="AI699" s="2"/>
       <c r="AJ699" s="2"/>
     </row>
-    <row r="700" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:36" ht="15.95" customHeight="1">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="2"/>
@@ -27838,7 +27844,7 @@
       <c r="AI700" s="2"/>
       <c r="AJ700" s="2"/>
     </row>
-    <row r="701" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:36" ht="15.95" customHeight="1">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="2"/>
@@ -27876,7 +27882,7 @@
       <c r="AI701" s="2"/>
       <c r="AJ701" s="2"/>
     </row>
-    <row r="702" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:36" ht="15.95" customHeight="1">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="2"/>
@@ -27914,7 +27920,7 @@
       <c r="AI702" s="2"/>
       <c r="AJ702" s="2"/>
     </row>
-    <row r="703" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:36" ht="15.95" customHeight="1">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="2"/>
@@ -27952,7 +27958,7 @@
       <c r="AI703" s="2"/>
       <c r="AJ703" s="2"/>
     </row>
-    <row r="704" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:36" ht="15.95" customHeight="1">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="2"/>
@@ -27990,7 +27996,7 @@
       <c r="AI704" s="2"/>
       <c r="AJ704" s="2"/>
     </row>
-    <row r="705" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:36" ht="15.95" customHeight="1">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="2"/>
@@ -28028,7 +28034,7 @@
       <c r="AI705" s="2"/>
       <c r="AJ705" s="2"/>
     </row>
-    <row r="706" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:36" ht="15.95" customHeight="1">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="2"/>
@@ -28066,7 +28072,7 @@
       <c r="AI706" s="2"/>
       <c r="AJ706" s="2"/>
     </row>
-    <row r="707" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:36" ht="15.95" customHeight="1">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="2"/>
@@ -28104,7 +28110,7 @@
       <c r="AI707" s="2"/>
       <c r="AJ707" s="2"/>
     </row>
-    <row r="708" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:36" ht="15.95" customHeight="1">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="2"/>
@@ -28142,7 +28148,7 @@
       <c r="AI708" s="2"/>
       <c r="AJ708" s="2"/>
     </row>
-    <row r="709" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:36" ht="15.95" customHeight="1">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="2"/>
@@ -28180,7 +28186,7 @@
       <c r="AI709" s="2"/>
       <c r="AJ709" s="2"/>
     </row>
-    <row r="710" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:36" ht="15.95" customHeight="1">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="2"/>
@@ -28218,7 +28224,7 @@
       <c r="AI710" s="2"/>
       <c r="AJ710" s="2"/>
     </row>
-    <row r="711" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:36" ht="15.95" customHeight="1">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="2"/>
@@ -28256,7 +28262,7 @@
       <c r="AI711" s="2"/>
       <c r="AJ711" s="2"/>
     </row>
-    <row r="712" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:36" ht="15.95" customHeight="1">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="2"/>
@@ -28294,7 +28300,7 @@
       <c r="AI712" s="2"/>
       <c r="AJ712" s="2"/>
     </row>
-    <row r="713" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:36" ht="15.95" customHeight="1">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="2"/>
@@ -28332,7 +28338,7 @@
       <c r="AI713" s="2"/>
       <c r="AJ713" s="2"/>
     </row>
-    <row r="714" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:36" ht="15.95" customHeight="1">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="2"/>
@@ -28370,7 +28376,7 @@
       <c r="AI714" s="2"/>
       <c r="AJ714" s="2"/>
     </row>
-    <row r="715" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:36" ht="15.95" customHeight="1">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
@@ -28408,7 +28414,7 @@
       <c r="AI715" s="2"/>
       <c r="AJ715" s="2"/>
     </row>
-    <row r="716" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:36" ht="15.95" customHeight="1">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="2"/>
@@ -28446,7 +28452,7 @@
       <c r="AI716" s="2"/>
       <c r="AJ716" s="2"/>
     </row>
-    <row r="717" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:36" ht="15.95" customHeight="1">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="2"/>
@@ -28484,7 +28490,7 @@
       <c r="AI717" s="2"/>
       <c r="AJ717" s="2"/>
     </row>
-    <row r="718" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:36" ht="15.95" customHeight="1">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="2"/>
@@ -28522,7 +28528,7 @@
       <c r="AI718" s="2"/>
       <c r="AJ718" s="2"/>
     </row>
-    <row r="719" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:36" ht="15.95" customHeight="1">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="2"/>
@@ -28560,7 +28566,7 @@
       <c r="AI719" s="2"/>
       <c r="AJ719" s="2"/>
     </row>
-    <row r="720" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:36" ht="15.95" customHeight="1">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="2"/>
@@ -28598,7 +28604,7 @@
       <c r="AI720" s="2"/>
       <c r="AJ720" s="2"/>
     </row>
-    <row r="721" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:36" ht="15.95" customHeight="1">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="2"/>
@@ -28636,7 +28642,7 @@
       <c r="AI721" s="2"/>
       <c r="AJ721" s="2"/>
     </row>
-    <row r="722" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:36" ht="15.95" customHeight="1">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="2"/>
@@ -28674,7 +28680,7 @@
       <c r="AI722" s="2"/>
       <c r="AJ722" s="2"/>
     </row>
-    <row r="723" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:36" ht="15.95" customHeight="1">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="2"/>
@@ -28712,7 +28718,7 @@
       <c r="AI723" s="2"/>
       <c r="AJ723" s="2"/>
     </row>
-    <row r="724" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:36" ht="15.95" customHeight="1">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="2"/>
@@ -28750,7 +28756,7 @@
       <c r="AI724" s="2"/>
       <c r="AJ724" s="2"/>
     </row>
-    <row r="725" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:36" ht="15.95" customHeight="1">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="2"/>
@@ -28788,7 +28794,7 @@
       <c r="AI725" s="2"/>
       <c r="AJ725" s="2"/>
     </row>
-    <row r="726" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:36" ht="15.95" customHeight="1">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="2"/>
@@ -28826,7 +28832,7 @@
       <c r="AI726" s="2"/>
       <c r="AJ726" s="2"/>
     </row>
-    <row r="727" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:36" ht="15.95" customHeight="1">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="2"/>
@@ -28864,7 +28870,7 @@
       <c r="AI727" s="2"/>
       <c r="AJ727" s="2"/>
     </row>
-    <row r="728" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:36" ht="15.95" customHeight="1">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="2"/>
@@ -28902,7 +28908,7 @@
       <c r="AI728" s="2"/>
       <c r="AJ728" s="2"/>
     </row>
-    <row r="729" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:36" ht="15.95" customHeight="1">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="2"/>
@@ -28940,7 +28946,7 @@
       <c r="AI729" s="2"/>
       <c r="AJ729" s="2"/>
     </row>
-    <row r="730" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:36" ht="15.95" customHeight="1">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="2"/>
@@ -28978,7 +28984,7 @@
       <c r="AI730" s="2"/>
       <c r="AJ730" s="2"/>
     </row>
-    <row r="731" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:36" ht="15.95" customHeight="1">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="2"/>
@@ -29016,7 +29022,7 @@
       <c r="AI731" s="2"/>
       <c r="AJ731" s="2"/>
     </row>
-    <row r="732" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:36" ht="15.95" customHeight="1">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="2"/>
@@ -29054,7 +29060,7 @@
       <c r="AI732" s="2"/>
       <c r="AJ732" s="2"/>
     </row>
-    <row r="733" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:36" ht="15.95" customHeight="1">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="2"/>
@@ -29092,7 +29098,7 @@
       <c r="AI733" s="2"/>
       <c r="AJ733" s="2"/>
     </row>
-    <row r="734" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:36" ht="15.95" customHeight="1">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="2"/>
@@ -29130,7 +29136,7 @@
       <c r="AI734" s="2"/>
       <c r="AJ734" s="2"/>
     </row>
-    <row r="735" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:36" ht="15.95" customHeight="1">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="2"/>
@@ -29168,7 +29174,7 @@
       <c r="AI735" s="2"/>
       <c r="AJ735" s="2"/>
     </row>
-    <row r="736" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:36" ht="15.95" customHeight="1">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="2"/>
@@ -29206,7 +29212,7 @@
       <c r="AI736" s="2"/>
       <c r="AJ736" s="2"/>
     </row>
-    <row r="737" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:36" ht="15.95" customHeight="1">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="2"/>
@@ -29244,7 +29250,7 @@
       <c r="AI737" s="2"/>
       <c r="AJ737" s="2"/>
     </row>
-    <row r="738" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:36" ht="15.95" customHeight="1">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="2"/>
@@ -29282,7 +29288,7 @@
       <c r="AI738" s="2"/>
       <c r="AJ738" s="2"/>
     </row>
-    <row r="739" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:36" ht="15.95" customHeight="1">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="2"/>
@@ -29320,7 +29326,7 @@
       <c r="AI739" s="2"/>
       <c r="AJ739" s="2"/>
     </row>
-    <row r="740" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:36" ht="15.95" customHeight="1">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="2"/>
@@ -29358,7 +29364,7 @@
       <c r="AI740" s="2"/>
       <c r="AJ740" s="2"/>
     </row>
-    <row r="741" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:36" ht="15.95" customHeight="1">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="2"/>
@@ -29396,7 +29402,7 @@
       <c r="AI741" s="2"/>
       <c r="AJ741" s="2"/>
     </row>
-    <row r="742" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:36" ht="15.95" customHeight="1">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="2"/>
@@ -29434,7 +29440,7 @@
       <c r="AI742" s="2"/>
       <c r="AJ742" s="2"/>
     </row>
-    <row r="743" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:36" ht="15.95" customHeight="1">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="2"/>
@@ -29472,7 +29478,7 @@
       <c r="AI743" s="2"/>
       <c r="AJ743" s="2"/>
     </row>
-    <row r="744" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:36" ht="15.95" customHeight="1">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="2"/>
@@ -29510,7 +29516,7 @@
       <c r="AI744" s="2"/>
       <c r="AJ744" s="2"/>
     </row>
-    <row r="745" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:36" ht="15.95" customHeight="1">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="2"/>
@@ -29548,7 +29554,7 @@
       <c r="AI745" s="2"/>
       <c r="AJ745" s="2"/>
     </row>
-    <row r="746" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:36" ht="15.95" customHeight="1">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="2"/>
@@ -29586,7 +29592,7 @@
       <c r="AI746" s="2"/>
       <c r="AJ746" s="2"/>
     </row>
-    <row r="747" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:36" ht="15.95" customHeight="1">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="2"/>
@@ -29624,7 +29630,7 @@
       <c r="AI747" s="2"/>
       <c r="AJ747" s="2"/>
     </row>
-    <row r="748" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:36" ht="15.95" customHeight="1">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="2"/>
@@ -29662,7 +29668,7 @@
       <c r="AI748" s="2"/>
       <c r="AJ748" s="2"/>
     </row>
-    <row r="749" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:36" ht="15.95" customHeight="1">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="2"/>
@@ -29700,7 +29706,7 @@
       <c r="AI749" s="2"/>
       <c r="AJ749" s="2"/>
     </row>
-    <row r="750" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:36" ht="15.95" customHeight="1">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="2"/>
@@ -29738,7 +29744,7 @@
       <c r="AI750" s="2"/>
       <c r="AJ750" s="2"/>
     </row>
-    <row r="751" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:36" ht="15.95" customHeight="1">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="2"/>
@@ -29776,7 +29782,7 @@
       <c r="AI751" s="2"/>
       <c r="AJ751" s="2"/>
     </row>
-    <row r="752" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:36" ht="15.95" customHeight="1">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="2"/>
@@ -29814,7 +29820,7 @@
       <c r="AI752" s="2"/>
       <c r="AJ752" s="2"/>
     </row>
-    <row r="753" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:36" ht="15.95" customHeight="1">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="2"/>
@@ -29852,7 +29858,7 @@
       <c r="AI753" s="2"/>
       <c r="AJ753" s="2"/>
     </row>
-    <row r="754" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:36" ht="15.95" customHeight="1">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="2"/>
@@ -29890,7 +29896,7 @@
       <c r="AI754" s="2"/>
       <c r="AJ754" s="2"/>
     </row>
-    <row r="755" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:36" ht="15.95" customHeight="1">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="2"/>
@@ -29928,7 +29934,7 @@
       <c r="AI755" s="2"/>
       <c r="AJ755" s="2"/>
     </row>
-    <row r="756" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:36" ht="15.95" customHeight="1">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="2"/>
@@ -29966,7 +29972,7 @@
       <c r="AI756" s="2"/>
       <c r="AJ756" s="2"/>
     </row>
-    <row r="757" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:36" ht="15.95" customHeight="1">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="2"/>
@@ -30004,7 +30010,7 @@
       <c r="AI757" s="2"/>
       <c r="AJ757" s="2"/>
     </row>
-    <row r="758" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:36" ht="15.95" customHeight="1">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="2"/>
@@ -30042,7 +30048,7 @@
       <c r="AI758" s="2"/>
       <c r="AJ758" s="2"/>
     </row>
-    <row r="759" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:36" ht="15.95" customHeight="1">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="2"/>
@@ -30080,7 +30086,7 @@
       <c r="AI759" s="2"/>
       <c r="AJ759" s="2"/>
     </row>
-    <row r="760" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:36" ht="15.95" customHeight="1">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="2"/>
@@ -30118,7 +30124,7 @@
       <c r="AI760" s="2"/>
       <c r="AJ760" s="2"/>
     </row>
-    <row r="761" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:36" ht="15.95" customHeight="1">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="2"/>
@@ -30156,7 +30162,7 @@
       <c r="AI761" s="2"/>
       <c r="AJ761" s="2"/>
     </row>
-    <row r="762" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:36" ht="15.95" customHeight="1">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="2"/>
@@ -30194,7 +30200,7 @@
       <c r="AI762" s="2"/>
       <c r="AJ762" s="2"/>
     </row>
-    <row r="763" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:36" ht="15.95" customHeight="1">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="2"/>
@@ -30232,7 +30238,7 @@
       <c r="AI763" s="2"/>
       <c r="AJ763" s="2"/>
     </row>
-    <row r="764" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:36" ht="15.95" customHeight="1">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="2"/>
@@ -30270,7 +30276,7 @@
       <c r="AI764" s="2"/>
       <c r="AJ764" s="2"/>
     </row>
-    <row r="765" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:36" ht="15.95" customHeight="1">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="2"/>
@@ -30308,7 +30314,7 @@
       <c r="AI765" s="2"/>
       <c r="AJ765" s="2"/>
     </row>
-    <row r="766" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:36" ht="15.95" customHeight="1">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="2"/>
@@ -30346,7 +30352,7 @@
       <c r="AI766" s="2"/>
       <c r="AJ766" s="2"/>
     </row>
-    <row r="767" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:36" ht="15.95" customHeight="1">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="2"/>
@@ -30384,7 +30390,7 @@
       <c r="AI767" s="2"/>
       <c r="AJ767" s="2"/>
     </row>
-    <row r="768" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:36" ht="15.95" customHeight="1">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="2"/>
@@ -30422,7 +30428,7 @@
       <c r="AI768" s="2"/>
       <c r="AJ768" s="2"/>
     </row>
-    <row r="769" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:36" ht="15.95" customHeight="1">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="2"/>
@@ -30460,7 +30466,7 @@
       <c r="AI769" s="2"/>
       <c r="AJ769" s="2"/>
     </row>
-    <row r="770" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:36" ht="15.95" customHeight="1">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="2"/>
@@ -30498,7 +30504,7 @@
       <c r="AI770" s="2"/>
       <c r="AJ770" s="2"/>
     </row>
-    <row r="771" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:36" ht="15.95" customHeight="1">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="2"/>
@@ -30536,7 +30542,7 @@
       <c r="AI771" s="2"/>
       <c r="AJ771" s="2"/>
     </row>
-    <row r="772" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:36" ht="15.95" customHeight="1">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="2"/>
@@ -30574,7 +30580,7 @@
       <c r="AI772" s="2"/>
       <c r="AJ772" s="2"/>
     </row>
-    <row r="773" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:36" ht="15.95" customHeight="1">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="2"/>
@@ -30612,7 +30618,7 @@
       <c r="AI773" s="2"/>
       <c r="AJ773" s="2"/>
     </row>
-    <row r="774" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:36" ht="15.95" customHeight="1">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="2"/>
@@ -30650,7 +30656,7 @@
       <c r="AI774" s="2"/>
       <c r="AJ774" s="2"/>
     </row>
-    <row r="775" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:36" ht="15.95" customHeight="1">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="2"/>
@@ -30688,7 +30694,7 @@
       <c r="AI775" s="2"/>
       <c r="AJ775" s="2"/>
     </row>
-    <row r="776" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:36" ht="15.95" customHeight="1">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="2"/>
@@ -30726,7 +30732,7 @@
       <c r="AI776" s="2"/>
       <c r="AJ776" s="2"/>
     </row>
-    <row r="777" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:36" ht="15.95" customHeight="1">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="2"/>
@@ -30764,7 +30770,7 @@
       <c r="AI777" s="2"/>
       <c r="AJ777" s="2"/>
     </row>
-    <row r="778" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:36" ht="15.95" customHeight="1">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="2"/>
@@ -30802,7 +30808,7 @@
       <c r="AI778" s="2"/>
       <c r="AJ778" s="2"/>
     </row>
-    <row r="779" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:36" ht="15.95" customHeight="1">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="2"/>
@@ -30840,7 +30846,7 @@
       <c r="AI779" s="2"/>
       <c r="AJ779" s="2"/>
     </row>
-    <row r="780" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:36" ht="15.95" customHeight="1">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="2"/>
@@ -30878,7 +30884,7 @@
       <c r="AI780" s="2"/>
       <c r="AJ780" s="2"/>
     </row>
-    <row r="781" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:36" ht="15.95" customHeight="1">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="2"/>
@@ -30916,7 +30922,7 @@
       <c r="AI781" s="2"/>
       <c r="AJ781" s="2"/>
     </row>
-    <row r="782" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:36" ht="15.95" customHeight="1">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="2"/>
@@ -30954,7 +30960,7 @@
       <c r="AI782" s="2"/>
       <c r="AJ782" s="2"/>
     </row>
-    <row r="783" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:36" ht="15.95" customHeight="1">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="2"/>
@@ -30992,7 +30998,7 @@
       <c r="AI783" s="2"/>
       <c r="AJ783" s="2"/>
     </row>
-    <row r="784" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:36" ht="15.95" customHeight="1">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="2"/>
@@ -31030,7 +31036,7 @@
       <c r="AI784" s="2"/>
       <c r="AJ784" s="2"/>
     </row>
-    <row r="785" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:36" ht="15.95" customHeight="1">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="2"/>
@@ -31068,7 +31074,7 @@
       <c r="AI785" s="2"/>
       <c r="AJ785" s="2"/>
     </row>
-    <row r="786" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:36" ht="15.95" customHeight="1">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="2"/>
@@ -31106,7 +31112,7 @@
       <c r="AI786" s="2"/>
       <c r="AJ786" s="2"/>
     </row>
-    <row r="787" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:36" ht="15.95" customHeight="1">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="2"/>
@@ -31144,7 +31150,7 @@
       <c r="AI787" s="2"/>
       <c r="AJ787" s="2"/>
     </row>
-    <row r="788" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:36" ht="15.95" customHeight="1">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="2"/>
@@ -31182,7 +31188,7 @@
       <c r="AI788" s="2"/>
       <c r="AJ788" s="2"/>
     </row>
-    <row r="789" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:36" ht="15.95" customHeight="1">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="2"/>
@@ -31220,7 +31226,7 @@
       <c r="AI789" s="2"/>
       <c r="AJ789" s="2"/>
     </row>
-    <row r="790" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:36" ht="15.95" customHeight="1">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="2"/>
@@ -31258,7 +31264,7 @@
       <c r="AI790" s="2"/>
       <c r="AJ790" s="2"/>
     </row>
-    <row r="791" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:36" ht="15.95" customHeight="1">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="2"/>
@@ -31296,7 +31302,7 @@
       <c r="AI791" s="2"/>
       <c r="AJ791" s="2"/>
     </row>
-    <row r="792" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:36" ht="15.95" customHeight="1">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="2"/>
@@ -31334,7 +31340,7 @@
       <c r="AI792" s="2"/>
       <c r="AJ792" s="2"/>
     </row>
-    <row r="793" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:36" ht="15.95" customHeight="1">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="2"/>
@@ -31372,7 +31378,7 @@
       <c r="AI793" s="2"/>
       <c r="AJ793" s="2"/>
     </row>
-    <row r="794" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:36" ht="15.95" customHeight="1">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="2"/>
@@ -31410,7 +31416,7 @@
       <c r="AI794" s="2"/>
       <c r="AJ794" s="2"/>
     </row>
-    <row r="795" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:36" ht="15.95" customHeight="1">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="2"/>
@@ -31448,7 +31454,7 @@
       <c r="AI795" s="2"/>
       <c r="AJ795" s="2"/>
     </row>
-    <row r="796" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:36" ht="15.95" customHeight="1">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="2"/>
@@ -31486,7 +31492,7 @@
       <c r="AI796" s="2"/>
       <c r="AJ796" s="2"/>
     </row>
-    <row r="797" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:36" ht="15.95" customHeight="1">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="2"/>
@@ -31524,7 +31530,7 @@
       <c r="AI797" s="2"/>
       <c r="AJ797" s="2"/>
     </row>
-    <row r="798" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:36" ht="15.95" customHeight="1">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="2"/>
@@ -31562,7 +31568,7 @@
       <c r="AI798" s="2"/>
       <c r="AJ798" s="2"/>
     </row>
-    <row r="799" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:36" ht="15.95" customHeight="1">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="2"/>
@@ -31600,7 +31606,7 @@
       <c r="AI799" s="2"/>
       <c r="AJ799" s="2"/>
     </row>
-    <row r="800" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:36" ht="15.95" customHeight="1">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="2"/>
@@ -31638,7 +31644,7 @@
       <c r="AI800" s="2"/>
       <c r="AJ800" s="2"/>
     </row>
-    <row r="801" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:36" ht="15.95" customHeight="1">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="2"/>
@@ -31676,7 +31682,7 @@
       <c r="AI801" s="2"/>
       <c r="AJ801" s="2"/>
     </row>
-    <row r="802" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:36" ht="15.95" customHeight="1">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="2"/>
@@ -31714,7 +31720,7 @@
       <c r="AI802" s="2"/>
       <c r="AJ802" s="2"/>
     </row>
-    <row r="803" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:36" ht="15.95" customHeight="1">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="2"/>
@@ -31752,7 +31758,7 @@
       <c r="AI803" s="2"/>
       <c r="AJ803" s="2"/>
     </row>
-    <row r="804" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:36" ht="15.95" customHeight="1">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="2"/>
@@ -31790,7 +31796,7 @@
       <c r="AI804" s="2"/>
       <c r="AJ804" s="2"/>
     </row>
-    <row r="805" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:36" ht="15.95" customHeight="1">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="2"/>
@@ -31828,7 +31834,7 @@
       <c r="AI805" s="2"/>
       <c r="AJ805" s="2"/>
     </row>
-    <row r="806" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:36" ht="15.95" customHeight="1">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="2"/>
@@ -31866,7 +31872,7 @@
       <c r="AI806" s="2"/>
       <c r="AJ806" s="2"/>
     </row>
-    <row r="807" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:36" ht="15.95" customHeight="1">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="2"/>
@@ -31904,7 +31910,7 @@
       <c r="AI807" s="2"/>
       <c r="AJ807" s="2"/>
     </row>
-    <row r="808" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:36" ht="15.95" customHeight="1">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="2"/>
@@ -31942,7 +31948,7 @@
       <c r="AI808" s="2"/>
       <c r="AJ808" s="2"/>
     </row>
-    <row r="809" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:36" ht="15.95" customHeight="1">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="2"/>
@@ -31980,7 +31986,7 @@
       <c r="AI809" s="2"/>
       <c r="AJ809" s="2"/>
     </row>
-    <row r="810" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:36" ht="15.95" customHeight="1">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="2"/>
@@ -32018,7 +32024,7 @@
       <c r="AI810" s="2"/>
       <c r="AJ810" s="2"/>
     </row>
-    <row r="811" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:36" ht="15.95" customHeight="1">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="2"/>
@@ -32056,7 +32062,7 @@
       <c r="AI811" s="2"/>
       <c r="AJ811" s="2"/>
     </row>
-    <row r="812" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:36" ht="15.95" customHeight="1">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="2"/>
@@ -32094,7 +32100,7 @@
       <c r="AI812" s="2"/>
       <c r="AJ812" s="2"/>
     </row>
-    <row r="813" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:36" ht="15.95" customHeight="1">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="2"/>
@@ -32132,7 +32138,7 @@
       <c r="AI813" s="2"/>
       <c r="AJ813" s="2"/>
     </row>
-    <row r="814" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:36" ht="15.95" customHeight="1">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="2"/>
@@ -32170,7 +32176,7 @@
       <c r="AI814" s="2"/>
       <c r="AJ814" s="2"/>
     </row>
-    <row r="815" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:36" ht="15.95" customHeight="1">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="2"/>
@@ -32208,7 +32214,7 @@
       <c r="AI815" s="2"/>
       <c r="AJ815" s="2"/>
     </row>
-    <row r="816" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:36" ht="15.95" customHeight="1">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="2"/>
@@ -32246,7 +32252,7 @@
       <c r="AI816" s="2"/>
       <c r="AJ816" s="2"/>
     </row>
-    <row r="817" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:36" ht="15.95" customHeight="1">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="2"/>
@@ -32284,7 +32290,7 @@
       <c r="AI817" s="2"/>
       <c r="AJ817" s="2"/>
     </row>
-    <row r="818" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:36" ht="15.95" customHeight="1">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="2"/>
@@ -32322,7 +32328,7 @@
       <c r="AI818" s="2"/>
       <c r="AJ818" s="2"/>
     </row>
-    <row r="819" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:36" ht="15.95" customHeight="1">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="2"/>
@@ -32360,7 +32366,7 @@
       <c r="AI819" s="2"/>
       <c r="AJ819" s="2"/>
     </row>
-    <row r="820" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:36" ht="15.95" customHeight="1">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="2"/>
@@ -32398,7 +32404,7 @@
       <c r="AI820" s="2"/>
       <c r="AJ820" s="2"/>
     </row>
-    <row r="821" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:36" ht="15.95" customHeight="1">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="2"/>
@@ -32436,7 +32442,7 @@
       <c r="AI821" s="2"/>
       <c r="AJ821" s="2"/>
     </row>
-    <row r="822" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:36" ht="15.95" customHeight="1">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="2"/>
@@ -32474,7 +32480,7 @@
       <c r="AI822" s="2"/>
       <c r="AJ822" s="2"/>
     </row>
-    <row r="823" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:36" ht="15.95" customHeight="1">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="2"/>
@@ -32512,7 +32518,7 @@
       <c r="AI823" s="2"/>
       <c r="AJ823" s="2"/>
     </row>
-    <row r="824" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:36" ht="15.95" customHeight="1">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="2"/>
@@ -32550,7 +32556,7 @@
       <c r="AI824" s="2"/>
       <c r="AJ824" s="2"/>
     </row>
-    <row r="825" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:36" ht="15.95" customHeight="1">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="2"/>
@@ -32588,7 +32594,7 @@
       <c r="AI825" s="2"/>
       <c r="AJ825" s="2"/>
     </row>
-    <row r="826" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:36" ht="15.95" customHeight="1">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="2"/>
@@ -32626,7 +32632,7 @@
       <c r="AI826" s="2"/>
       <c r="AJ826" s="2"/>
     </row>
-    <row r="827" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:36" ht="15.95" customHeight="1">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="2"/>
@@ -32664,7 +32670,7 @@
       <c r="AI827" s="2"/>
       <c r="AJ827" s="2"/>
     </row>
-    <row r="828" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:36" ht="15.95" customHeight="1">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="2"/>
@@ -32702,7 +32708,7 @@
       <c r="AI828" s="2"/>
       <c r="AJ828" s="2"/>
     </row>
-    <row r="829" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:36" ht="15.95" customHeight="1">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="2"/>
@@ -32740,7 +32746,7 @@
       <c r="AI829" s="2"/>
       <c r="AJ829" s="2"/>
     </row>
-    <row r="830" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:36" ht="15.95" customHeight="1">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="2"/>
@@ -32778,7 +32784,7 @@
       <c r="AI830" s="2"/>
       <c r="AJ830" s="2"/>
     </row>
-    <row r="831" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:36" ht="15.95" customHeight="1">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="2"/>
@@ -32816,7 +32822,7 @@
       <c r="AI831" s="2"/>
       <c r="AJ831" s="2"/>
     </row>
-    <row r="832" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:36" ht="15.95" customHeight="1">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="2"/>
@@ -32854,7 +32860,7 @@
       <c r="AI832" s="2"/>
       <c r="AJ832" s="2"/>
     </row>
-    <row r="833" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:36" ht="15.95" customHeight="1">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="2"/>
@@ -32892,7 +32898,7 @@
       <c r="AI833" s="2"/>
       <c r="AJ833" s="2"/>
     </row>
-    <row r="834" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:36" ht="15.95" customHeight="1">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="2"/>
@@ -32930,7 +32936,7 @@
       <c r="AI834" s="2"/>
       <c r="AJ834" s="2"/>
     </row>
-    <row r="835" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:36" ht="15.95" customHeight="1">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="2"/>
@@ -32968,7 +32974,7 @@
       <c r="AI835" s="2"/>
       <c r="AJ835" s="2"/>
     </row>
-    <row r="836" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:36" ht="15.95" customHeight="1">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="2"/>
@@ -33006,7 +33012,7 @@
       <c r="AI836" s="2"/>
       <c r="AJ836" s="2"/>
     </row>
-    <row r="837" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:36" ht="15.95" customHeight="1">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="2"/>
@@ -33044,7 +33050,7 @@
       <c r="AI837" s="2"/>
       <c r="AJ837" s="2"/>
     </row>
-    <row r="838" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:36" ht="15.95" customHeight="1">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="2"/>
@@ -33082,7 +33088,7 @@
       <c r="AI838" s="2"/>
       <c r="AJ838" s="2"/>
     </row>
-    <row r="839" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:36" ht="15.95" customHeight="1">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="2"/>
@@ -33120,7 +33126,7 @@
       <c r="AI839" s="2"/>
       <c r="AJ839" s="2"/>
     </row>
-    <row r="840" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:36" ht="15.95" customHeight="1">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="2"/>
@@ -33158,7 +33164,7 @@
       <c r="AI840" s="2"/>
       <c r="AJ840" s="2"/>
     </row>
-    <row r="841" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:36" ht="15.95" customHeight="1">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="2"/>
@@ -33196,7 +33202,7 @@
       <c r="AI841" s="2"/>
       <c r="AJ841" s="2"/>
     </row>
-    <row r="842" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:36" ht="15.95" customHeight="1">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="2"/>
@@ -33234,7 +33240,7 @@
       <c r="AI842" s="2"/>
       <c r="AJ842" s="2"/>
     </row>
-    <row r="843" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:36" ht="15.95" customHeight="1">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="2"/>
@@ -33272,7 +33278,7 @@
       <c r="AI843" s="2"/>
       <c r="AJ843" s="2"/>
     </row>
-    <row r="844" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:36" ht="15.95" customHeight="1">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="2"/>
@@ -33310,7 +33316,7 @@
       <c r="AI844" s="2"/>
       <c r="AJ844" s="2"/>
     </row>
-    <row r="845" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:36" ht="15.95" customHeight="1">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="2"/>
@@ -33348,7 +33354,7 @@
       <c r="AI845" s="2"/>
       <c r="AJ845" s="2"/>
     </row>
-    <row r="846" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:36" ht="15.95" customHeight="1">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="2"/>
@@ -33386,7 +33392,7 @@
       <c r="AI846" s="2"/>
       <c r="AJ846" s="2"/>
     </row>
-    <row r="847" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:36" ht="15.95" customHeight="1">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="2"/>
@@ -33424,7 +33430,7 @@
       <c r="AI847" s="2"/>
       <c r="AJ847" s="2"/>
     </row>
-    <row r="848" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:36" ht="15.95" customHeight="1">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="2"/>
@@ -33462,7 +33468,7 @@
       <c r="AI848" s="2"/>
       <c r="AJ848" s="2"/>
     </row>
-    <row r="849" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:36" ht="15.95" customHeight="1">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="2"/>
@@ -33500,7 +33506,7 @@
       <c r="AI849" s="2"/>
       <c r="AJ849" s="2"/>
     </row>
-    <row r="850" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:36" ht="15.95" customHeight="1">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="2"/>
@@ -33538,7 +33544,7 @@
       <c r="AI850" s="2"/>
       <c r="AJ850" s="2"/>
     </row>
-    <row r="851" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:36" ht="15.95" customHeight="1">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="2"/>
@@ -33576,7 +33582,7 @@
       <c r="AI851" s="2"/>
       <c r="AJ851" s="2"/>
     </row>
-    <row r="852" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:36" ht="15.95" customHeight="1">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="2"/>
@@ -33614,7 +33620,7 @@
       <c r="AI852" s="2"/>
       <c r="AJ852" s="2"/>
     </row>
-    <row r="853" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:36" ht="15.95" customHeight="1">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="2"/>
@@ -33652,7 +33658,7 @@
       <c r="AI853" s="2"/>
       <c r="AJ853" s="2"/>
     </row>
-    <row r="854" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:36" ht="15.95" customHeight="1">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="2"/>
@@ -33690,7 +33696,7 @@
       <c r="AI854" s="2"/>
       <c r="AJ854" s="2"/>
     </row>
-    <row r="855" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:36" ht="15.95" customHeight="1">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="2"/>
@@ -33728,7 +33734,7 @@
       <c r="AI855" s="2"/>
       <c r="AJ855" s="2"/>
     </row>
-    <row r="856" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:36" ht="15.95" customHeight="1">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="2"/>
@@ -33766,7 +33772,7 @@
       <c r="AI856" s="2"/>
       <c r="AJ856" s="2"/>
     </row>
-    <row r="857" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:36" ht="15.95" customHeight="1">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="2"/>
@@ -33804,7 +33810,7 @@
       <c r="AI857" s="2"/>
       <c r="AJ857" s="2"/>
     </row>
-    <row r="858" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:36" ht="15.95" customHeight="1">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="2"/>
@@ -33842,7 +33848,7 @@
       <c r="AI858" s="2"/>
       <c r="AJ858" s="2"/>
     </row>
-    <row r="859" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:36" ht="15.95" customHeight="1">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="2"/>
@@ -33880,7 +33886,7 @@
       <c r="AI859" s="2"/>
       <c r="AJ859" s="2"/>
     </row>
-    <row r="860" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:36" ht="15.95" customHeight="1">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="2"/>
@@ -33918,7 +33924,7 @@
       <c r="AI860" s="2"/>
       <c r="AJ860" s="2"/>
     </row>
-    <row r="861" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:36" ht="15.95" customHeight="1">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="2"/>
@@ -33956,7 +33962,7 @@
       <c r="AI861" s="2"/>
       <c r="AJ861" s="2"/>
     </row>
-    <row r="862" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:36" ht="15.95" customHeight="1">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="2"/>
@@ -33994,7 +34000,7 @@
       <c r="AI862" s="2"/>
       <c r="AJ862" s="2"/>
     </row>
-    <row r="863" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:36" ht="15.95" customHeight="1">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="2"/>
@@ -34032,7 +34038,7 @@
       <c r="AI863" s="2"/>
       <c r="AJ863" s="2"/>
     </row>
-    <row r="864" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:36" ht="15.95" customHeight="1">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="2"/>
@@ -34070,7 +34076,7 @@
       <c r="AI864" s="2"/>
       <c r="AJ864" s="2"/>
     </row>
-    <row r="865" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:36" ht="15.95" customHeight="1">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="2"/>
@@ -34108,7 +34114,7 @@
       <c r="AI865" s="2"/>
       <c r="AJ865" s="2"/>
     </row>
-    <row r="866" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:36" ht="15.95" customHeight="1">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="2"/>
@@ -34146,7 +34152,7 @@
       <c r="AI866" s="2"/>
       <c r="AJ866" s="2"/>
     </row>
-    <row r="867" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:36" ht="15.95" customHeight="1">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="2"/>
@@ -34184,7 +34190,7 @@
       <c r="AI867" s="2"/>
       <c r="AJ867" s="2"/>
     </row>
-    <row r="868" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:36" ht="15.95" customHeight="1">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="2"/>
@@ -34222,7 +34228,7 @@
       <c r="AI868" s="2"/>
       <c r="AJ868" s="2"/>
     </row>
-    <row r="869" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:36" ht="15.95" customHeight="1">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="2"/>
@@ -34260,7 +34266,7 @@
       <c r="AI869" s="2"/>
       <c r="AJ869" s="2"/>
     </row>
-    <row r="870" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:36" ht="15.95" customHeight="1">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="2"/>
@@ -34298,7 +34304,7 @@
       <c r="AI870" s="2"/>
       <c r="AJ870" s="2"/>
     </row>
-    <row r="871" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:36" ht="15.95" customHeight="1">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="2"/>
@@ -34336,7 +34342,7 @@
       <c r="AI871" s="2"/>
       <c r="AJ871" s="2"/>
     </row>
-    <row r="872" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:36" ht="15.95" customHeight="1">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="2"/>
@@ -34374,7 +34380,7 @@
       <c r="AI872" s="2"/>
       <c r="AJ872" s="2"/>
     </row>
-    <row r="873" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:36" ht="15.95" customHeight="1">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="2"/>
@@ -34412,7 +34418,7 @@
       <c r="AI873" s="2"/>
       <c r="AJ873" s="2"/>
     </row>
-    <row r="874" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:36" ht="15.95" customHeight="1">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="2"/>
@@ -34450,7 +34456,7 @@
       <c r="AI874" s="2"/>
       <c r="AJ874" s="2"/>
     </row>
-    <row r="875" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:36" ht="15.95" customHeight="1">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="2"/>
@@ -34488,7 +34494,7 @@
       <c r="AI875" s="2"/>
       <c r="AJ875" s="2"/>
     </row>
-    <row r="876" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:36" ht="15.95" customHeight="1">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="2"/>
@@ -34526,7 +34532,7 @@
       <c r="AI876" s="2"/>
       <c r="AJ876" s="2"/>
     </row>
-    <row r="877" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:36" ht="15.95" customHeight="1">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="2"/>
@@ -34564,7 +34570,7 @@
       <c r="AI877" s="2"/>
       <c r="AJ877" s="2"/>
     </row>
-    <row r="878" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:36" ht="15.95" customHeight="1">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="2"/>
@@ -34602,7 +34608,7 @@
       <c r="AI878" s="2"/>
       <c r="AJ878" s="2"/>
     </row>
-    <row r="879" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:36" ht="15.95" customHeight="1">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="2"/>
@@ -34640,7 +34646,7 @@
       <c r="AI879" s="2"/>
       <c r="AJ879" s="2"/>
     </row>
-    <row r="880" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:36" ht="15.95" customHeight="1">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="2"/>
@@ -34678,7 +34684,7 @@
       <c r="AI880" s="2"/>
       <c r="AJ880" s="2"/>
     </row>
-    <row r="881" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:36" ht="15.95" customHeight="1">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="2"/>
@@ -34716,7 +34722,7 @@
       <c r="AI881" s="2"/>
       <c r="AJ881" s="2"/>
     </row>
-    <row r="882" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:36" ht="15.95" customHeight="1">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="2"/>
@@ -34754,7 +34760,7 @@
       <c r="AI882" s="2"/>
       <c r="AJ882" s="2"/>
     </row>
-    <row r="883" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:36" ht="15.95" customHeight="1">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="2"/>
@@ -34792,7 +34798,7 @@
       <c r="AI883" s="2"/>
       <c r="AJ883" s="2"/>
     </row>
-    <row r="884" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:36" ht="15.95" customHeight="1">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="2"/>
@@ -34830,7 +34836,7 @@
       <c r="AI884" s="2"/>
       <c r="AJ884" s="2"/>
     </row>
-    <row r="885" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:36" ht="15.95" customHeight="1">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="2"/>
@@ -34868,7 +34874,7 @@
       <c r="AI885" s="2"/>
       <c r="AJ885" s="2"/>
     </row>
-    <row r="886" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:36" ht="15.95" customHeight="1">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="2"/>
@@ -34906,7 +34912,7 @@
       <c r="AI886" s="2"/>
       <c r="AJ886" s="2"/>
     </row>
-    <row r="887" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:36" ht="15.95" customHeight="1">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="2"/>
@@ -34944,7 +34950,7 @@
       <c r="AI887" s="2"/>
       <c r="AJ887" s="2"/>
     </row>
-    <row r="888" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:36" ht="15.95" customHeight="1">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="2"/>
@@ -34982,7 +34988,7 @@
       <c r="AI888" s="2"/>
       <c r="AJ888" s="2"/>
     </row>
-    <row r="889" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:36" ht="15.95" customHeight="1">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="2"/>
@@ -35020,7 +35026,7 @@
       <c r="AI889" s="2"/>
       <c r="AJ889" s="2"/>
     </row>
-    <row r="890" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:36" ht="15.95" customHeight="1">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="2"/>
@@ -35058,7 +35064,7 @@
       <c r="AI890" s="2"/>
       <c r="AJ890" s="2"/>
     </row>
-    <row r="891" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:36" ht="15.95" customHeight="1">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="2"/>
@@ -35096,7 +35102,7 @@
       <c r="AI891" s="2"/>
       <c r="AJ891" s="2"/>
     </row>
-    <row r="892" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:36" ht="15.95" customHeight="1">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="2"/>
@@ -35134,7 +35140,7 @@
       <c r="AI892" s="2"/>
       <c r="AJ892" s="2"/>
     </row>
-    <row r="893" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:36" ht="15.95" customHeight="1">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="2"/>
@@ -35172,7 +35178,7 @@
       <c r="AI893" s="2"/>
       <c r="AJ893" s="2"/>
     </row>
-    <row r="894" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:36" ht="15.95" customHeight="1">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="2"/>
@@ -35210,7 +35216,7 @@
       <c r="AI894" s="2"/>
       <c r="AJ894" s="2"/>
     </row>
-    <row r="895" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:36" ht="15.95" customHeight="1">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="2"/>
@@ -35248,7 +35254,7 @@
       <c r="AI895" s="2"/>
       <c r="AJ895" s="2"/>
     </row>
-    <row r="896" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:36" ht="15.95" customHeight="1">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="2"/>
@@ -35286,7 +35292,7 @@
       <c r="AI896" s="2"/>
       <c r="AJ896" s="2"/>
     </row>
-    <row r="897" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:36" ht="15.95" customHeight="1">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="2"/>
@@ -35324,7 +35330,7 @@
       <c r="AI897" s="2"/>
       <c r="AJ897" s="2"/>
     </row>
-    <row r="898" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:36" ht="15.95" customHeight="1">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="2"/>
@@ -35362,7 +35368,7 @@
       <c r="AI898" s="2"/>
       <c r="AJ898" s="2"/>
     </row>
-    <row r="899" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:36" ht="15.95" customHeight="1">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="2"/>
@@ -35400,7 +35406,7 @@
       <c r="AI899" s="2"/>
       <c r="AJ899" s="2"/>
     </row>
-    <row r="900" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:36" ht="15.95" customHeight="1">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="2"/>
@@ -35438,7 +35444,7 @@
       <c r="AI900" s="2"/>
       <c r="AJ900" s="2"/>
     </row>
-    <row r="901" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:36" ht="15.95" customHeight="1">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="2"/>
@@ -35476,7 +35482,7 @@
       <c r="AI901" s="2"/>
       <c r="AJ901" s="2"/>
     </row>
-    <row r="902" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:36" ht="15.95" customHeight="1">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="2"/>
@@ -35514,7 +35520,7 @@
       <c r="AI902" s="2"/>
       <c r="AJ902" s="2"/>
     </row>
-    <row r="903" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:36" ht="15.95" customHeight="1">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="2"/>
@@ -35552,7 +35558,7 @@
       <c r="AI903" s="2"/>
       <c r="AJ903" s="2"/>
     </row>
-    <row r="904" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:36" ht="15.95" customHeight="1">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="2"/>
@@ -35590,7 +35596,7 @@
       <c r="AI904" s="2"/>
       <c r="AJ904" s="2"/>
     </row>
-    <row r="905" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:36" ht="15.95" customHeight="1">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="2"/>
@@ -35628,7 +35634,7 @@
       <c r="AI905" s="2"/>
       <c r="AJ905" s="2"/>
     </row>
-    <row r="906" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:36" ht="15.95" customHeight="1">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="2"/>
@@ -35666,7 +35672,7 @@
       <c r="AI906" s="2"/>
       <c r="AJ906" s="2"/>
     </row>
-    <row r="907" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:36" ht="15.95" customHeight="1">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="2"/>
@@ -35704,7 +35710,7 @@
       <c r="AI907" s="2"/>
       <c r="AJ907" s="2"/>
     </row>
-    <row r="908" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:36" ht="15.95" customHeight="1">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="2"/>
@@ -35742,7 +35748,7 @@
       <c r="AI908" s="2"/>
       <c r="AJ908" s="2"/>
     </row>
-    <row r="909" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:36" ht="15.95" customHeight="1">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="2"/>
@@ -35780,7 +35786,7 @@
       <c r="AI909" s="2"/>
       <c r="AJ909" s="2"/>
     </row>
-    <row r="910" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:36" ht="15.95" customHeight="1">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="2"/>
@@ -35818,7 +35824,7 @@
       <c r="AI910" s="2"/>
       <c r="AJ910" s="2"/>
     </row>
-    <row r="911" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:36" ht="15.95" customHeight="1">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="2"/>
@@ -35856,7 +35862,7 @@
       <c r="AI911" s="2"/>
       <c r="AJ911" s="2"/>
     </row>
-    <row r="912" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:36" ht="15.95" customHeight="1">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="2"/>
@@ -35894,7 +35900,7 @@
       <c r="AI912" s="2"/>
       <c r="AJ912" s="2"/>
     </row>
-    <row r="913" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:36" ht="15.95" customHeight="1">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="2"/>
@@ -35932,7 +35938,7 @@
       <c r="AI913" s="2"/>
       <c r="AJ913" s="2"/>
     </row>
-    <row r="914" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:36" ht="15.95" customHeight="1">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="2"/>
@@ -35970,7 +35976,7 @@
       <c r="AI914" s="2"/>
       <c r="AJ914" s="2"/>
     </row>
-    <row r="915" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:36" ht="15.95" customHeight="1">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="2"/>
@@ -36008,7 +36014,7 @@
       <c r="AI915" s="2"/>
       <c r="AJ915" s="2"/>
     </row>
-    <row r="916" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:36" ht="15.95" customHeight="1">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="2"/>
@@ -36046,7 +36052,7 @@
       <c r="AI916" s="2"/>
       <c r="AJ916" s="2"/>
     </row>
-    <row r="917" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:36" ht="15.95" customHeight="1">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="2"/>
@@ -36084,7 +36090,7 @@
       <c r="AI917" s="2"/>
       <c r="AJ917" s="2"/>
     </row>
-    <row r="918" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:36" ht="15.95" customHeight="1">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="2"/>
@@ -36122,7 +36128,7 @@
       <c r="AI918" s="2"/>
       <c r="AJ918" s="2"/>
     </row>
-    <row r="919" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:36" ht="15.95" customHeight="1">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="2"/>
@@ -36160,7 +36166,7 @@
       <c r="AI919" s="2"/>
       <c r="AJ919" s="2"/>
     </row>
-    <row r="920" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:36" ht="15.95" customHeight="1">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="2"/>
@@ -36198,7 +36204,7 @@
       <c r="AI920" s="2"/>
       <c r="AJ920" s="2"/>
     </row>
-    <row r="921" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:36" ht="15.95" customHeight="1">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="2"/>
@@ -36236,7 +36242,7 @@
       <c r="AI921" s="2"/>
       <c r="AJ921" s="2"/>
     </row>
-    <row r="922" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:36" ht="15.95" customHeight="1">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="2"/>
@@ -36274,7 +36280,7 @@
       <c r="AI922" s="2"/>
       <c r="AJ922" s="2"/>
     </row>
-    <row r="923" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:36" ht="15.95" customHeight="1">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="2"/>
@@ -36312,7 +36318,7 @@
       <c r="AI923" s="2"/>
       <c r="AJ923" s="2"/>
     </row>
-    <row r="924" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:36" ht="15.95" customHeight="1">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="2"/>
@@ -36350,7 +36356,7 @@
       <c r="AI924" s="2"/>
       <c r="AJ924" s="2"/>
     </row>
-    <row r="925" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:36" ht="15.95" customHeight="1">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="2"/>
@@ -36388,7 +36394,7 @@
       <c r="AI925" s="2"/>
       <c r="AJ925" s="2"/>
     </row>
-    <row r="926" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:36" ht="15.95" customHeight="1">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="2"/>
@@ -36426,7 +36432,7 @@
       <c r="AI926" s="2"/>
       <c r="AJ926" s="2"/>
     </row>
-    <row r="927" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:36" ht="15.95" customHeight="1">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="2"/>
@@ -36464,7 +36470,7 @@
       <c r="AI927" s="2"/>
       <c r="AJ927" s="2"/>
     </row>
-    <row r="928" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:36" ht="15.95" customHeight="1">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="2"/>
@@ -36502,7 +36508,7 @@
       <c r="AI928" s="2"/>
       <c r="AJ928" s="2"/>
     </row>
-    <row r="929" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:36" ht="15.95" customHeight="1">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="2"/>
@@ -36540,7 +36546,7 @@
       <c r="AI929" s="2"/>
       <c r="AJ929" s="2"/>
     </row>
-    <row r="930" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:36" ht="15.95" customHeight="1">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="2"/>
@@ -36578,7 +36584,7 @@
       <c r="AI930" s="2"/>
       <c r="AJ930" s="2"/>
     </row>
-    <row r="931" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:36" ht="15.95" customHeight="1">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="2"/>
@@ -36616,7 +36622,7 @@
       <c r="AI931" s="2"/>
       <c r="AJ931" s="2"/>
     </row>
-    <row r="932" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:36" ht="15.95" customHeight="1">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="2"/>
@@ -36654,7 +36660,7 @@
       <c r="AI932" s="2"/>
       <c r="AJ932" s="2"/>
     </row>
-    <row r="933" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:36" ht="15.95" customHeight="1">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="2"/>
@@ -36692,7 +36698,7 @@
       <c r="AI933" s="2"/>
       <c r="AJ933" s="2"/>
     </row>
-    <row r="934" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:36" ht="15.95" customHeight="1">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="2"/>
@@ -36730,7 +36736,7 @@
       <c r="AI934" s="2"/>
       <c r="AJ934" s="2"/>
     </row>
-    <row r="935" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:36" ht="15.95" customHeight="1">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="2"/>
@@ -36768,7 +36774,7 @@
       <c r="AI935" s="2"/>
       <c r="AJ935" s="2"/>
     </row>
-    <row r="936" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:36" ht="15.95" customHeight="1">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="2"/>
@@ -36806,7 +36812,7 @@
       <c r="AI936" s="2"/>
       <c r="AJ936" s="2"/>
     </row>
-    <row r="937" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:36" ht="15.95" customHeight="1">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="2"/>
@@ -36844,7 +36850,7 @@
       <c r="AI937" s="2"/>
       <c r="AJ937" s="2"/>
     </row>
-    <row r="938" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:36" ht="15.95" customHeight="1">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="2"/>
@@ -36882,7 +36888,7 @@
       <c r="AI938" s="2"/>
       <c r="AJ938" s="2"/>
     </row>
-    <row r="939" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:36" ht="15.95" customHeight="1">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="2"/>
@@ -36920,7 +36926,7 @@
       <c r="AI939" s="2"/>
       <c r="AJ939" s="2"/>
     </row>
-    <row r="940" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:36" ht="15.95" customHeight="1">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="2"/>
@@ -36958,7 +36964,7 @@
       <c r="AI940" s="2"/>
       <c r="AJ940" s="2"/>
     </row>
-    <row r="941" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:36" ht="15.95" customHeight="1">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="2"/>
@@ -36996,7 +37002,7 @@
       <c r="AI941" s="2"/>
       <c r="AJ941" s="2"/>
     </row>
-    <row r="942" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:36" ht="15.95" customHeight="1">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="2"/>
@@ -37034,7 +37040,7 @@
       <c r="AI942" s="2"/>
       <c r="AJ942" s="2"/>
     </row>
-    <row r="943" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:36" ht="15.95" customHeight="1">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="2"/>
@@ -37072,7 +37078,7 @@
       <c r="AI943" s="2"/>
       <c r="AJ943" s="2"/>
     </row>
-    <row r="944" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:36" ht="15.95" customHeight="1">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="2"/>
@@ -37110,7 +37116,7 @@
       <c r="AI944" s="2"/>
       <c r="AJ944" s="2"/>
     </row>
-    <row r="945" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:36" ht="15.95" customHeight="1">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="2"/>
@@ -37148,7 +37154,7 @@
       <c r="AI945" s="2"/>
       <c r="AJ945" s="2"/>
     </row>
-    <row r="946" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:36" ht="15.95" customHeight="1">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="2"/>
@@ -37186,7 +37192,7 @@
       <c r="AI946" s="2"/>
       <c r="AJ946" s="2"/>
     </row>
-    <row r="947" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:36" ht="15.95" customHeight="1">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="2"/>
@@ -37224,7 +37230,7 @@
       <c r="AI947" s="2"/>
       <c r="AJ947" s="2"/>
     </row>
-    <row r="948" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:36" ht="15.95" customHeight="1">
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="2"/>
@@ -37262,7 +37268,7 @@
       <c r="AI948" s="2"/>
       <c r="AJ948" s="2"/>
     </row>
-    <row r="949" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:36" ht="15.95" customHeight="1">
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="2"/>
@@ -37300,7 +37306,7 @@
       <c r="AI949" s="2"/>
       <c r="AJ949" s="2"/>
     </row>
-    <row r="950" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:36" ht="15.95" customHeight="1">
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="2"/>
@@ -37338,7 +37344,7 @@
       <c r="AI950" s="2"/>
       <c r="AJ950" s="2"/>
     </row>
-    <row r="951" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:36" ht="15.95" customHeight="1">
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="2"/>
@@ -37376,7 +37382,7 @@
       <c r="AI951" s="2"/>
       <c r="AJ951" s="2"/>
     </row>
-    <row r="952" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:36" ht="15.95" customHeight="1">
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
       <c r="C952" s="2"/>
@@ -37414,7 +37420,7 @@
       <c r="AI952" s="2"/>
       <c r="AJ952" s="2"/>
     </row>
-    <row r="953" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:36" ht="15.95" customHeight="1">
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
       <c r="C953" s="2"/>
@@ -37452,7 +37458,7 @@
       <c r="AI953" s="2"/>
       <c r="AJ953" s="2"/>
     </row>
-    <row r="954" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:36" ht="15.95" customHeight="1">
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
       <c r="C954" s="2"/>
@@ -37490,7 +37496,7 @@
       <c r="AI954" s="2"/>
       <c r="AJ954" s="2"/>
     </row>
-    <row r="955" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:36" ht="15.95" customHeight="1">
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
       <c r="C955" s="2"/>
@@ -37528,7 +37534,7 @@
       <c r="AI955" s="2"/>
       <c r="AJ955" s="2"/>
     </row>
-    <row r="956" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:36" ht="15.95" customHeight="1">
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
       <c r="C956" s="2"/>
@@ -37566,7 +37572,7 @@
       <c r="AI956" s="2"/>
       <c r="AJ956" s="2"/>
     </row>
-    <row r="957" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:36" ht="15.95" customHeight="1">
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
       <c r="C957" s="2"/>
@@ -37604,7 +37610,7 @@
       <c r="AI957" s="2"/>
       <c r="AJ957" s="2"/>
     </row>
-    <row r="958" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:36" ht="15.95" customHeight="1">
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
       <c r="C958" s="2"/>
@@ -37642,7 +37648,7 @@
       <c r="AI958" s="2"/>
       <c r="AJ958" s="2"/>
     </row>
-    <row r="959" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:36" ht="15.95" customHeight="1">
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
       <c r="C959" s="2"/>
@@ -37680,7 +37686,7 @@
       <c r="AI959" s="2"/>
       <c r="AJ959" s="2"/>
     </row>
-    <row r="960" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:36" ht="15.95" customHeight="1">
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
       <c r="C960" s="2"/>
@@ -37718,7 +37724,7 @@
       <c r="AI960" s="2"/>
       <c r="AJ960" s="2"/>
     </row>
-    <row r="961" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:36" ht="15.95" customHeight="1">
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="2"/>
@@ -37756,7 +37762,7 @@
       <c r="AI961" s="2"/>
       <c r="AJ961" s="2"/>
     </row>
-    <row r="962" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:36" ht="15.95" customHeight="1">
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="2"/>
@@ -37794,7 +37800,7 @@
       <c r="AI962" s="2"/>
       <c r="AJ962" s="2"/>
     </row>
-    <row r="963" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:36" ht="15.95" customHeight="1">
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
       <c r="C963" s="2"/>
@@ -37832,7 +37838,7 @@
       <c r="AI963" s="2"/>
       <c r="AJ963" s="2"/>
     </row>
-    <row r="964" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:36" ht="15.95" customHeight="1">
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
       <c r="C964" s="2"/>
@@ -37870,7 +37876,7 @@
       <c r="AI964" s="2"/>
       <c r="AJ964" s="2"/>
     </row>
-    <row r="965" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:36" ht="15.95" customHeight="1">
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
       <c r="C965" s="2"/>
@@ -37908,7 +37914,7 @@
       <c r="AI965" s="2"/>
       <c r="AJ965" s="2"/>
     </row>
-    <row r="966" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:36" ht="15.95" customHeight="1">
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
       <c r="C966" s="2"/>
@@ -37946,7 +37952,7 @@
       <c r="AI966" s="2"/>
       <c r="AJ966" s="2"/>
     </row>
-    <row r="967" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:36" ht="15.95" customHeight="1">
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
       <c r="C967" s="2"/>
@@ -37984,7 +37990,7 @@
       <c r="AI967" s="2"/>
       <c r="AJ967" s="2"/>
     </row>
-    <row r="968" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:36" ht="15.95" customHeight="1">
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
       <c r="C968" s="2"/>
@@ -38022,7 +38028,7 @@
       <c r="AI968" s="2"/>
       <c r="AJ968" s="2"/>
     </row>
-    <row r="969" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:36" ht="15.95" customHeight="1">
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
       <c r="C969" s="2"/>
@@ -38060,7 +38066,7 @@
       <c r="AI969" s="2"/>
       <c r="AJ969" s="2"/>
     </row>
-    <row r="970" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:36" ht="15.95" customHeight="1">
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
       <c r="C970" s="2"/>
@@ -38098,7 +38104,7 @@
       <c r="AI970" s="2"/>
       <c r="AJ970" s="2"/>
     </row>
-    <row r="971" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:36" ht="15.95" customHeight="1">
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
       <c r="C971" s="2"/>
@@ -38136,7 +38142,7 @@
       <c r="AI971" s="2"/>
       <c r="AJ971" s="2"/>
     </row>
-    <row r="972" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:36" ht="15.95" customHeight="1">
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
       <c r="C972" s="2"/>
@@ -38174,7 +38180,7 @@
       <c r="AI972" s="2"/>
       <c r="AJ972" s="2"/>
     </row>
-    <row r="973" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:36" ht="15.95" customHeight="1">
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
       <c r="C973" s="2"/>
@@ -38212,7 +38218,7 @@
       <c r="AI973" s="2"/>
       <c r="AJ973" s="2"/>
     </row>
-    <row r="974" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:36" ht="15.95" customHeight="1">
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
       <c r="C974" s="2"/>
@@ -38250,7 +38256,7 @@
       <c r="AI974" s="2"/>
       <c r="AJ974" s="2"/>
     </row>
-    <row r="975" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:36" ht="15.95" customHeight="1">
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
       <c r="C975" s="2"/>
@@ -38288,7 +38294,7 @@
       <c r="AI975" s="2"/>
       <c r="AJ975" s="2"/>
     </row>
-    <row r="976" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:36" ht="15.95" customHeight="1">
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
       <c r="C976" s="2"/>
@@ -38326,7 +38332,7 @@
       <c r="AI976" s="2"/>
       <c r="AJ976" s="2"/>
     </row>
-    <row r="977" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:36" ht="15.95" customHeight="1">
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
       <c r="C977" s="2"/>
@@ -38364,7 +38370,7 @@
       <c r="AI977" s="2"/>
       <c r="AJ977" s="2"/>
     </row>
-    <row r="978" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:36" ht="15.95" customHeight="1">
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
       <c r="C978" s="2"/>
@@ -38402,7 +38408,7 @@
       <c r="AI978" s="2"/>
       <c r="AJ978" s="2"/>
     </row>
-    <row r="979" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:36" ht="15.95" customHeight="1">
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
       <c r="C979" s="2"/>
@@ -38440,7 +38446,7 @@
       <c r="AI979" s="2"/>
       <c r="AJ979" s="2"/>
     </row>
-    <row r="980" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:36" ht="15.95" customHeight="1">
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
       <c r="C980" s="2"/>
@@ -38478,7 +38484,7 @@
       <c r="AI980" s="2"/>
       <c r="AJ980" s="2"/>
     </row>
-    <row r="981" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:36" ht="15.95" customHeight="1">
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
       <c r="C981" s="2"/>
@@ -38516,7 +38522,7 @@
       <c r="AI981" s="2"/>
       <c r="AJ981" s="2"/>
     </row>
-    <row r="982" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:36" ht="15.95" customHeight="1">
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
       <c r="C982" s="2"/>
@@ -38554,7 +38560,7 @@
       <c r="AI982" s="2"/>
       <c r="AJ982" s="2"/>
     </row>
-    <row r="983" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:36" ht="15.95" customHeight="1">
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
       <c r="C983" s="2"/>
@@ -38592,7 +38598,7 @@
       <c r="AI983" s="2"/>
       <c r="AJ983" s="2"/>
     </row>
-    <row r="984" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:36" ht="15.95" customHeight="1">
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
       <c r="C984" s="2"/>
@@ -38630,7 +38636,7 @@
       <c r="AI984" s="2"/>
       <c r="AJ984" s="2"/>
     </row>
-    <row r="985" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:36" ht="15.95" customHeight="1">
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
       <c r="C985" s="2"/>
@@ -38668,7 +38674,7 @@
       <c r="AI985" s="2"/>
       <c r="AJ985" s="2"/>
     </row>
-    <row r="986" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:36" ht="15.95" customHeight="1">
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
       <c r="C986" s="2"/>
@@ -38706,7 +38712,7 @@
       <c r="AI986" s="2"/>
       <c r="AJ986" s="2"/>
     </row>
-    <row r="987" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:36" ht="15.95" customHeight="1">
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
       <c r="C987" s="2"/>
@@ -38744,7 +38750,7 @@
       <c r="AI987" s="2"/>
       <c r="AJ987" s="2"/>
     </row>
-    <row r="988" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:36" ht="15.95" customHeight="1">
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
       <c r="C988" s="2"/>
@@ -38782,7 +38788,7 @@
       <c r="AI988" s="2"/>
       <c r="AJ988" s="2"/>
     </row>
-    <row r="989" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:36" ht="15.95" customHeight="1">
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
       <c r="C989" s="2"/>
@@ -38820,7 +38826,7 @@
       <c r="AI989" s="2"/>
       <c r="AJ989" s="2"/>
     </row>
-    <row r="990" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:36" ht="15.95" customHeight="1">
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
       <c r="C990" s="2"/>
@@ -38858,7 +38864,7 @@
       <c r="AI990" s="2"/>
       <c r="AJ990" s="2"/>
     </row>
-    <row r="991" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:36" ht="15.95" customHeight="1">
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
       <c r="C991" s="2"/>
@@ -38896,7 +38902,7 @@
       <c r="AI991" s="2"/>
       <c r="AJ991" s="2"/>
     </row>
-    <row r="992" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:36" ht="15.95" customHeight="1">
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
       <c r="C992" s="2"/>
@@ -38934,7 +38940,7 @@
       <c r="AI992" s="2"/>
       <c r="AJ992" s="2"/>
     </row>
-    <row r="993" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:36" ht="15.95" customHeight="1">
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
       <c r="C993" s="2"/>
@@ -38972,7 +38978,7 @@
       <c r="AI993" s="2"/>
       <c r="AJ993" s="2"/>
     </row>
-    <row r="994" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:36" ht="15.95" customHeight="1">
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
       <c r="C994" s="2"/>
@@ -39010,7 +39016,7 @@
       <c r="AI994" s="2"/>
       <c r="AJ994" s="2"/>
     </row>
-    <row r="995" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:36" ht="15.95" customHeight="1">
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
       <c r="C995" s="2"/>
@@ -39048,7 +39054,7 @@
       <c r="AI995" s="2"/>
       <c r="AJ995" s="2"/>
     </row>
-    <row r="996" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:36" ht="15.95" customHeight="1">
       <c r="A996" s="2"/>
       <c r="B996" s="2"/>
       <c r="C996" s="2"/>
@@ -39086,7 +39092,7 @@
       <c r="AI996" s="2"/>
       <c r="AJ996" s="2"/>
     </row>
-    <row r="997" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:36" ht="15.95" customHeight="1">
       <c r="A997" s="2"/>
       <c r="B997" s="2"/>
       <c r="C997" s="2"/>
@@ -39124,7 +39130,7 @@
       <c r="AI997" s="2"/>
       <c r="AJ997" s="2"/>
     </row>
-    <row r="998" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:36" ht="15.95" customHeight="1">
       <c r="A998" s="2"/>
       <c r="B998" s="2"/>
       <c r="C998" s="2"/>
@@ -39162,7 +39168,7 @@
       <c r="AI998" s="2"/>
       <c r="AJ998" s="2"/>
     </row>
-    <row r="999" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:36" ht="15.95" customHeight="1">
       <c r="A999" s="2"/>
       <c r="B999" s="2"/>
       <c r="C999" s="2"/>
@@ -39200,7 +39206,7 @@
       <c r="AI999" s="2"/>
       <c r="AJ999" s="2"/>
     </row>
-    <row r="1000" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:36" ht="15.95" customHeight="1">
       <c r="A1000" s="2"/>
       <c r="B1000" s="2"/>
       <c r="C1000" s="2"/>
@@ -39244,6 +39250,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -39254,15 +39269,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -39523,44 +39529,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="06a0b0f5-ab3f-4382-8730-459fb424e421"/>
-    <ds:schemaRef ds:uri="26f1519c-0a18-4175-bd8e-760b6597752e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D55B629F-9BAD-43E6-819F-B097A47F8C05}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44B7B1D8-F3F2-46A8-A792-B679C78EEEEB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EAF4117-7505-4BC4-BAFA-FEDB85CDF386}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="26f1519c-0a18-4175-bd8e-760b6597752e"/>
-    <ds:schemaRef ds:uri="def454d3-7361-4a53-bd39-35a8c96a39c0"/>
-    <ds:schemaRef ds:uri="06a0b0f5-ab3f-4382-8730-459fb424e421"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EAF4117-7505-4BC4-BAFA-FEDB85CDF386}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
